--- a/업체정보/업체정보_간편입력.xlsx
+++ b/업체정보/업체정보_간편입력.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="306">
   <si>
     <t>상호명</t>
   </si>
@@ -737,6 +737,398 @@
   </si>
   <si>
     <t>010-3443-0056</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">서울 강남구 강남대로62길 23 역삼빌딩 1층 </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>다슬음</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>0507-1484-3401</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울 마포구 와우산로17길 19-17 1층</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>맷집</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>0507-1384-7968</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울 송파구 오금로11길 37 109호</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>호락호락</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>0507-1341-2682</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울 강서구 강서로5나길 16 1층</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>0507-1325-2538</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>까치집</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>경기 남양주시 진접읍 해밀예당3로 7 2층</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>술로맨스</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>0507-1329-7286</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울 영등포구 도림로 445 102호</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>문래가온</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>0507-1336-1858</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>경기 안양시 만안구 장내로 101 지상1층</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>야간매점</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>010-6293-3439</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울 강남구 학동로 342 SK허브블루상가 1층</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>중앙실비</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>0507-1391-0320</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">서울 강남구 도산대로45길 10-2 1층 </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>트키</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>0507-1370-2654</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울 강남구 학동로53길 19 1층</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>타카이</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>0507-1455-0321</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울 강남구 도산대로49길 6-7 1층</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>더코너하우스</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>0507-1394-5990</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>테라스석 동반 가능</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>오제 오징어제육</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울 강남구 도산대로27길 40 1층</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>0507-1404-3971</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울 강남구 논현로139길 12</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>모스가든</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>0507-1489-1988</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>룸 동반 가능</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울 강남구 학동로 343 B1층 구월의소철</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>0507-1417-3212</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>구월의 소철</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">서울 강남구 학동로21길 6 </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>파퓰러커피</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>0507-1342-5064</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울 동대문구 장한로6길 53 102호</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>동대문대하구이사계절집</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>0507-1370-4530</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울 중구 다산로46길 36 2층, 3층, 4층</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>신당육</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>02-6953-8816</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>소형견 가능</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>소형견 가능 리드줄 필수</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">서울 중구 퇴계로 409-11 1층 </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>심세정</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>0507-1444-7579</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>별관, 테라스 가능</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울 광진구 능동로 264 한사랑빌딩 1층</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울돼지구이</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>0507-1336-1116</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">서울 중구 청계천로 360 나동 104호 </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wnch동묘(운치)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>0507-1330-8166</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>유모차, 케이지 필수</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>케이지 필수</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>전시회</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울 동대문구 왕산로 131 2층</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>0507-1394-8570</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>소형견, 테라스 가능</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울 중구 다산로 232 1층</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>오신돼지갈비</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>0507-1357-9288</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>유모차, 케이지 필수</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울 성북구 동소문로22길 64 1층</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>금뚜껑</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>0507-1361-0997</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>테라스 가능</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">서울 중랑구 봉우재로43길 12 1층 </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>피자빌리지</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>0507-1448-1263</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울 성북구 동소문로22길 57-16 1층</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>메종 드 잠봉</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>0507-1403-0031</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울 성북구 고려대로7길 48 1층</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>운치</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>0507-1475-4644</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울 중구 퇴계로81길 10 1층</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>누리담</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>0507-1386-3922</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>유모차, 케이지 필수</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울 중구 퇴계로 461 1층 101호</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>보메청담</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>02-2233-0937</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울 성북구 고려대로1길 69 1층</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>펫터니아 하우스</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>0507-1334-2014</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -3365,641 +3757,1535 @@
       </c>
     </row>
     <row r="38" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A38" s="14"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="15"/>
-      <c r="E38" s="15"/>
-      <c r="F38" s="15"/>
-      <c r="G38" s="15"/>
-      <c r="H38" s="15"/>
-      <c r="I38" s="15"/>
-      <c r="J38" s="16"/>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="16"/>
-      <c r="O38" s="19"/>
+      <c r="A38" s="14" t="s">
+        <v>209</v>
+      </c>
+      <c r="B38" s="14" t="s">
+        <v>208</v>
+      </c>
+      <c r="C38" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="D38" s="15">
+        <v>0</v>
+      </c>
+      <c r="E38" s="15">
+        <v>0</v>
+      </c>
+      <c r="F38" s="15">
+        <v>0</v>
+      </c>
+      <c r="G38" s="15">
+        <v>0</v>
+      </c>
+      <c r="H38" s="15">
+        <v>1</v>
+      </c>
+      <c r="I38" s="15">
+        <v>0</v>
+      </c>
+      <c r="J38" s="16">
+        <v>0</v>
+      </c>
+      <c r="K38" s="16">
+        <v>1</v>
+      </c>
+      <c r="L38" s="16">
+        <v>0</v>
+      </c>
+      <c r="M38" s="16">
+        <v>0</v>
+      </c>
+      <c r="N38" s="16">
+        <v>0</v>
+      </c>
+      <c r="O38" s="19">
+        <v>0</v>
+      </c>
       <c r="P38" s="14"/>
       <c r="Q38" s="17" t="str">
         <f>IF(LEN(TRIM(B38))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B38),FIND(" ",TRIM(B38)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B38),FIND(" ",TRIM(B38)&amp;" ")-1)))</f>
-        <v/>
+        <v>서울</v>
       </c>
     </row>
     <row r="39" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A39" s="14"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="15"/>
-      <c r="E39" s="15"/>
-      <c r="F39" s="15"/>
-      <c r="G39" s="15"/>
-      <c r="H39" s="15"/>
-      <c r="I39" s="15"/>
-      <c r="J39" s="16"/>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="16"/>
-      <c r="O39" s="19"/>
+      <c r="A39" s="14" t="s">
+        <v>212</v>
+      </c>
+      <c r="B39" s="14" t="s">
+        <v>211</v>
+      </c>
+      <c r="C39" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="D39" s="15">
+        <v>0</v>
+      </c>
+      <c r="E39" s="15">
+        <v>0</v>
+      </c>
+      <c r="F39" s="15">
+        <v>0</v>
+      </c>
+      <c r="G39" s="15">
+        <v>0</v>
+      </c>
+      <c r="H39" s="15">
+        <v>1</v>
+      </c>
+      <c r="I39" s="15">
+        <v>0</v>
+      </c>
+      <c r="J39" s="16">
+        <v>0</v>
+      </c>
+      <c r="K39" s="16">
+        <v>1</v>
+      </c>
+      <c r="L39" s="16">
+        <v>0</v>
+      </c>
+      <c r="M39" s="16">
+        <v>0</v>
+      </c>
+      <c r="N39" s="16">
+        <v>0</v>
+      </c>
+      <c r="O39" s="19">
+        <v>0</v>
+      </c>
       <c r="P39" s="14"/>
       <c r="Q39" s="17" t="str">
         <f>IF(LEN(TRIM(B39))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B39),FIND(" ",TRIM(B39)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B39),FIND(" ",TRIM(B39)&amp;" ")-1)))</f>
-        <v/>
+        <v>서울</v>
       </c>
     </row>
     <row r="40" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A40" s="14"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="15"/>
-      <c r="E40" s="15"/>
-      <c r="F40" s="15"/>
-      <c r="G40" s="15"/>
-      <c r="H40" s="15"/>
-      <c r="I40" s="15"/>
-      <c r="J40" s="16"/>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="16"/>
-      <c r="O40" s="19"/>
+      <c r="A40" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="B40" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="C40" s="14" t="s">
+        <v>216</v>
+      </c>
+      <c r="D40" s="15">
+        <v>0</v>
+      </c>
+      <c r="E40" s="15">
+        <v>0</v>
+      </c>
+      <c r="F40" s="15">
+        <v>0</v>
+      </c>
+      <c r="G40" s="15">
+        <v>0</v>
+      </c>
+      <c r="H40" s="15">
+        <v>1</v>
+      </c>
+      <c r="I40" s="15">
+        <v>0</v>
+      </c>
+      <c r="J40" s="16">
+        <v>0</v>
+      </c>
+      <c r="K40" s="16">
+        <v>1</v>
+      </c>
+      <c r="L40" s="16">
+        <v>0</v>
+      </c>
+      <c r="M40" s="16">
+        <v>0</v>
+      </c>
+      <c r="N40" s="16">
+        <v>0</v>
+      </c>
+      <c r="O40" s="19">
+        <v>0</v>
+      </c>
       <c r="P40" s="14"/>
       <c r="Q40" s="17" t="str">
         <f>IF(LEN(TRIM(B40))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B40),FIND(" ",TRIM(B40)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B40),FIND(" ",TRIM(B40)&amp;" ")-1)))</f>
-        <v/>
+        <v>서울</v>
       </c>
     </row>
     <row r="41" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A41" s="14"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="15"/>
-      <c r="E41" s="15"/>
-      <c r="F41" s="15"/>
-      <c r="G41" s="15"/>
-      <c r="H41" s="15"/>
-      <c r="I41" s="15"/>
-      <c r="J41" s="16"/>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
-      <c r="N41" s="16"/>
-      <c r="O41" s="19"/>
+      <c r="A41" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="B41" s="14" t="s">
+        <v>217</v>
+      </c>
+      <c r="C41" s="14" t="s">
+        <v>218</v>
+      </c>
+      <c r="D41" s="15">
+        <v>0</v>
+      </c>
+      <c r="E41" s="15">
+        <v>0</v>
+      </c>
+      <c r="F41" s="15">
+        <v>0</v>
+      </c>
+      <c r="G41" s="15">
+        <v>0</v>
+      </c>
+      <c r="H41" s="15">
+        <v>1</v>
+      </c>
+      <c r="I41" s="15">
+        <v>0</v>
+      </c>
+      <c r="J41" s="16">
+        <v>1</v>
+      </c>
+      <c r="K41" s="16">
+        <v>1</v>
+      </c>
+      <c r="L41" s="16">
+        <v>0</v>
+      </c>
+      <c r="M41" s="16">
+        <v>0</v>
+      </c>
+      <c r="N41" s="16">
+        <v>0</v>
+      </c>
+      <c r="O41" s="19">
+        <v>0</v>
+      </c>
       <c r="P41" s="14"/>
       <c r="Q41" s="17" t="str">
         <f>IF(LEN(TRIM(B41))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B41),FIND(" ",TRIM(B41)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B41),FIND(" ",TRIM(B41)&amp;" ")-1)))</f>
-        <v/>
+        <v>서울</v>
       </c>
     </row>
     <row r="42" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A42" s="14"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="15"/>
-      <c r="E42" s="15"/>
-      <c r="F42" s="15"/>
-      <c r="G42" s="15"/>
-      <c r="H42" s="15"/>
-      <c r="I42" s="15"/>
-      <c r="J42" s="16"/>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
-      <c r="N42" s="16"/>
-      <c r="O42" s="19"/>
+      <c r="A42" s="14" t="s">
+        <v>221</v>
+      </c>
+      <c r="B42" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="C42" s="14" t="s">
+        <v>222</v>
+      </c>
+      <c r="D42" s="15">
+        <v>0</v>
+      </c>
+      <c r="E42" s="15">
+        <v>0</v>
+      </c>
+      <c r="F42" s="15">
+        <v>0</v>
+      </c>
+      <c r="G42" s="15">
+        <v>0</v>
+      </c>
+      <c r="H42" s="15">
+        <v>1</v>
+      </c>
+      <c r="I42" s="15">
+        <v>0</v>
+      </c>
+      <c r="J42" s="16">
+        <v>1</v>
+      </c>
+      <c r="K42" s="16">
+        <v>1</v>
+      </c>
+      <c r="L42" s="16">
+        <v>1</v>
+      </c>
+      <c r="M42" s="16">
+        <v>0</v>
+      </c>
+      <c r="N42" s="16">
+        <v>0</v>
+      </c>
+      <c r="O42" s="19">
+        <v>0</v>
+      </c>
       <c r="P42" s="14"/>
       <c r="Q42" s="17" t="str">
         <f>IF(LEN(TRIM(B42))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B42),FIND(" ",TRIM(B42)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B42),FIND(" ",TRIM(B42)&amp;" ")-1)))</f>
-        <v/>
+        <v>경기</v>
       </c>
     </row>
     <row r="43" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A43" s="14"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="15"/>
-      <c r="E43" s="15"/>
-      <c r="F43" s="15"/>
-      <c r="G43" s="15"/>
-      <c r="H43" s="15"/>
-      <c r="I43" s="15"/>
-      <c r="J43" s="16"/>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
-      <c r="N43" s="16"/>
-      <c r="O43" s="19"/>
+      <c r="A43" s="14" t="s">
+        <v>224</v>
+      </c>
+      <c r="B43" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="C43" s="14" t="s">
+        <v>225</v>
+      </c>
+      <c r="D43" s="15">
+        <v>0</v>
+      </c>
+      <c r="E43" s="15">
+        <v>0</v>
+      </c>
+      <c r="F43" s="15">
+        <v>0</v>
+      </c>
+      <c r="G43" s="15">
+        <v>0</v>
+      </c>
+      <c r="H43" s="15">
+        <v>1</v>
+      </c>
+      <c r="I43" s="15">
+        <v>0</v>
+      </c>
+      <c r="J43" s="16">
+        <v>1</v>
+      </c>
+      <c r="K43" s="16">
+        <v>1</v>
+      </c>
+      <c r="L43" s="16">
+        <v>0</v>
+      </c>
+      <c r="M43" s="16">
+        <v>0</v>
+      </c>
+      <c r="N43" s="16">
+        <v>0</v>
+      </c>
+      <c r="O43" s="19">
+        <v>0</v>
+      </c>
       <c r="P43" s="14"/>
       <c r="Q43" s="17" t="str">
         <f>IF(LEN(TRIM(B43))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B43),FIND(" ",TRIM(B43)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B43),FIND(" ",TRIM(B43)&amp;" ")-1)))</f>
-        <v/>
+        <v>서울</v>
       </c>
     </row>
     <row r="44" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A44" s="14"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="15"/>
-      <c r="E44" s="15"/>
-      <c r="F44" s="15"/>
-      <c r="G44" s="15"/>
-      <c r="H44" s="15"/>
-      <c r="I44" s="15"/>
-      <c r="J44" s="16"/>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
-      <c r="N44" s="16"/>
-      <c r="O44" s="19"/>
+      <c r="A44" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="B44" s="14" t="s">
+        <v>226</v>
+      </c>
+      <c r="C44" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="D44" s="15">
+        <v>0</v>
+      </c>
+      <c r="E44" s="15">
+        <v>0</v>
+      </c>
+      <c r="F44" s="15">
+        <v>0</v>
+      </c>
+      <c r="G44" s="15">
+        <v>0</v>
+      </c>
+      <c r="H44" s="15">
+        <v>1</v>
+      </c>
+      <c r="I44" s="15">
+        <v>0</v>
+      </c>
+      <c r="J44" s="16">
+        <v>0</v>
+      </c>
+      <c r="K44" s="16">
+        <v>1</v>
+      </c>
+      <c r="L44" s="16">
+        <v>0</v>
+      </c>
+      <c r="M44" s="16">
+        <v>0</v>
+      </c>
+      <c r="N44" s="16">
+        <v>0</v>
+      </c>
+      <c r="O44" s="19">
+        <v>0</v>
+      </c>
       <c r="P44" s="14"/>
       <c r="Q44" s="17" t="str">
         <f>IF(LEN(TRIM(B44))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B44),FIND(" ",TRIM(B44)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B44),FIND(" ",TRIM(B44)&amp;" ")-1)))</f>
-        <v/>
+        <v>경기</v>
       </c>
     </row>
     <row r="45" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A45" s="14"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="15"/>
-      <c r="E45" s="15"/>
-      <c r="F45" s="15"/>
-      <c r="G45" s="15"/>
-      <c r="H45" s="15"/>
-      <c r="I45" s="15"/>
-      <c r="J45" s="16"/>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
-      <c r="N45" s="16"/>
-      <c r="O45" s="19"/>
+      <c r="A45" s="14" t="s">
+        <v>230</v>
+      </c>
+      <c r="B45" s="14" t="s">
+        <v>229</v>
+      </c>
+      <c r="C45" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="D45" s="15">
+        <v>0</v>
+      </c>
+      <c r="E45" s="15">
+        <v>0</v>
+      </c>
+      <c r="F45" s="15">
+        <v>0</v>
+      </c>
+      <c r="G45" s="15">
+        <v>0</v>
+      </c>
+      <c r="H45" s="15">
+        <v>1</v>
+      </c>
+      <c r="I45" s="15">
+        <v>0</v>
+      </c>
+      <c r="J45" s="16">
+        <v>1</v>
+      </c>
+      <c r="K45" s="16">
+        <v>1</v>
+      </c>
+      <c r="L45" s="16">
+        <v>0</v>
+      </c>
+      <c r="M45" s="16">
+        <v>0</v>
+      </c>
+      <c r="N45" s="16">
+        <v>0</v>
+      </c>
+      <c r="O45" s="19">
+        <v>0</v>
+      </c>
       <c r="P45" s="14"/>
       <c r="Q45" s="17" t="str">
         <f>IF(LEN(TRIM(B45))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B45),FIND(" ",TRIM(B45)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B45),FIND(" ",TRIM(B45)&amp;" ")-1)))</f>
-        <v/>
+        <v>서울</v>
       </c>
     </row>
     <row r="46" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A46" s="14"/>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="15"/>
-      <c r="E46" s="15"/>
-      <c r="F46" s="15"/>
-      <c r="G46" s="15"/>
-      <c r="H46" s="15"/>
-      <c r="I46" s="15"/>
-      <c r="J46" s="16"/>
-      <c r="K46" s="16"/>
-      <c r="L46" s="16"/>
-      <c r="M46" s="16"/>
-      <c r="N46" s="16"/>
-      <c r="O46" s="19"/>
+      <c r="A46" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="B46" s="14" t="s">
+        <v>232</v>
+      </c>
+      <c r="C46" s="14" t="s">
+        <v>234</v>
+      </c>
+      <c r="D46" s="15">
+        <v>0</v>
+      </c>
+      <c r="E46" s="15">
+        <v>1</v>
+      </c>
+      <c r="F46" s="15">
+        <v>0</v>
+      </c>
+      <c r="G46" s="15">
+        <v>0</v>
+      </c>
+      <c r="H46" s="15">
+        <v>0</v>
+      </c>
+      <c r="I46" s="15">
+        <v>0</v>
+      </c>
+      <c r="J46" s="16">
+        <v>1</v>
+      </c>
+      <c r="K46" s="16">
+        <v>1</v>
+      </c>
+      <c r="L46" s="16">
+        <v>1</v>
+      </c>
+      <c r="M46" s="16">
+        <v>0</v>
+      </c>
+      <c r="N46" s="16">
+        <v>0</v>
+      </c>
+      <c r="O46" s="19">
+        <v>0</v>
+      </c>
       <c r="P46" s="14"/>
       <c r="Q46" s="17" t="str">
         <f>IF(LEN(TRIM(B46))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B46),FIND(" ",TRIM(B46)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B46),FIND(" ",TRIM(B46)&amp;" ")-1)))</f>
-        <v/>
+        <v>서울</v>
       </c>
     </row>
     <row r="47" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A47" s="14"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="15"/>
-      <c r="E47" s="15"/>
-      <c r="F47" s="15"/>
-      <c r="G47" s="15"/>
-      <c r="H47" s="15"/>
-      <c r="I47" s="15"/>
-      <c r="J47" s="16"/>
-      <c r="K47" s="16"/>
-      <c r="L47" s="16"/>
-      <c r="M47" s="16"/>
-      <c r="N47" s="16"/>
-      <c r="O47" s="19"/>
+      <c r="A47" s="14" t="s">
+        <v>236</v>
+      </c>
+      <c r="B47" s="14" t="s">
+        <v>235</v>
+      </c>
+      <c r="C47" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="D47" s="15">
+        <v>0</v>
+      </c>
+      <c r="E47" s="15">
+        <v>0</v>
+      </c>
+      <c r="F47" s="15">
+        <v>0</v>
+      </c>
+      <c r="G47" s="15">
+        <v>1</v>
+      </c>
+      <c r="H47" s="15">
+        <v>0</v>
+      </c>
+      <c r="I47" s="15">
+        <v>0</v>
+      </c>
+      <c r="J47" s="16">
+        <v>1</v>
+      </c>
+      <c r="K47" s="16">
+        <v>1</v>
+      </c>
+      <c r="L47" s="16">
+        <v>0</v>
+      </c>
+      <c r="M47" s="16">
+        <v>0</v>
+      </c>
+      <c r="N47" s="16">
+        <v>0</v>
+      </c>
+      <c r="O47" s="19">
+        <v>0</v>
+      </c>
       <c r="P47" s="14"/>
       <c r="Q47" s="17" t="str">
         <f>IF(LEN(TRIM(B47))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B47),FIND(" ",TRIM(B47)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B47),FIND(" ",TRIM(B47)&amp;" ")-1)))</f>
-        <v/>
+        <v>서울</v>
       </c>
     </row>
     <row r="48" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A48" s="14"/>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="15"/>
-      <c r="E48" s="15"/>
-      <c r="F48" s="15"/>
-      <c r="G48" s="15"/>
-      <c r="H48" s="15"/>
-      <c r="I48" s="15"/>
-      <c r="J48" s="16"/>
-      <c r="K48" s="16"/>
-      <c r="L48" s="16"/>
-      <c r="M48" s="16"/>
-      <c r="N48" s="16"/>
-      <c r="O48" s="19"/>
-      <c r="P48" s="14"/>
+      <c r="A48" s="14" t="s">
+        <v>239</v>
+      </c>
+      <c r="B48" s="14" t="s">
+        <v>238</v>
+      </c>
+      <c r="C48" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="D48" s="15">
+        <v>0</v>
+      </c>
+      <c r="E48" s="15">
+        <v>0</v>
+      </c>
+      <c r="F48" s="15">
+        <v>0</v>
+      </c>
+      <c r="G48" s="15">
+        <v>1</v>
+      </c>
+      <c r="H48" s="15">
+        <v>0</v>
+      </c>
+      <c r="I48" s="15">
+        <v>0</v>
+      </c>
+      <c r="J48" s="16">
+        <v>1</v>
+      </c>
+      <c r="K48" s="16">
+        <v>0</v>
+      </c>
+      <c r="L48" s="16">
+        <v>1</v>
+      </c>
+      <c r="M48" s="16">
+        <v>0</v>
+      </c>
+      <c r="N48" s="16">
+        <v>0</v>
+      </c>
+      <c r="O48" s="19">
+        <v>0</v>
+      </c>
+      <c r="P48" s="14" t="s">
+        <v>241</v>
+      </c>
       <c r="Q48" s="17" t="str">
         <f>IF(LEN(TRIM(B48))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B48),FIND(" ",TRIM(B48)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B48),FIND(" ",TRIM(B48)&amp;" ")-1)))</f>
-        <v/>
+        <v>서울</v>
       </c>
     </row>
     <row r="49" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A49" s="14"/>
-      <c r="B49" s="14"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="15"/>
-      <c r="E49" s="15"/>
-      <c r="F49" s="15"/>
-      <c r="G49" s="15"/>
-      <c r="H49" s="15"/>
-      <c r="I49" s="15"/>
-      <c r="J49" s="16"/>
-      <c r="K49" s="16"/>
-      <c r="L49" s="16"/>
-      <c r="M49" s="16"/>
-      <c r="N49" s="16"/>
-      <c r="O49" s="19"/>
+      <c r="A49" s="14" t="s">
+        <v>242</v>
+      </c>
+      <c r="B49" s="14" t="s">
+        <v>243</v>
+      </c>
+      <c r="C49" s="14" t="s">
+        <v>244</v>
+      </c>
+      <c r="D49" s="15">
+        <v>0</v>
+      </c>
+      <c r="E49" s="15">
+        <v>0</v>
+      </c>
+      <c r="F49" s="15">
+        <v>0</v>
+      </c>
+      <c r="G49" s="15">
+        <v>1</v>
+      </c>
+      <c r="H49" s="15">
+        <v>0</v>
+      </c>
+      <c r="I49" s="15">
+        <v>0</v>
+      </c>
+      <c r="J49" s="16">
+        <v>0</v>
+      </c>
+      <c r="K49" s="16">
+        <v>1</v>
+      </c>
+      <c r="L49" s="16">
+        <v>0</v>
+      </c>
+      <c r="M49" s="16">
+        <v>0</v>
+      </c>
+      <c r="N49" s="16">
+        <v>0</v>
+      </c>
+      <c r="O49" s="19">
+        <v>0</v>
+      </c>
       <c r="P49" s="14"/>
       <c r="Q49" s="17" t="str">
         <f>IF(LEN(TRIM(B49))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B49),FIND(" ",TRIM(B49)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B49),FIND(" ",TRIM(B49)&amp;" ")-1)))</f>
-        <v/>
+        <v>서울</v>
       </c>
     </row>
     <row r="50" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A50" s="14"/>
-      <c r="B50" s="14"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="15"/>
-      <c r="E50" s="15"/>
-      <c r="F50" s="15"/>
-      <c r="G50" s="15"/>
-      <c r="H50" s="15"/>
-      <c r="I50" s="15"/>
-      <c r="J50" s="16"/>
-      <c r="K50" s="16"/>
-      <c r="L50" s="16"/>
-      <c r="M50" s="16"/>
-      <c r="N50" s="16"/>
-      <c r="O50" s="19"/>
+      <c r="A50" s="14" t="s">
+        <v>246</v>
+      </c>
+      <c r="B50" s="14" t="s">
+        <v>245</v>
+      </c>
+      <c r="C50" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="D50" s="15">
+        <v>0</v>
+      </c>
+      <c r="E50" s="15">
+        <v>0</v>
+      </c>
+      <c r="F50" s="15">
+        <v>0</v>
+      </c>
+      <c r="G50" s="15">
+        <v>1</v>
+      </c>
+      <c r="H50" s="15">
+        <v>0</v>
+      </c>
+      <c r="I50" s="15">
+        <v>0</v>
+      </c>
+      <c r="J50" s="16">
+        <v>1</v>
+      </c>
+      <c r="K50" s="16">
+        <v>1</v>
+      </c>
+      <c r="L50" s="16">
+        <v>0</v>
+      </c>
+      <c r="M50" s="16">
+        <v>0</v>
+      </c>
+      <c r="N50" s="16">
+        <v>0</v>
+      </c>
+      <c r="O50" s="19">
+        <v>0</v>
+      </c>
       <c r="P50" s="14"/>
       <c r="Q50" s="17" t="str">
         <f>IF(LEN(TRIM(B50))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B50),FIND(" ",TRIM(B50)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B50),FIND(" ",TRIM(B50)&amp;" ")-1)))</f>
-        <v/>
+        <v>서울</v>
       </c>
     </row>
     <row r="51" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A51" s="14"/>
-      <c r="B51" s="14"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="15"/>
-      <c r="E51" s="15"/>
-      <c r="F51" s="15"/>
-      <c r="G51" s="15"/>
-      <c r="H51" s="15"/>
-      <c r="I51" s="15"/>
-      <c r="J51" s="16"/>
-      <c r="K51" s="16"/>
-      <c r="L51" s="16"/>
-      <c r="M51" s="16"/>
-      <c r="N51" s="16"/>
-      <c r="O51" s="19"/>
-      <c r="P51" s="14"/>
+      <c r="A51" s="14" t="s">
+        <v>251</v>
+      </c>
+      <c r="B51" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="C51" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="D51" s="15">
+        <v>0</v>
+      </c>
+      <c r="E51" s="15">
+        <v>0</v>
+      </c>
+      <c r="F51" s="15">
+        <v>0</v>
+      </c>
+      <c r="G51" s="15">
+        <v>0</v>
+      </c>
+      <c r="H51" s="15">
+        <v>1</v>
+      </c>
+      <c r="I51" s="15">
+        <v>0</v>
+      </c>
+      <c r="J51" s="16">
+        <v>1</v>
+      </c>
+      <c r="K51" s="16">
+        <v>1</v>
+      </c>
+      <c r="L51" s="16">
+        <v>0</v>
+      </c>
+      <c r="M51" s="16">
+        <v>0</v>
+      </c>
+      <c r="N51" s="16">
+        <v>0</v>
+      </c>
+      <c r="O51" s="19">
+        <v>0</v>
+      </c>
+      <c r="P51" s="14" t="s">
+        <v>248</v>
+      </c>
       <c r="Q51" s="17" t="str">
         <f>IF(LEN(TRIM(B51))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B51),FIND(" ",TRIM(B51)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B51),FIND(" ",TRIM(B51)&amp;" ")-1)))</f>
-        <v/>
+        <v>서울</v>
       </c>
     </row>
     <row r="52" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A52" s="14"/>
-      <c r="B52" s="14"/>
-      <c r="C52" s="14"/>
-      <c r="D52" s="15"/>
-      <c r="E52" s="15"/>
-      <c r="F52" s="15"/>
-      <c r="G52" s="15"/>
-      <c r="H52" s="15"/>
-      <c r="I52" s="15"/>
-      <c r="J52" s="16"/>
-      <c r="K52" s="16"/>
-      <c r="L52" s="16"/>
-      <c r="M52" s="16"/>
-      <c r="N52" s="16"/>
-      <c r="O52" s="19"/>
+      <c r="A52" s="14" t="s">
+        <v>253</v>
+      </c>
+      <c r="B52" s="14" t="s">
+        <v>252</v>
+      </c>
+      <c r="C52" s="14" t="s">
+        <v>254</v>
+      </c>
+      <c r="D52" s="15">
+        <v>0</v>
+      </c>
+      <c r="E52" s="15">
+        <v>1</v>
+      </c>
+      <c r="F52" s="15">
+        <v>0</v>
+      </c>
+      <c r="G52" s="15">
+        <v>0</v>
+      </c>
+      <c r="H52" s="15">
+        <v>0</v>
+      </c>
+      <c r="I52" s="15">
+        <v>0</v>
+      </c>
+      <c r="J52" s="16">
+        <v>0</v>
+      </c>
+      <c r="K52" s="16">
+        <v>1</v>
+      </c>
+      <c r="L52" s="16">
+        <v>1</v>
+      </c>
+      <c r="M52" s="16">
+        <v>0</v>
+      </c>
+      <c r="N52" s="16">
+        <v>0</v>
+      </c>
+      <c r="O52" s="19">
+        <v>0</v>
+      </c>
       <c r="P52" s="14"/>
       <c r="Q52" s="17" t="str">
         <f>IF(LEN(TRIM(B52))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B52),FIND(" ",TRIM(B52)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B52),FIND(" ",TRIM(B52)&amp;" ")-1)))</f>
-        <v/>
+        <v>서울</v>
       </c>
     </row>
     <row r="53" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A53" s="14"/>
-      <c r="B53" s="14"/>
-      <c r="C53" s="14"/>
-      <c r="D53" s="15"/>
-      <c r="E53" s="15"/>
-      <c r="F53" s="15"/>
-      <c r="G53" s="15"/>
-      <c r="H53" s="15"/>
-      <c r="I53" s="15"/>
-      <c r="J53" s="16"/>
-      <c r="K53" s="16"/>
-      <c r="L53" s="16"/>
-      <c r="M53" s="16"/>
-      <c r="N53" s="16"/>
-      <c r="O53" s="19"/>
-      <c r="P53" s="14"/>
+      <c r="A53" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="B53" s="14" t="s">
+        <v>255</v>
+      </c>
+      <c r="C53" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="D53" s="15">
+        <v>0</v>
+      </c>
+      <c r="E53" s="15">
+        <v>0</v>
+      </c>
+      <c r="F53" s="15">
+        <v>0</v>
+      </c>
+      <c r="G53" s="15">
+        <v>0</v>
+      </c>
+      <c r="H53" s="15">
+        <v>1</v>
+      </c>
+      <c r="I53" s="15">
+        <v>0</v>
+      </c>
+      <c r="J53" s="16">
+        <v>1</v>
+      </c>
+      <c r="K53" s="16">
+        <v>1</v>
+      </c>
+      <c r="L53" s="16">
+        <v>0</v>
+      </c>
+      <c r="M53" s="16">
+        <v>0</v>
+      </c>
+      <c r="N53" s="16">
+        <v>0</v>
+      </c>
+      <c r="O53" s="19">
+        <v>0</v>
+      </c>
+      <c r="P53" s="14" t="s">
+        <v>262</v>
+      </c>
       <c r="Q53" s="17" t="str">
         <f>IF(LEN(TRIM(B53))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B53),FIND(" ",TRIM(B53)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B53),FIND(" ",TRIM(B53)&amp;" ")-1)))</f>
-        <v/>
+        <v>서울</v>
       </c>
     </row>
     <row r="54" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A54" s="14"/>
-      <c r="B54" s="14"/>
-      <c r="C54" s="14"/>
-      <c r="D54" s="15"/>
-      <c r="E54" s="15"/>
-      <c r="F54" s="15"/>
-      <c r="G54" s="15"/>
-      <c r="H54" s="15"/>
-      <c r="I54" s="15"/>
-      <c r="J54" s="16"/>
-      <c r="K54" s="16"/>
-      <c r="L54" s="16"/>
-      <c r="M54" s="16"/>
-      <c r="N54" s="16"/>
-      <c r="O54" s="19"/>
-      <c r="P54" s="14"/>
+      <c r="A54" s="14" t="s">
+        <v>259</v>
+      </c>
+      <c r="B54" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="C54" s="14" t="s">
+        <v>260</v>
+      </c>
+      <c r="D54" s="15">
+        <v>0</v>
+      </c>
+      <c r="E54" s="15">
+        <v>0</v>
+      </c>
+      <c r="F54" s="15">
+        <v>0</v>
+      </c>
+      <c r="G54" s="15">
+        <v>1</v>
+      </c>
+      <c r="H54" s="15">
+        <v>1</v>
+      </c>
+      <c r="I54" s="15">
+        <v>0</v>
+      </c>
+      <c r="J54" s="16">
+        <v>1</v>
+      </c>
+      <c r="K54" s="16">
+        <v>1</v>
+      </c>
+      <c r="L54" s="16">
+        <v>1</v>
+      </c>
+      <c r="M54" s="16">
+        <v>0</v>
+      </c>
+      <c r="N54" s="16">
+        <v>0</v>
+      </c>
+      <c r="O54" s="19">
+        <v>0</v>
+      </c>
+      <c r="P54" s="14" t="s">
+        <v>261</v>
+      </c>
       <c r="Q54" s="17" t="str">
         <f>IF(LEN(TRIM(B54))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B54),FIND(" ",TRIM(B54)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B54),FIND(" ",TRIM(B54)&amp;" ")-1)))</f>
-        <v/>
+        <v>서울</v>
       </c>
     </row>
     <row r="55" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A55" s="14"/>
-      <c r="B55" s="14"/>
-      <c r="C55" s="14"/>
-      <c r="D55" s="15"/>
-      <c r="E55" s="15"/>
-      <c r="F55" s="15"/>
-      <c r="G55" s="15"/>
-      <c r="H55" s="15"/>
-      <c r="I55" s="15"/>
-      <c r="J55" s="16"/>
-      <c r="K55" s="16"/>
-      <c r="L55" s="16"/>
-      <c r="M55" s="16"/>
-      <c r="N55" s="16"/>
-      <c r="O55" s="19"/>
-      <c r="P55" s="14"/>
+      <c r="A55" s="14" t="s">
+        <v>264</v>
+      </c>
+      <c r="B55" s="14" t="s">
+        <v>263</v>
+      </c>
+      <c r="C55" s="14" t="s">
+        <v>265</v>
+      </c>
+      <c r="D55" s="15">
+        <v>0</v>
+      </c>
+      <c r="E55" s="15">
+        <v>1</v>
+      </c>
+      <c r="F55" s="15">
+        <v>0</v>
+      </c>
+      <c r="G55" s="15">
+        <v>0</v>
+      </c>
+      <c r="H55" s="15">
+        <v>0</v>
+      </c>
+      <c r="I55" s="15">
+        <v>0</v>
+      </c>
+      <c r="J55" s="16">
+        <v>0</v>
+      </c>
+      <c r="K55" s="16">
+        <v>0</v>
+      </c>
+      <c r="L55" s="16">
+        <v>1</v>
+      </c>
+      <c r="M55" s="16">
+        <v>0</v>
+      </c>
+      <c r="N55" s="16">
+        <v>0</v>
+      </c>
+      <c r="O55" s="19">
+        <v>0</v>
+      </c>
+      <c r="P55" s="14" t="s">
+        <v>266</v>
+      </c>
       <c r="Q55" s="17" t="str">
         <f>IF(LEN(TRIM(B55))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B55),FIND(" ",TRIM(B55)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B55),FIND(" ",TRIM(B55)&amp;" ")-1)))</f>
-        <v/>
+        <v>서울</v>
       </c>
     </row>
     <row r="56" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A56" s="14"/>
-      <c r="B56" s="14"/>
-      <c r="C56" s="14"/>
-      <c r="D56" s="15"/>
-      <c r="E56" s="15"/>
-      <c r="F56" s="15"/>
-      <c r="G56" s="15"/>
-      <c r="H56" s="15"/>
-      <c r="I56" s="15"/>
-      <c r="J56" s="16"/>
-      <c r="K56" s="16"/>
-      <c r="L56" s="16"/>
-      <c r="M56" s="16"/>
-      <c r="N56" s="16"/>
-      <c r="O56" s="19"/>
-      <c r="P56" s="14"/>
+      <c r="A56" s="14" t="s">
+        <v>268</v>
+      </c>
+      <c r="B56" s="14" t="s">
+        <v>267</v>
+      </c>
+      <c r="C56" s="14" t="s">
+        <v>269</v>
+      </c>
+      <c r="D56" s="15">
+        <v>0</v>
+      </c>
+      <c r="E56" s="15">
+        <v>0</v>
+      </c>
+      <c r="F56" s="15">
+        <v>0</v>
+      </c>
+      <c r="G56" s="15">
+        <v>0</v>
+      </c>
+      <c r="H56" s="15">
+        <v>1</v>
+      </c>
+      <c r="I56" s="15">
+        <v>0</v>
+      </c>
+      <c r="J56" s="16">
+        <v>1</v>
+      </c>
+      <c r="K56" s="16">
+        <v>1</v>
+      </c>
+      <c r="L56" s="16">
+        <v>0</v>
+      </c>
+      <c r="M56" s="16">
+        <v>0</v>
+      </c>
+      <c r="N56" s="16">
+        <v>0</v>
+      </c>
+      <c r="O56" s="19">
+        <v>0</v>
+      </c>
+      <c r="P56" s="14" t="s">
+        <v>273</v>
+      </c>
       <c r="Q56" s="17" t="str">
         <f>IF(LEN(TRIM(B56))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B56),FIND(" ",TRIM(B56)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B56),FIND(" ",TRIM(B56)&amp;" ")-1)))</f>
-        <v/>
+        <v>서울</v>
       </c>
     </row>
     <row r="57" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A57" s="14"/>
-      <c r="B57" s="14"/>
-      <c r="C57" s="14"/>
-      <c r="D57" s="15"/>
-      <c r="E57" s="15"/>
-      <c r="F57" s="15"/>
-      <c r="G57" s="15"/>
-      <c r="H57" s="15"/>
-      <c r="I57" s="15"/>
-      <c r="J57" s="16"/>
-      <c r="K57" s="16"/>
-      <c r="L57" s="16"/>
-      <c r="M57" s="16"/>
-      <c r="N57" s="16"/>
-      <c r="O57" s="19"/>
+      <c r="A57" s="14" t="s">
+        <v>271</v>
+      </c>
+      <c r="B57" s="14" t="s">
+        <v>270</v>
+      </c>
+      <c r="C57" s="14" t="s">
+        <v>272</v>
+      </c>
+      <c r="D57" s="15">
+        <v>0</v>
+      </c>
+      <c r="E57" s="15">
+        <v>0</v>
+      </c>
+      <c r="F57" s="15">
+        <v>0</v>
+      </c>
+      <c r="G57" s="15">
+        <v>1</v>
+      </c>
+      <c r="H57" s="15">
+        <v>1</v>
+      </c>
+      <c r="I57" s="15">
+        <v>0</v>
+      </c>
+      <c r="J57" s="16">
+        <v>1</v>
+      </c>
+      <c r="K57" s="16">
+        <v>1</v>
+      </c>
+      <c r="L57" s="16">
+        <v>0</v>
+      </c>
+      <c r="M57" s="16">
+        <v>0</v>
+      </c>
+      <c r="N57" s="16">
+        <v>0</v>
+      </c>
+      <c r="O57" s="19">
+        <v>0</v>
+      </c>
       <c r="P57" s="14"/>
       <c r="Q57" s="17" t="str">
         <f>IF(LEN(TRIM(B57))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B57),FIND(" ",TRIM(B57)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B57),FIND(" ",TRIM(B57)&amp;" ")-1)))</f>
-        <v/>
+        <v>서울</v>
       </c>
     </row>
     <row r="58" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A58" s="14"/>
-      <c r="B58" s="14"/>
-      <c r="C58" s="14"/>
-      <c r="D58" s="15"/>
-      <c r="E58" s="15"/>
-      <c r="F58" s="15"/>
-      <c r="G58" s="15"/>
-      <c r="H58" s="15"/>
-      <c r="I58" s="15"/>
-      <c r="J58" s="16"/>
-      <c r="K58" s="16"/>
-      <c r="L58" s="16"/>
-      <c r="M58" s="16"/>
-      <c r="N58" s="16"/>
-      <c r="O58" s="19"/>
-      <c r="P58" s="14"/>
+      <c r="A58" s="14" t="s">
+        <v>275</v>
+      </c>
+      <c r="B58" s="14" t="s">
+        <v>276</v>
+      </c>
+      <c r="C58" s="14" t="s">
+        <v>277</v>
+      </c>
+      <c r="D58" s="15">
+        <v>0</v>
+      </c>
+      <c r="E58" s="15">
+        <v>0</v>
+      </c>
+      <c r="F58" s="15">
+        <v>0</v>
+      </c>
+      <c r="G58" s="15">
+        <v>0</v>
+      </c>
+      <c r="H58" s="15">
+        <v>1</v>
+      </c>
+      <c r="I58" s="15">
+        <v>0</v>
+      </c>
+      <c r="J58" s="16">
+        <v>1</v>
+      </c>
+      <c r="K58" s="16">
+        <v>1</v>
+      </c>
+      <c r="L58" s="16">
+        <v>1</v>
+      </c>
+      <c r="M58" s="16">
+        <v>0</v>
+      </c>
+      <c r="N58" s="16">
+        <v>0</v>
+      </c>
+      <c r="O58" s="19">
+        <v>0</v>
+      </c>
+      <c r="P58" s="14" t="s">
+        <v>274</v>
+      </c>
       <c r="Q58" s="17" t="str">
         <f>IF(LEN(TRIM(B58))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B58),FIND(" ",TRIM(B58)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B58),FIND(" ",TRIM(B58)&amp;" ")-1)))</f>
-        <v/>
+        <v>서울</v>
       </c>
     </row>
     <row r="59" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A59" s="14"/>
-      <c r="B59" s="14"/>
-      <c r="C59" s="14"/>
-      <c r="D59" s="15"/>
-      <c r="E59" s="15"/>
-      <c r="F59" s="15"/>
-      <c r="G59" s="15"/>
-      <c r="H59" s="15"/>
-      <c r="I59" s="15"/>
-      <c r="J59" s="16"/>
-      <c r="K59" s="16"/>
-      <c r="L59" s="16"/>
-      <c r="M59" s="16"/>
-      <c r="N59" s="16"/>
-      <c r="O59" s="19"/>
-      <c r="P59" s="14"/>
+      <c r="A59" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="B59" s="14" t="s">
+        <v>279</v>
+      </c>
+      <c r="C59" s="14" t="s">
+        <v>281</v>
+      </c>
+      <c r="D59" s="15">
+        <v>0</v>
+      </c>
+      <c r="E59" s="15">
+        <v>0</v>
+      </c>
+      <c r="F59" s="15">
+        <v>0</v>
+      </c>
+      <c r="G59" s="15">
+        <v>0</v>
+      </c>
+      <c r="H59" s="15">
+        <v>1</v>
+      </c>
+      <c r="I59" s="15">
+        <v>0</v>
+      </c>
+      <c r="J59" s="16">
+        <v>1</v>
+      </c>
+      <c r="K59" s="16">
+        <v>0</v>
+      </c>
+      <c r="L59" s="16">
+        <v>1</v>
+      </c>
+      <c r="M59" s="16">
+        <v>0</v>
+      </c>
+      <c r="N59" s="16">
+        <v>0</v>
+      </c>
+      <c r="O59" s="19">
+        <v>0</v>
+      </c>
+      <c r="P59" s="14" t="s">
+        <v>278</v>
+      </c>
       <c r="Q59" s="17" t="str">
         <f>IF(LEN(TRIM(B59))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B59),FIND(" ",TRIM(B59)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B59),FIND(" ",TRIM(B59)&amp;" ")-1)))</f>
-        <v/>
+        <v>서울</v>
       </c>
     </row>
     <row r="60" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A60" s="14"/>
-      <c r="B60" s="14"/>
-      <c r="C60" s="14"/>
-      <c r="D60" s="15"/>
-      <c r="E60" s="15"/>
-      <c r="F60" s="15"/>
-      <c r="G60" s="15"/>
-      <c r="H60" s="15"/>
-      <c r="I60" s="15"/>
-      <c r="J60" s="16"/>
-      <c r="K60" s="16"/>
-      <c r="L60" s="16"/>
-      <c r="M60" s="16"/>
-      <c r="N60" s="16"/>
-      <c r="O60" s="19"/>
-      <c r="P60" s="14"/>
+      <c r="A60" s="14" t="s">
+        <v>284</v>
+      </c>
+      <c r="B60" s="14" t="s">
+        <v>283</v>
+      </c>
+      <c r="C60" s="14" t="s">
+        <v>285</v>
+      </c>
+      <c r="D60" s="15">
+        <v>0</v>
+      </c>
+      <c r="E60" s="15">
+        <v>0</v>
+      </c>
+      <c r="F60" s="15">
+        <v>0</v>
+      </c>
+      <c r="G60" s="15">
+        <v>0</v>
+      </c>
+      <c r="H60" s="15">
+        <v>1</v>
+      </c>
+      <c r="I60" s="15">
+        <v>0</v>
+      </c>
+      <c r="J60" s="16">
+        <v>1</v>
+      </c>
+      <c r="K60" s="16">
+        <v>1</v>
+      </c>
+      <c r="L60" s="16">
+        <v>0</v>
+      </c>
+      <c r="M60" s="16">
+        <v>0</v>
+      </c>
+      <c r="N60" s="16">
+        <v>0</v>
+      </c>
+      <c r="O60" s="19">
+        <v>0</v>
+      </c>
+      <c r="P60" s="14" t="s">
+        <v>282</v>
+      </c>
       <c r="Q60" s="17" t="str">
         <f>IF(LEN(TRIM(B60))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B60),FIND(" ",TRIM(B60)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B60),FIND(" ",TRIM(B60)&amp;" ")-1)))</f>
-        <v/>
+        <v>서울</v>
       </c>
     </row>
     <row r="61" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A61" s="14"/>
-      <c r="B61" s="14"/>
-      <c r="C61" s="14"/>
-      <c r="D61" s="15"/>
-      <c r="E61" s="15"/>
-      <c r="F61" s="15"/>
-      <c r="G61" s="15"/>
-      <c r="H61" s="15"/>
-      <c r="I61" s="15"/>
-      <c r="J61" s="16"/>
-      <c r="K61" s="16"/>
-      <c r="L61" s="16"/>
-      <c r="M61" s="16"/>
-      <c r="N61" s="16"/>
-      <c r="O61" s="19"/>
-      <c r="P61" s="14"/>
+      <c r="A61" s="14" t="s">
+        <v>288</v>
+      </c>
+      <c r="B61" s="14" t="s">
+        <v>287</v>
+      </c>
+      <c r="C61" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="D61" s="15">
+        <v>0</v>
+      </c>
+      <c r="E61" s="15">
+        <v>0</v>
+      </c>
+      <c r="F61" s="15">
+        <v>0</v>
+      </c>
+      <c r="G61" s="15">
+        <v>1</v>
+      </c>
+      <c r="H61" s="15">
+        <v>0</v>
+      </c>
+      <c r="I61" s="15">
+        <v>0</v>
+      </c>
+      <c r="J61" s="16">
+        <v>0</v>
+      </c>
+      <c r="K61" s="16">
+        <v>0</v>
+      </c>
+      <c r="L61" s="16">
+        <v>1</v>
+      </c>
+      <c r="M61" s="16">
+        <v>0</v>
+      </c>
+      <c r="N61" s="16">
+        <v>0</v>
+      </c>
+      <c r="O61" s="19">
+        <v>0</v>
+      </c>
+      <c r="P61" s="14" t="s">
+        <v>286</v>
+      </c>
       <c r="Q61" s="17" t="str">
         <f>IF(LEN(TRIM(B61))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B61),FIND(" ",TRIM(B61)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B61),FIND(" ",TRIM(B61)&amp;" ")-1)))</f>
-        <v/>
+        <v>서울</v>
       </c>
     </row>
     <row r="62" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A62" s="14"/>
-      <c r="B62" s="14"/>
-      <c r="C62" s="14"/>
-      <c r="D62" s="15"/>
-      <c r="E62" s="15"/>
-      <c r="F62" s="15"/>
-      <c r="G62" s="15"/>
-      <c r="H62" s="15"/>
-      <c r="I62" s="15"/>
-      <c r="J62" s="16"/>
-      <c r="K62" s="16"/>
-      <c r="L62" s="16"/>
-      <c r="M62" s="16"/>
-      <c r="N62" s="16"/>
-      <c r="O62" s="19"/>
-      <c r="P62" s="14"/>
+      <c r="A62" s="14" t="s">
+        <v>291</v>
+      </c>
+      <c r="B62" s="14" t="s">
+        <v>290</v>
+      </c>
+      <c r="C62" s="14" t="s">
+        <v>292</v>
+      </c>
+      <c r="D62" s="15">
+        <v>0</v>
+      </c>
+      <c r="E62" s="15">
+        <v>0</v>
+      </c>
+      <c r="F62" s="15">
+        <v>0</v>
+      </c>
+      <c r="G62" s="15">
+        <v>1</v>
+      </c>
+      <c r="H62" s="15">
+        <v>0</v>
+      </c>
+      <c r="I62" s="15">
+        <v>0</v>
+      </c>
+      <c r="J62" s="16">
+        <v>0</v>
+      </c>
+      <c r="K62" s="16">
+        <v>0</v>
+      </c>
+      <c r="L62" s="16">
+        <v>1</v>
+      </c>
+      <c r="M62" s="16">
+        <v>0</v>
+      </c>
+      <c r="N62" s="16">
+        <v>0</v>
+      </c>
+      <c r="O62" s="19">
+        <v>0</v>
+      </c>
+      <c r="P62" s="14" t="s">
+        <v>286</v>
+      </c>
       <c r="Q62" s="17" t="str">
         <f>IF(LEN(TRIM(B62))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B62),FIND(" ",TRIM(B62)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B62),FIND(" ",TRIM(B62)&amp;" ")-1)))</f>
-        <v/>
+        <v>서울</v>
       </c>
     </row>
     <row r="63" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A63" s="14"/>
-      <c r="B63" s="14"/>
-      <c r="C63" s="14"/>
-      <c r="D63" s="15"/>
-      <c r="E63" s="15"/>
-      <c r="F63" s="15"/>
-      <c r="G63" s="15"/>
-      <c r="H63" s="15"/>
-      <c r="I63" s="15"/>
-      <c r="J63" s="16"/>
-      <c r="K63" s="16"/>
-      <c r="L63" s="16"/>
-      <c r="M63" s="16"/>
-      <c r="N63" s="16"/>
-      <c r="O63" s="19"/>
+      <c r="A63" s="14" t="s">
+        <v>294</v>
+      </c>
+      <c r="B63" s="14" t="s">
+        <v>293</v>
+      </c>
+      <c r="C63" s="14" t="s">
+        <v>295</v>
+      </c>
+      <c r="D63" s="15">
+        <v>0</v>
+      </c>
+      <c r="E63" s="15">
+        <v>0</v>
+      </c>
+      <c r="F63" s="15">
+        <v>0</v>
+      </c>
+      <c r="G63" s="15">
+        <v>1</v>
+      </c>
+      <c r="H63" s="15">
+        <v>0</v>
+      </c>
+      <c r="I63" s="15">
+        <v>0</v>
+      </c>
+      <c r="J63" s="16">
+        <v>1</v>
+      </c>
+      <c r="K63" s="16">
+        <v>1</v>
+      </c>
+      <c r="L63" s="16">
+        <v>1</v>
+      </c>
+      <c r="M63" s="16">
+        <v>0</v>
+      </c>
+      <c r="N63" s="16">
+        <v>0</v>
+      </c>
+      <c r="O63" s="19">
+        <v>0</v>
+      </c>
       <c r="P63" s="14"/>
       <c r="Q63" s="17" t="str">
         <f>IF(LEN(TRIM(B63))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B63),FIND(" ",TRIM(B63)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B63),FIND(" ",TRIM(B63)&amp;" ")-1)))</f>
-        <v/>
+        <v>서울</v>
       </c>
     </row>
     <row r="64" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A64" s="14"/>
-      <c r="B64" s="14"/>
-      <c r="C64" s="14"/>
-      <c r="D64" s="15"/>
-      <c r="E64" s="15"/>
-      <c r="F64" s="15"/>
-      <c r="G64" s="15"/>
-      <c r="H64" s="15"/>
-      <c r="I64" s="15"/>
-      <c r="J64" s="16"/>
-      <c r="K64" s="16"/>
-      <c r="L64" s="16"/>
-      <c r="M64" s="16"/>
-      <c r="N64" s="16"/>
-      <c r="O64" s="19"/>
+      <c r="A64" s="14" t="s">
+        <v>297</v>
+      </c>
+      <c r="B64" s="14" t="s">
+        <v>296</v>
+      </c>
+      <c r="C64" s="14" t="s">
+        <v>298</v>
+      </c>
+      <c r="D64" s="15">
+        <v>0</v>
+      </c>
+      <c r="E64" s="15">
+        <v>0</v>
+      </c>
+      <c r="F64" s="15">
+        <v>0</v>
+      </c>
+      <c r="G64" s="15">
+        <v>0</v>
+      </c>
+      <c r="H64" s="15">
+        <v>1</v>
+      </c>
+      <c r="I64" s="15">
+        <v>0</v>
+      </c>
+      <c r="J64" s="16">
+        <v>0</v>
+      </c>
+      <c r="K64" s="16">
+        <v>1</v>
+      </c>
+      <c r="L64" s="16">
+        <v>0</v>
+      </c>
+      <c r="M64" s="16">
+        <v>0</v>
+      </c>
+      <c r="N64" s="16">
+        <v>0</v>
+      </c>
+      <c r="O64" s="19">
+        <v>0</v>
+      </c>
       <c r="P64" s="14"/>
       <c r="Q64" s="17" t="str">
         <f>IF(LEN(TRIM(B64))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B64),FIND(" ",TRIM(B64)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B64),FIND(" ",TRIM(B64)&amp;" ")-1)))</f>
-        <v/>
+        <v>서울</v>
       </c>
     </row>
     <row r="65" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A65" s="14"/>
-      <c r="B65" s="14"/>
-      <c r="C65" s="14"/>
-      <c r="D65" s="15"/>
-      <c r="E65" s="15"/>
-      <c r="F65" s="15"/>
-      <c r="G65" s="15"/>
-      <c r="H65" s="15"/>
-      <c r="I65" s="15"/>
-      <c r="J65" s="16"/>
-      <c r="K65" s="16"/>
-      <c r="L65" s="16"/>
-      <c r="M65" s="16"/>
-      <c r="N65" s="16"/>
-      <c r="O65" s="19"/>
-      <c r="P65" s="14"/>
+      <c r="A65" s="14" t="s">
+        <v>301</v>
+      </c>
+      <c r="B65" s="14" t="s">
+        <v>300</v>
+      </c>
+      <c r="C65" s="14" t="s">
+        <v>302</v>
+      </c>
+      <c r="D65" s="15">
+        <v>0</v>
+      </c>
+      <c r="E65" s="15">
+        <v>0</v>
+      </c>
+      <c r="F65" s="15">
+        <v>0</v>
+      </c>
+      <c r="G65" s="15">
+        <v>1</v>
+      </c>
+      <c r="H65" s="15">
+        <v>0</v>
+      </c>
+      <c r="I65" s="15">
+        <v>0</v>
+      </c>
+      <c r="J65" s="16">
+        <v>1</v>
+      </c>
+      <c r="K65" s="16">
+        <v>1</v>
+      </c>
+      <c r="L65" s="16">
+        <v>1</v>
+      </c>
+      <c r="M65" s="16">
+        <v>0</v>
+      </c>
+      <c r="N65" s="16">
+        <v>0</v>
+      </c>
+      <c r="O65" s="19">
+        <v>0</v>
+      </c>
+      <c r="P65" s="14" t="s">
+        <v>299</v>
+      </c>
       <c r="Q65" s="17" t="str">
         <f>IF(LEN(TRIM(B65))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B65),FIND(" ",TRIM(B65)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B65),FIND(" ",TRIM(B65)&amp;" ")-1)))</f>
-        <v/>
+        <v>서울</v>
       </c>
     </row>
     <row r="66" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A66" s="14"/>
-      <c r="B66" s="14"/>
-      <c r="C66" s="14"/>
-      <c r="D66" s="15"/>
-      <c r="E66" s="15"/>
-      <c r="F66" s="15"/>
-      <c r="G66" s="15"/>
-      <c r="H66" s="15"/>
-      <c r="I66" s="15"/>
-      <c r="J66" s="16"/>
-      <c r="K66" s="16"/>
-      <c r="L66" s="16"/>
-      <c r="M66" s="16"/>
-      <c r="N66" s="16"/>
-      <c r="O66" s="19"/>
+      <c r="A66" s="14" t="s">
+        <v>304</v>
+      </c>
+      <c r="B66" s="14" t="s">
+        <v>303</v>
+      </c>
+      <c r="C66" s="14" t="s">
+        <v>305</v>
+      </c>
+      <c r="D66" s="15">
+        <v>0</v>
+      </c>
+      <c r="E66" s="15">
+        <v>1</v>
+      </c>
+      <c r="F66" s="15">
+        <v>0</v>
+      </c>
+      <c r="G66" s="15">
+        <v>0</v>
+      </c>
+      <c r="H66" s="15">
+        <v>0</v>
+      </c>
+      <c r="I66" s="15">
+        <v>0</v>
+      </c>
+      <c r="J66" s="16">
+        <v>1</v>
+      </c>
+      <c r="K66" s="16">
+        <v>1</v>
+      </c>
+      <c r="L66" s="16">
+        <v>1</v>
+      </c>
+      <c r="M66" s="16">
+        <v>0</v>
+      </c>
+      <c r="N66" s="16">
+        <v>0</v>
+      </c>
+      <c r="O66" s="19">
+        <v>0</v>
+      </c>
       <c r="P66" s="14"/>
       <c r="Q66" s="17" t="str">
         <f>IF(LEN(TRIM(B66))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B66),FIND(" ",TRIM(B66)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B66),FIND(" ",TRIM(B66)&amp;" ")-1)))</f>
-        <v/>
+        <v>서울</v>
       </c>
     </row>
     <row r="67" spans="1:17" ht="25.5" customHeight="1">

--- a/업체정보/업체정보_간편입력.xlsx
+++ b/업체정보/업체정보_간편입력.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="434">
   <si>
     <t>상호명</t>
   </si>
@@ -1284,6 +1284,174 @@
   </si>
   <si>
     <t>카페마리</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>0507-1411-3461</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울 마포구 잔다리로 20-12 1층 신이도가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>신이도가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>QR코드 입장, 대형견 불가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울 마포구 와우산로 76 2층</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>만월다방 시네마</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>010-5086-3336</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울 서대문구 연희로27길 99</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>새라울</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>070-4001-0458</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울 마포구 동교로29길 42 2층</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>ddd 연남</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>리드줄 필수</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>0507-1374-5548</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울 마포구 광성로 41-3 C동 1층</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>포닐</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>0507-1494-1049</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울 마포구 잔다리로 73 1F</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>콤파일</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>070-7525-0955</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울 마포구 서강로9길 24 코이토</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>코이토</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>0507-1416-3070</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">서울 서대문구 연희맛로 17-14 2층 </t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>센티멘트</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>0507-1327-3659</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울 마포구 토정로 130 5층</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>만월다방 한강점</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>0507-1345-2712</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울 종로구 사직로9길 22 102호</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>스태픽스</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>유모차, 케이지 필수</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>0507-1409-0333</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울 마포구 동교로38길 33-6 1.5층</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>카페피엠무드</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>02-336-1256</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">서울 마포구 망원로3길 7 </t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Uig 우이그</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>0507-1325-8729</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울 마포구 성미산로 190-13 1층</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>무드여운</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>네이버예약</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -1295,7 +1463,7 @@
     <numFmt numFmtId="176" formatCode="[=1]&quot;예&quot;;[=0]&quot;아니오&quot;;General"/>
     <numFmt numFmtId="177" formatCode="[=1]&quot;가능&quot;;[=0]&quot;불가&quot;;General"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -1348,8 +1516,21 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF153047"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1381,6 +1562,12 @@
         <fgColor rgb="FFEFF6FA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="65"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1395,7 +1582,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1433,34 +1620,45 @@
     <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="177" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="10" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="18">
+  <dxfs count="19">
     <dxf>
       <font>
         <u val="none"/>
@@ -1468,6 +1666,7 @@
         <name val="맑은 고딕"/>
         <scheme val="none"/>
       </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1476,6 +1675,46 @@
         <name val="맑은 고딕"/>
         <scheme val="none"/>
       </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <name val="맑은 고딕"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <name val="맑은 고딕"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <name val="맑은 고딕"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <name val="맑은 고딕"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1491,6 +1730,7 @@
           <bgColor indexed="65"/>
         </patternFill>
       </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1506,6 +1746,7 @@
           <bgColor indexed="65"/>
         </patternFill>
       </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1521,6 +1762,7 @@
           <bgColor indexed="65"/>
         </patternFill>
       </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1529,6 +1771,7 @@
         <name val="맑은 고딕"/>
         <scheme val="none"/>
       </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1537,6 +1780,7 @@
         <name val="맑은 고딕"/>
         <scheme val="none"/>
       </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1545,6 +1789,7 @@
         <name val="맑은 고딕"/>
         <scheme val="none"/>
       </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1553,6 +1798,7 @@
         <name val="맑은 고딕"/>
         <scheme val="none"/>
       </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1561,6 +1807,7 @@
         <name val="맑은 고딕"/>
         <scheme val="none"/>
       </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1569,6 +1816,7 @@
         <name val="맑은 고딕"/>
         <scheme val="none"/>
       </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1577,6 +1825,7 @@
         <name val="맑은 고딕"/>
         <scheme val="none"/>
       </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1585,6 +1834,7 @@
         <name val="맑은 고딕"/>
         <scheme val="none"/>
       </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1593,38 +1843,7 @@
         <name val="맑은 고딕"/>
         <scheme val="none"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <name val="맑은 고딕"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <name val="맑은 고딕"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <name val="맑은 고딕"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <name val="맑은 고딕"/>
-        <scheme val="none"/>
-      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1640,28 +1859,28 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="VenueInput" displayName="VenueInput" ref="A1:Q101" totalsRowShown="0" dataDxfId="17">
-  <autoFilter ref="A1:Q101"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="VenueInput" displayName="VenueInput" ref="A1:Q225" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
+  <autoFilter ref="A1:Q225"/>
   <tableColumns count="17">
-    <tableColumn id="1" name="상호명" dataDxfId="16"/>
-    <tableColumn id="2" name="주소" dataDxfId="15"/>
-    <tableColumn id="3" name="업체연락처" dataDxfId="14"/>
-    <tableColumn id="4" name="운동장카페" dataDxfId="13"/>
-    <tableColumn id="5" name="동반 카페" dataDxfId="12"/>
-    <tableColumn id="6" name="대형견카페" dataDxfId="11"/>
-    <tableColumn id="7" name="동반 음식점" dataDxfId="10"/>
-    <tableColumn id="8" name="동반 술집" dataDxfId="9"/>
-    <tableColumn id="9" name="동반 펜션" dataDxfId="8"/>
-    <tableColumn id="10" name="주차가능" dataDxfId="7"/>
-    <tableColumn id="11" name="실내 동반" dataDxfId="6"/>
-    <tableColumn id="12" name="테라스 동반" dataDxfId="5"/>
-    <tableColumn id="15" name="호텔링" dataDxfId="4"/>
-    <tableColumn id="16" name="유치원" dataDxfId="3"/>
-    <tableColumn id="17" name="애견미용" dataDxfId="2"/>
-    <tableColumn id="13" name="동반 조건 및 메모" dataDxfId="1"/>
-    <tableColumn id="14" name="지역" dataDxfId="0"/>
+    <tableColumn id="1" name="상호명" dataDxfId="2"/>
+    <tableColumn id="2" name="주소" dataDxfId="0"/>
+    <tableColumn id="3" name="업체연락처" dataDxfId="1"/>
+    <tableColumn id="4" name="운동장카페" dataDxfId="18"/>
+    <tableColumn id="5" name="동반 카페" dataDxfId="17"/>
+    <tableColumn id="6" name="대형견카페" dataDxfId="16"/>
+    <tableColumn id="7" name="동반 음식점" dataDxfId="15"/>
+    <tableColumn id="8" name="동반 술집" dataDxfId="14"/>
+    <tableColumn id="9" name="동반 펜션" dataDxfId="13"/>
+    <tableColumn id="10" name="주차가능" dataDxfId="12"/>
+    <tableColumn id="11" name="실내 동반" dataDxfId="11"/>
+    <tableColumn id="12" name="테라스 동반" dataDxfId="10"/>
+    <tableColumn id="15" name="호텔링" dataDxfId="9"/>
+    <tableColumn id="16" name="유치원" dataDxfId="8"/>
+    <tableColumn id="17" name="애견미용" dataDxfId="7"/>
+    <tableColumn id="13" name="동반 조건 및 메모" dataDxfId="6"/>
+    <tableColumn id="14" name="지역" dataDxfId="5"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -1863,23 +2082,23 @@
   <sheetPr>
     <tabColor rgb="FF0F766E"/>
   </sheetPr>
-  <dimension ref="A1:Q101"/>
+  <dimension ref="A1:Q225"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="21.125" style="18" customWidth="1"/>
-    <col min="2" max="2" width="37.75" style="18" customWidth="1"/>
+    <col min="1" max="1" width="21.125" style="23" customWidth="1"/>
+    <col min="2" max="2" width="37.75" style="23" customWidth="1"/>
     <col min="3" max="3" width="16.625" style="18" customWidth="1"/>
-    <col min="4" max="11" width="12.5" style="18" customWidth="1"/>
+    <col min="4" max="4" width="10.625" style="18" customWidth="1"/>
+    <col min="5" max="11" width="12.5" style="18" customWidth="1"/>
     <col min="12" max="12" width="13.5" style="18" customWidth="1"/>
     <col min="13" max="13" width="9.5" style="18" customWidth="1"/>
-    <col min="14" max="14" width="9.75" style="18" customWidth="1"/>
-    <col min="15" max="15" width="9.75" style="13" customWidth="1"/>
+    <col min="14" max="15" width="9.75" style="18" customWidth="1"/>
     <col min="16" max="16" width="33.375" style="18" customWidth="1"/>
     <col min="17" max="17" width="12" style="18" customWidth="1"/>
     <col min="18" max="16384" width="9" style="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="13" customFormat="1" ht="34.5" customHeight="1">
+    <row r="1" spans="1:17" ht="34.5" customHeight="1">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -1933,13 +2152,13 @@
       </c>
     </row>
     <row r="2" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="16" t="s">
         <v>13</v>
       </c>
       <c r="D2" s="15">
@@ -1960,38 +2179,38 @@
       <c r="I2" s="15">
         <v>0</v>
       </c>
-      <c r="J2" s="16">
-        <v>1</v>
-      </c>
-      <c r="K2" s="16">
-        <v>1</v>
-      </c>
-      <c r="L2" s="16">
-        <v>1</v>
-      </c>
-      <c r="M2" s="16">
-        <v>0</v>
-      </c>
-      <c r="N2" s="16">
-        <v>0</v>
-      </c>
-      <c r="O2" s="19">
-        <v>0</v>
-      </c>
-      <c r="P2" s="14"/>
+      <c r="J2" s="13">
+        <v>1</v>
+      </c>
+      <c r="K2" s="13">
+        <v>1</v>
+      </c>
+      <c r="L2" s="13">
+        <v>1</v>
+      </c>
+      <c r="M2" s="13">
+        <v>0</v>
+      </c>
+      <c r="N2" s="13">
+        <v>0</v>
+      </c>
+      <c r="O2" s="13">
+        <v>0</v>
+      </c>
+      <c r="P2" s="16"/>
       <c r="Q2" s="17" t="str">
         <f>IF(LEN(TRIM(B2))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B2),FIND(" ",TRIM(B2)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B2),FIND(" ",TRIM(B2)&amp;" ")-1)))</f>
         <v>서울</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="16" t="s">
         <v>16</v>
       </c>
       <c r="D3" s="15">
@@ -2012,38 +2231,38 @@
       <c r="I3" s="15">
         <v>0</v>
       </c>
-      <c r="J3" s="16">
-        <v>1</v>
-      </c>
-      <c r="K3" s="16">
-        <v>1</v>
-      </c>
-      <c r="L3" s="16">
-        <v>1</v>
-      </c>
-      <c r="M3" s="16">
-        <v>0</v>
-      </c>
-      <c r="N3" s="16">
-        <v>0</v>
-      </c>
-      <c r="O3" s="19">
-        <v>0</v>
-      </c>
-      <c r="P3" s="14"/>
+      <c r="J3" s="13">
+        <v>1</v>
+      </c>
+      <c r="K3" s="13">
+        <v>1</v>
+      </c>
+      <c r="L3" s="13">
+        <v>1</v>
+      </c>
+      <c r="M3" s="13">
+        <v>0</v>
+      </c>
+      <c r="N3" s="13">
+        <v>0</v>
+      </c>
+      <c r="O3" s="13">
+        <v>0</v>
+      </c>
+      <c r="P3" s="16"/>
       <c r="Q3" s="17" t="str">
         <f>IF(LEN(TRIM(B3))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B3),FIND(" ",TRIM(B3)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B3),FIND(" ",TRIM(B3)&amp;" ")-1)))</f>
         <v>경기</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="16" t="s">
         <v>19</v>
       </c>
       <c r="D4" s="15">
@@ -2064,25 +2283,25 @@
       <c r="I4" s="15">
         <v>0</v>
       </c>
-      <c r="J4" s="16">
-        <v>1</v>
-      </c>
-      <c r="K4" s="16">
-        <v>1</v>
-      </c>
-      <c r="L4" s="16">
-        <v>1</v>
-      </c>
-      <c r="M4" s="16">
-        <v>0</v>
-      </c>
-      <c r="N4" s="16">
-        <v>0</v>
-      </c>
-      <c r="O4" s="19">
-        <v>0</v>
-      </c>
-      <c r="P4" s="14" t="s">
+      <c r="J4" s="13">
+        <v>1</v>
+      </c>
+      <c r="K4" s="13">
+        <v>1</v>
+      </c>
+      <c r="L4" s="13">
+        <v>1</v>
+      </c>
+      <c r="M4" s="13">
+        <v>0</v>
+      </c>
+      <c r="N4" s="13">
+        <v>0</v>
+      </c>
+      <c r="O4" s="13">
+        <v>0</v>
+      </c>
+      <c r="P4" s="16" t="s">
         <v>20</v>
       </c>
       <c r="Q4" s="17" t="str">
@@ -2091,13 +2310,13 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="16" t="s">
         <v>23</v>
       </c>
       <c r="D5" s="15">
@@ -2118,38 +2337,38 @@
       <c r="I5" s="15">
         <v>0</v>
       </c>
-      <c r="J5" s="16">
-        <v>1</v>
-      </c>
-      <c r="K5" s="16">
-        <v>1</v>
-      </c>
-      <c r="L5" s="16">
-        <v>1</v>
-      </c>
-      <c r="M5" s="16">
-        <v>0</v>
-      </c>
-      <c r="N5" s="16">
-        <v>0</v>
-      </c>
-      <c r="O5" s="19">
-        <v>0</v>
-      </c>
-      <c r="P5" s="14"/>
+      <c r="J5" s="13">
+        <v>1</v>
+      </c>
+      <c r="K5" s="13">
+        <v>1</v>
+      </c>
+      <c r="L5" s="13">
+        <v>1</v>
+      </c>
+      <c r="M5" s="13">
+        <v>0</v>
+      </c>
+      <c r="N5" s="13">
+        <v>0</v>
+      </c>
+      <c r="O5" s="13">
+        <v>0</v>
+      </c>
+      <c r="P5" s="16"/>
       <c r="Q5" s="17" t="str">
         <f>IF(LEN(TRIM(B5))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B5),FIND(" ",TRIM(B5)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B5),FIND(" ",TRIM(B5)&amp;" ")-1)))</f>
         <v>경기</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="16" t="s">
         <v>26</v>
       </c>
       <c r="D6" s="15">
@@ -2170,38 +2389,38 @@
       <c r="I6" s="15">
         <v>0</v>
       </c>
-      <c r="J6" s="16">
-        <v>1</v>
-      </c>
-      <c r="K6" s="16">
-        <v>1</v>
-      </c>
-      <c r="L6" s="16">
-        <v>1</v>
-      </c>
-      <c r="M6" s="16">
-        <v>0</v>
-      </c>
-      <c r="N6" s="16">
-        <v>0</v>
-      </c>
-      <c r="O6" s="19">
-        <v>0</v>
-      </c>
-      <c r="P6" s="14"/>
+      <c r="J6" s="13">
+        <v>1</v>
+      </c>
+      <c r="K6" s="13">
+        <v>1</v>
+      </c>
+      <c r="L6" s="13">
+        <v>1</v>
+      </c>
+      <c r="M6" s="13">
+        <v>0</v>
+      </c>
+      <c r="N6" s="13">
+        <v>0</v>
+      </c>
+      <c r="O6" s="13">
+        <v>0</v>
+      </c>
+      <c r="P6" s="16"/>
       <c r="Q6" s="17" t="str">
         <f>IF(LEN(TRIM(B6))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B6),FIND(" ",TRIM(B6)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B6),FIND(" ",TRIM(B6)&amp;" ")-1)))</f>
         <v>경기</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="16" t="s">
         <v>29</v>
       </c>
       <c r="D7" s="15">
@@ -2222,38 +2441,38 @@
       <c r="I7" s="15">
         <v>0</v>
       </c>
-      <c r="J7" s="16">
-        <v>1</v>
-      </c>
-      <c r="K7" s="16">
-        <v>1</v>
-      </c>
-      <c r="L7" s="16">
-        <v>1</v>
-      </c>
-      <c r="M7" s="16">
-        <v>0</v>
-      </c>
-      <c r="N7" s="16">
-        <v>0</v>
-      </c>
-      <c r="O7" s="19">
-        <v>0</v>
-      </c>
-      <c r="P7" s="14"/>
+      <c r="J7" s="13">
+        <v>1</v>
+      </c>
+      <c r="K7" s="13">
+        <v>1</v>
+      </c>
+      <c r="L7" s="13">
+        <v>1</v>
+      </c>
+      <c r="M7" s="13">
+        <v>0</v>
+      </c>
+      <c r="N7" s="13">
+        <v>0</v>
+      </c>
+      <c r="O7" s="13">
+        <v>0</v>
+      </c>
+      <c r="P7" s="16"/>
       <c r="Q7" s="17" t="str">
         <f>IF(LEN(TRIM(B7))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B7),FIND(" ",TRIM(B7)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B7),FIND(" ",TRIM(B7)&amp;" ")-1)))</f>
         <v>경기</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="14" t="s">
+      <c r="B8" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="C8" s="16" t="s">
         <v>32</v>
       </c>
       <c r="D8" s="15">
@@ -2274,38 +2493,38 @@
       <c r="I8" s="15">
         <v>0</v>
       </c>
-      <c r="J8" s="16">
-        <v>1</v>
-      </c>
-      <c r="K8" s="16">
-        <v>1</v>
-      </c>
-      <c r="L8" s="16">
-        <v>1</v>
-      </c>
-      <c r="M8" s="16">
-        <v>0</v>
-      </c>
-      <c r="N8" s="16">
-        <v>0</v>
-      </c>
-      <c r="O8" s="19">
-        <v>0</v>
-      </c>
-      <c r="P8" s="14"/>
+      <c r="J8" s="13">
+        <v>1</v>
+      </c>
+      <c r="K8" s="13">
+        <v>1</v>
+      </c>
+      <c r="L8" s="13">
+        <v>1</v>
+      </c>
+      <c r="M8" s="13">
+        <v>0</v>
+      </c>
+      <c r="N8" s="13">
+        <v>0</v>
+      </c>
+      <c r="O8" s="13">
+        <v>0</v>
+      </c>
+      <c r="P8" s="16"/>
       <c r="Q8" s="17" t="str">
         <f>IF(LEN(TRIM(B8))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B8),FIND(" ",TRIM(B8)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B8),FIND(" ",TRIM(B8)&amp;" ")-1)))</f>
         <v>경기</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A9" s="14" t="s">
+      <c r="A9" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C9" s="16" t="s">
         <v>35</v>
       </c>
       <c r="D9" s="15">
@@ -2326,38 +2545,38 @@
       <c r="I9" s="15">
         <v>0</v>
       </c>
-      <c r="J9" s="16">
-        <v>1</v>
-      </c>
-      <c r="K9" s="16">
-        <v>1</v>
-      </c>
-      <c r="L9" s="16">
-        <v>1</v>
-      </c>
-      <c r="M9" s="16">
-        <v>0</v>
-      </c>
-      <c r="N9" s="16">
-        <v>0</v>
-      </c>
-      <c r="O9" s="19">
-        <v>0</v>
-      </c>
-      <c r="P9" s="14"/>
+      <c r="J9" s="13">
+        <v>1</v>
+      </c>
+      <c r="K9" s="13">
+        <v>1</v>
+      </c>
+      <c r="L9" s="13">
+        <v>1</v>
+      </c>
+      <c r="M9" s="13">
+        <v>0</v>
+      </c>
+      <c r="N9" s="13">
+        <v>0</v>
+      </c>
+      <c r="O9" s="13">
+        <v>0</v>
+      </c>
+      <c r="P9" s="16"/>
       <c r="Q9" s="17" t="str">
         <f>IF(LEN(TRIM(B9))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B9),FIND(" ",TRIM(B9)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B9),FIND(" ",TRIM(B9)&amp;" ")-1)))</f>
         <v>경기</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A10" s="14" t="s">
+      <c r="A10" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="B10" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C10" s="16" t="s">
         <v>38</v>
       </c>
       <c r="D10" s="15">
@@ -2378,38 +2597,38 @@
       <c r="I10" s="15">
         <v>0</v>
       </c>
-      <c r="J10" s="16">
-        <v>1</v>
-      </c>
-      <c r="K10" s="16">
-        <v>1</v>
-      </c>
-      <c r="L10" s="16">
-        <v>1</v>
-      </c>
-      <c r="M10" s="16">
-        <v>0</v>
-      </c>
-      <c r="N10" s="16">
-        <v>0</v>
-      </c>
-      <c r="O10" s="19">
-        <v>0</v>
-      </c>
-      <c r="P10" s="14"/>
+      <c r="J10" s="13">
+        <v>1</v>
+      </c>
+      <c r="K10" s="13">
+        <v>1</v>
+      </c>
+      <c r="L10" s="13">
+        <v>1</v>
+      </c>
+      <c r="M10" s="13">
+        <v>0</v>
+      </c>
+      <c r="N10" s="13">
+        <v>0</v>
+      </c>
+      <c r="O10" s="13">
+        <v>0</v>
+      </c>
+      <c r="P10" s="16"/>
       <c r="Q10" s="17" t="str">
         <f>IF(LEN(TRIM(B10))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B10),FIND(" ",TRIM(B10)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B10),FIND(" ",TRIM(B10)&amp;" ")-1)))</f>
         <v>경기</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A11" s="14" t="s">
+      <c r="A11" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="B11" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="C11" s="16" t="s">
         <v>41</v>
       </c>
       <c r="D11" s="15">
@@ -2430,38 +2649,38 @@
       <c r="I11" s="15">
         <v>0</v>
       </c>
-      <c r="J11" s="16">
-        <v>1</v>
-      </c>
-      <c r="K11" s="16">
-        <v>1</v>
-      </c>
-      <c r="L11" s="16">
-        <v>1</v>
-      </c>
-      <c r="M11" s="16">
-        <v>0</v>
-      </c>
-      <c r="N11" s="16">
-        <v>0</v>
-      </c>
-      <c r="O11" s="19">
-        <v>0</v>
-      </c>
-      <c r="P11" s="14"/>
+      <c r="J11" s="13">
+        <v>1</v>
+      </c>
+      <c r="K11" s="13">
+        <v>1</v>
+      </c>
+      <c r="L11" s="13">
+        <v>1</v>
+      </c>
+      <c r="M11" s="13">
+        <v>0</v>
+      </c>
+      <c r="N11" s="13">
+        <v>0</v>
+      </c>
+      <c r="O11" s="13">
+        <v>0</v>
+      </c>
+      <c r="P11" s="16"/>
       <c r="Q11" s="17" t="str">
         <f>IF(LEN(TRIM(B11))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B11),FIND(" ",TRIM(B11)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B11),FIND(" ",TRIM(B11)&amp;" ")-1)))</f>
         <v>경기</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A12" s="14" t="s">
+      <c r="A12" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="B12" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="C12" s="16" t="s">
         <v>44</v>
       </c>
       <c r="D12" s="15">
@@ -2482,38 +2701,38 @@
       <c r="I12" s="15">
         <v>0</v>
       </c>
-      <c r="J12" s="16">
-        <v>1</v>
-      </c>
-      <c r="K12" s="16">
-        <v>1</v>
-      </c>
-      <c r="L12" s="16">
-        <v>1</v>
-      </c>
-      <c r="M12" s="16">
-        <v>0</v>
-      </c>
-      <c r="N12" s="16">
-        <v>0</v>
-      </c>
-      <c r="O12" s="19">
-        <v>0</v>
-      </c>
-      <c r="P12" s="14"/>
+      <c r="J12" s="13">
+        <v>1</v>
+      </c>
+      <c r="K12" s="13">
+        <v>1</v>
+      </c>
+      <c r="L12" s="13">
+        <v>1</v>
+      </c>
+      <c r="M12" s="13">
+        <v>0</v>
+      </c>
+      <c r="N12" s="13">
+        <v>0</v>
+      </c>
+      <c r="O12" s="13">
+        <v>0</v>
+      </c>
+      <c r="P12" s="16"/>
       <c r="Q12" s="17" t="str">
         <f>IF(LEN(TRIM(B12))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B12),FIND(" ",TRIM(B12)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B12),FIND(" ",TRIM(B12)&amp;" ")-1)))</f>
         <v>경기</v>
       </c>
     </row>
     <row r="13" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A13" s="14" t="s">
+      <c r="A13" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="B13" s="14" t="s">
+      <c r="B13" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="16" t="s">
         <v>47</v>
       </c>
       <c r="D13" s="15">
@@ -2534,38 +2753,38 @@
       <c r="I13" s="15">
         <v>0</v>
       </c>
-      <c r="J13" s="16">
-        <v>1</v>
-      </c>
-      <c r="K13" s="16">
-        <v>1</v>
-      </c>
-      <c r="L13" s="16">
-        <v>1</v>
-      </c>
-      <c r="M13" s="16">
-        <v>0</v>
-      </c>
-      <c r="N13" s="16">
-        <v>0</v>
-      </c>
-      <c r="O13" s="19">
-        <v>0</v>
-      </c>
-      <c r="P13" s="14"/>
+      <c r="J13" s="13">
+        <v>1</v>
+      </c>
+      <c r="K13" s="13">
+        <v>1</v>
+      </c>
+      <c r="L13" s="13">
+        <v>1</v>
+      </c>
+      <c r="M13" s="13">
+        <v>0</v>
+      </c>
+      <c r="N13" s="13">
+        <v>0</v>
+      </c>
+      <c r="O13" s="13">
+        <v>0</v>
+      </c>
+      <c r="P13" s="16"/>
       <c r="Q13" s="17" t="str">
         <f>IF(LEN(TRIM(B13))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B13),FIND(" ",TRIM(B13)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B13),FIND(" ",TRIM(B13)&amp;" ")-1)))</f>
         <v>경기</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A14" s="14" t="s">
+      <c r="A14" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="C14" s="16" t="s">
         <v>50</v>
       </c>
       <c r="D14" s="15">
@@ -2586,38 +2805,38 @@
       <c r="I14" s="15">
         <v>0</v>
       </c>
-      <c r="J14" s="16">
-        <v>1</v>
-      </c>
-      <c r="K14" s="16">
-        <v>1</v>
-      </c>
-      <c r="L14" s="16">
-        <v>1</v>
-      </c>
-      <c r="M14" s="16">
-        <v>0</v>
-      </c>
-      <c r="N14" s="16">
-        <v>0</v>
-      </c>
-      <c r="O14" s="19">
-        <v>0</v>
-      </c>
-      <c r="P14" s="14"/>
+      <c r="J14" s="13">
+        <v>1</v>
+      </c>
+      <c r="K14" s="13">
+        <v>1</v>
+      </c>
+      <c r="L14" s="13">
+        <v>1</v>
+      </c>
+      <c r="M14" s="13">
+        <v>0</v>
+      </c>
+      <c r="N14" s="13">
+        <v>0</v>
+      </c>
+      <c r="O14" s="13">
+        <v>0</v>
+      </c>
+      <c r="P14" s="16"/>
       <c r="Q14" s="17" t="str">
         <f>IF(LEN(TRIM(B14))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B14),FIND(" ",TRIM(B14)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B14),FIND(" ",TRIM(B14)&amp;" ")-1)))</f>
         <v>경기</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A15" s="14" t="s">
+      <c r="A15" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="B15" s="14" t="s">
+      <c r="B15" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="C15" s="14" t="s">
+      <c r="C15" s="16" t="s">
         <v>53</v>
       </c>
       <c r="D15" s="15">
@@ -2638,38 +2857,38 @@
       <c r="I15" s="15">
         <v>0</v>
       </c>
-      <c r="J15" s="16">
-        <v>1</v>
-      </c>
-      <c r="K15" s="16">
-        <v>1</v>
-      </c>
-      <c r="L15" s="16">
-        <v>0</v>
-      </c>
-      <c r="M15" s="16">
-        <v>0</v>
-      </c>
-      <c r="N15" s="16">
-        <v>1</v>
-      </c>
-      <c r="O15" s="19">
-        <v>0</v>
-      </c>
-      <c r="P15" s="14"/>
+      <c r="J15" s="13">
+        <v>1</v>
+      </c>
+      <c r="K15" s="13">
+        <v>1</v>
+      </c>
+      <c r="L15" s="13">
+        <v>0</v>
+      </c>
+      <c r="M15" s="13">
+        <v>0</v>
+      </c>
+      <c r="N15" s="13">
+        <v>1</v>
+      </c>
+      <c r="O15" s="13">
+        <v>0</v>
+      </c>
+      <c r="P15" s="16"/>
       <c r="Q15" s="17" t="str">
         <f>IF(LEN(TRIM(B15))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B15),FIND(" ",TRIM(B15)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B15),FIND(" ",TRIM(B15)&amp;" ")-1)))</f>
         <v>경기</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A16" s="14" t="s">
+      <c r="A16" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="B16" s="14" t="s">
+      <c r="B16" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="C16" s="14" t="s">
+      <c r="C16" s="16" t="s">
         <v>56</v>
       </c>
       <c r="D16" s="15">
@@ -2690,38 +2909,38 @@
       <c r="I16" s="15">
         <v>0</v>
       </c>
-      <c r="J16" s="16">
-        <v>1</v>
-      </c>
-      <c r="K16" s="16">
-        <v>1</v>
-      </c>
-      <c r="L16" s="16">
-        <v>1</v>
-      </c>
-      <c r="M16" s="16">
-        <v>0</v>
-      </c>
-      <c r="N16" s="16">
-        <v>0</v>
-      </c>
-      <c r="O16" s="19">
-        <v>0</v>
-      </c>
-      <c r="P16" s="14"/>
+      <c r="J16" s="13">
+        <v>1</v>
+      </c>
+      <c r="K16" s="13">
+        <v>1</v>
+      </c>
+      <c r="L16" s="13">
+        <v>1</v>
+      </c>
+      <c r="M16" s="13">
+        <v>0</v>
+      </c>
+      <c r="N16" s="13">
+        <v>0</v>
+      </c>
+      <c r="O16" s="13">
+        <v>0</v>
+      </c>
+      <c r="P16" s="16"/>
       <c r="Q16" s="17" t="str">
         <f>IF(LEN(TRIM(B16))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B16),FIND(" ",TRIM(B16)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B16),FIND(" ",TRIM(B16)&amp;" ")-1)))</f>
         <v>경기</v>
       </c>
     </row>
     <row r="17" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A17" s="14" t="s">
+      <c r="A17" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="B17" s="14" t="s">
+      <c r="B17" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="C17" s="14" t="s">
+      <c r="C17" s="16" t="s">
         <v>59</v>
       </c>
       <c r="D17" s="15">
@@ -2742,38 +2961,38 @@
       <c r="I17" s="15">
         <v>0</v>
       </c>
-      <c r="J17" s="16">
-        <v>1</v>
-      </c>
-      <c r="K17" s="16">
-        <v>1</v>
-      </c>
-      <c r="L17" s="16">
-        <v>0</v>
-      </c>
-      <c r="M17" s="16">
-        <v>0</v>
-      </c>
-      <c r="N17" s="16">
-        <v>0</v>
-      </c>
-      <c r="O17" s="19">
-        <v>0</v>
-      </c>
-      <c r="P17" s="14"/>
+      <c r="J17" s="13">
+        <v>1</v>
+      </c>
+      <c r="K17" s="13">
+        <v>1</v>
+      </c>
+      <c r="L17" s="13">
+        <v>0</v>
+      </c>
+      <c r="M17" s="13">
+        <v>0</v>
+      </c>
+      <c r="N17" s="13">
+        <v>0</v>
+      </c>
+      <c r="O17" s="13">
+        <v>0</v>
+      </c>
+      <c r="P17" s="16"/>
       <c r="Q17" s="17" t="str">
         <f>IF(LEN(TRIM(B17))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B17),FIND(" ",TRIM(B17)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B17),FIND(" ",TRIM(B17)&amp;" ")-1)))</f>
         <v>경기</v>
       </c>
     </row>
     <row r="18" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A18" s="14" t="s">
+      <c r="A18" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="B18" s="14" t="s">
+      <c r="B18" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="C18" s="14" t="s">
+      <c r="C18" s="16" t="s">
         <v>62</v>
       </c>
       <c r="D18" s="15">
@@ -2794,38 +3013,38 @@
       <c r="I18" s="15">
         <v>0</v>
       </c>
-      <c r="J18" s="16">
-        <v>1</v>
-      </c>
-      <c r="K18" s="16">
-        <v>1</v>
-      </c>
-      <c r="L18" s="16">
-        <v>1</v>
-      </c>
-      <c r="M18" s="16">
-        <v>1</v>
-      </c>
-      <c r="N18" s="16">
-        <v>1</v>
-      </c>
-      <c r="O18" s="19">
-        <v>0</v>
-      </c>
-      <c r="P18" s="14"/>
+      <c r="J18" s="13">
+        <v>1</v>
+      </c>
+      <c r="K18" s="13">
+        <v>1</v>
+      </c>
+      <c r="L18" s="13">
+        <v>1</v>
+      </c>
+      <c r="M18" s="13">
+        <v>1</v>
+      </c>
+      <c r="N18" s="13">
+        <v>1</v>
+      </c>
+      <c r="O18" s="13">
+        <v>0</v>
+      </c>
+      <c r="P18" s="16"/>
       <c r="Q18" s="17" t="str">
         <f>IF(LEN(TRIM(B18))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B18),FIND(" ",TRIM(B18)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B18),FIND(" ",TRIM(B18)&amp;" ")-1)))</f>
         <v>경기</v>
       </c>
     </row>
     <row r="19" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A19" s="14" t="s">
+      <c r="A19" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="B19" s="14" t="s">
+      <c r="B19" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="C19" s="14" t="s">
+      <c r="C19" s="16" t="s">
         <v>65</v>
       </c>
       <c r="D19" s="15">
@@ -2846,38 +3065,38 @@
       <c r="I19" s="15">
         <v>0</v>
       </c>
-      <c r="J19" s="16">
-        <v>1</v>
-      </c>
-      <c r="K19" s="16">
-        <v>1</v>
-      </c>
-      <c r="L19" s="16">
-        <v>1</v>
-      </c>
-      <c r="M19" s="16">
-        <v>0</v>
-      </c>
-      <c r="N19" s="16">
-        <v>0</v>
-      </c>
-      <c r="O19" s="19">
-        <v>0</v>
-      </c>
-      <c r="P19" s="14"/>
+      <c r="J19" s="13">
+        <v>1</v>
+      </c>
+      <c r="K19" s="13">
+        <v>1</v>
+      </c>
+      <c r="L19" s="13">
+        <v>1</v>
+      </c>
+      <c r="M19" s="13">
+        <v>0</v>
+      </c>
+      <c r="N19" s="13">
+        <v>0</v>
+      </c>
+      <c r="O19" s="13">
+        <v>0</v>
+      </c>
+      <c r="P19" s="16"/>
       <c r="Q19" s="17" t="str">
         <f>IF(LEN(TRIM(B19))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B19),FIND(" ",TRIM(B19)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B19),FIND(" ",TRIM(B19)&amp;" ")-1)))</f>
         <v>경기</v>
       </c>
     </row>
     <row r="20" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A20" s="14" t="s">
+      <c r="A20" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="B20" s="14" t="s">
+      <c r="B20" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="14" t="s">
+      <c r="C20" s="16" t="s">
         <v>68</v>
       </c>
       <c r="D20" s="15">
@@ -2898,38 +3117,38 @@
       <c r="I20" s="15">
         <v>0</v>
       </c>
-      <c r="J20" s="16">
-        <v>1</v>
-      </c>
-      <c r="K20" s="16">
-        <v>1</v>
-      </c>
-      <c r="L20" s="16">
-        <v>1</v>
-      </c>
-      <c r="M20" s="16">
-        <v>1</v>
-      </c>
-      <c r="N20" s="16">
-        <v>1</v>
-      </c>
-      <c r="O20" s="19">
-        <v>0</v>
-      </c>
-      <c r="P20" s="14"/>
+      <c r="J20" s="13">
+        <v>1</v>
+      </c>
+      <c r="K20" s="13">
+        <v>1</v>
+      </c>
+      <c r="L20" s="13">
+        <v>1</v>
+      </c>
+      <c r="M20" s="13">
+        <v>1</v>
+      </c>
+      <c r="N20" s="13">
+        <v>1</v>
+      </c>
+      <c r="O20" s="13">
+        <v>0</v>
+      </c>
+      <c r="P20" s="16"/>
       <c r="Q20" s="17" t="str">
         <f>IF(LEN(TRIM(B20))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B20),FIND(" ",TRIM(B20)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B20),FIND(" ",TRIM(B20)&amp;" ")-1)))</f>
         <v>경기</v>
       </c>
     </row>
     <row r="21" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A21" s="14" t="s">
+      <c r="A21" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="B21" s="14" t="s">
+      <c r="B21" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="C21" s="14" t="s">
+      <c r="C21" s="16" t="s">
         <v>71</v>
       </c>
       <c r="D21" s="15">
@@ -2950,38 +3169,38 @@
       <c r="I21" s="15">
         <v>0</v>
       </c>
-      <c r="J21" s="16">
-        <v>1</v>
-      </c>
-      <c r="K21" s="16">
-        <v>1</v>
-      </c>
-      <c r="L21" s="16">
-        <v>1</v>
-      </c>
-      <c r="M21" s="16">
-        <v>0</v>
-      </c>
-      <c r="N21" s="16">
-        <v>0</v>
-      </c>
-      <c r="O21" s="19">
-        <v>0</v>
-      </c>
-      <c r="P21" s="14"/>
+      <c r="J21" s="13">
+        <v>1</v>
+      </c>
+      <c r="K21" s="13">
+        <v>1</v>
+      </c>
+      <c r="L21" s="13">
+        <v>1</v>
+      </c>
+      <c r="M21" s="13">
+        <v>0</v>
+      </c>
+      <c r="N21" s="13">
+        <v>0</v>
+      </c>
+      <c r="O21" s="13">
+        <v>0</v>
+      </c>
+      <c r="P21" s="16"/>
       <c r="Q21" s="17" t="str">
         <f>IF(LEN(TRIM(B21))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B21),FIND(" ",TRIM(B21)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B21),FIND(" ",TRIM(B21)&amp;" ")-1)))</f>
         <v>경기</v>
       </c>
     </row>
     <row r="22" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A22" s="14" t="s">
+      <c r="A22" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="B22" s="14" t="s">
+      <c r="B22" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="C22" s="14" t="s">
+      <c r="C22" s="16" t="s">
         <v>74</v>
       </c>
       <c r="D22" s="15">
@@ -3002,38 +3221,38 @@
       <c r="I22" s="15">
         <v>0</v>
       </c>
-      <c r="J22" s="16">
-        <v>1</v>
-      </c>
-      <c r="K22" s="16">
-        <v>1</v>
-      </c>
-      <c r="L22" s="16">
-        <v>0</v>
-      </c>
-      <c r="M22" s="16">
-        <v>0</v>
-      </c>
-      <c r="N22" s="16">
-        <v>0</v>
-      </c>
-      <c r="O22" s="19">
-        <v>0</v>
-      </c>
-      <c r="P22" s="14"/>
+      <c r="J22" s="13">
+        <v>1</v>
+      </c>
+      <c r="K22" s="13">
+        <v>1</v>
+      </c>
+      <c r="L22" s="13">
+        <v>0</v>
+      </c>
+      <c r="M22" s="13">
+        <v>0</v>
+      </c>
+      <c r="N22" s="13">
+        <v>0</v>
+      </c>
+      <c r="O22" s="13">
+        <v>0</v>
+      </c>
+      <c r="P22" s="16"/>
       <c r="Q22" s="17" t="str">
         <f>IF(LEN(TRIM(B22))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B22),FIND(" ",TRIM(B22)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B22),FIND(" ",TRIM(B22)&amp;" ")-1)))</f>
         <v>서울</v>
       </c>
     </row>
     <row r="23" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A23" s="14" t="s">
+      <c r="A23" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="B23" s="14" t="s">
+      <c r="B23" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="C23" s="14" t="s">
+      <c r="C23" s="16" t="s">
         <v>77</v>
       </c>
       <c r="D23" s="15">
@@ -3054,38 +3273,38 @@
       <c r="I23" s="15">
         <v>0</v>
       </c>
-      <c r="J23" s="16">
-        <v>1</v>
-      </c>
-      <c r="K23" s="16">
-        <v>1</v>
-      </c>
-      <c r="L23" s="16">
-        <v>0</v>
-      </c>
-      <c r="M23" s="16">
-        <v>1</v>
-      </c>
-      <c r="N23" s="16">
-        <v>0</v>
-      </c>
-      <c r="O23" s="19">
-        <v>0</v>
-      </c>
-      <c r="P23" s="14"/>
+      <c r="J23" s="13">
+        <v>1</v>
+      </c>
+      <c r="K23" s="13">
+        <v>1</v>
+      </c>
+      <c r="L23" s="13">
+        <v>0</v>
+      </c>
+      <c r="M23" s="13">
+        <v>1</v>
+      </c>
+      <c r="N23" s="13">
+        <v>0</v>
+      </c>
+      <c r="O23" s="13">
+        <v>0</v>
+      </c>
+      <c r="P23" s="16"/>
       <c r="Q23" s="17" t="str">
         <f>IF(LEN(TRIM(B23))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B23),FIND(" ",TRIM(B23)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B23),FIND(" ",TRIM(B23)&amp;" ")-1)))</f>
         <v>서울</v>
       </c>
     </row>
     <row r="24" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A24" s="14" t="s">
+      <c r="A24" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="B24" s="14" t="s">
+      <c r="B24" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="C24" s="14" t="s">
+      <c r="C24" s="16" t="s">
         <v>80</v>
       </c>
       <c r="D24" s="15">
@@ -3106,38 +3325,38 @@
       <c r="I24" s="15">
         <v>0</v>
       </c>
-      <c r="J24" s="16">
-        <v>1</v>
-      </c>
-      <c r="K24" s="16">
-        <v>1</v>
-      </c>
-      <c r="L24" s="16">
-        <v>1</v>
-      </c>
-      <c r="M24" s="16">
-        <v>0</v>
-      </c>
-      <c r="N24" s="16">
-        <v>0</v>
-      </c>
-      <c r="O24" s="19">
-        <v>0</v>
-      </c>
-      <c r="P24" s="14"/>
+      <c r="J24" s="13">
+        <v>1</v>
+      </c>
+      <c r="K24" s="13">
+        <v>1</v>
+      </c>
+      <c r="L24" s="13">
+        <v>1</v>
+      </c>
+      <c r="M24" s="13">
+        <v>0</v>
+      </c>
+      <c r="N24" s="13">
+        <v>0</v>
+      </c>
+      <c r="O24" s="13">
+        <v>0</v>
+      </c>
+      <c r="P24" s="16"/>
       <c r="Q24" s="17" t="str">
         <f>IF(LEN(TRIM(B24))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B24),FIND(" ",TRIM(B24)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B24),FIND(" ",TRIM(B24)&amp;" ")-1)))</f>
         <v>서울</v>
       </c>
     </row>
     <row r="25" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A25" s="14" t="s">
+      <c r="A25" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="B25" s="14" t="s">
+      <c r="B25" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="C25" s="14" t="s">
+      <c r="C25" s="16" t="s">
         <v>83</v>
       </c>
       <c r="D25" s="15">
@@ -3158,38 +3377,38 @@
       <c r="I25" s="15">
         <v>0</v>
       </c>
-      <c r="J25" s="16">
-        <v>1</v>
-      </c>
-      <c r="K25" s="16">
-        <v>1</v>
-      </c>
-      <c r="L25" s="16">
-        <v>1</v>
-      </c>
-      <c r="M25" s="16">
-        <v>0</v>
-      </c>
-      <c r="N25" s="16">
-        <v>0</v>
-      </c>
-      <c r="O25" s="19">
-        <v>0</v>
-      </c>
-      <c r="P25" s="14"/>
+      <c r="J25" s="13">
+        <v>1</v>
+      </c>
+      <c r="K25" s="13">
+        <v>1</v>
+      </c>
+      <c r="L25" s="13">
+        <v>1</v>
+      </c>
+      <c r="M25" s="13">
+        <v>0</v>
+      </c>
+      <c r="N25" s="13">
+        <v>0</v>
+      </c>
+      <c r="O25" s="13">
+        <v>0</v>
+      </c>
+      <c r="P25" s="16"/>
       <c r="Q25" s="17" t="str">
         <f>IF(LEN(TRIM(B25))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B25),FIND(" ",TRIM(B25)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B25),FIND(" ",TRIM(B25)&amp;" ")-1)))</f>
         <v>경기</v>
       </c>
     </row>
     <row r="26" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A26" s="14" t="s">
+      <c r="A26" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="B26" s="14" t="s">
+      <c r="B26" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="C26" s="14" t="s">
+      <c r="C26" s="16" t="s">
         <v>86</v>
       </c>
       <c r="D26" s="15">
@@ -3210,38 +3429,38 @@
       <c r="I26" s="15">
         <v>0</v>
       </c>
-      <c r="J26" s="16">
-        <v>1</v>
-      </c>
-      <c r="K26" s="16">
-        <v>1</v>
-      </c>
-      <c r="L26" s="16">
-        <v>0</v>
-      </c>
-      <c r="M26" s="16">
-        <v>1</v>
-      </c>
-      <c r="N26" s="16">
-        <v>1</v>
-      </c>
-      <c r="O26" s="19">
-        <v>0</v>
-      </c>
-      <c r="P26" s="14"/>
+      <c r="J26" s="13">
+        <v>1</v>
+      </c>
+      <c r="K26" s="13">
+        <v>1</v>
+      </c>
+      <c r="L26" s="13">
+        <v>0</v>
+      </c>
+      <c r="M26" s="13">
+        <v>1</v>
+      </c>
+      <c r="N26" s="13">
+        <v>1</v>
+      </c>
+      <c r="O26" s="13">
+        <v>0</v>
+      </c>
+      <c r="P26" s="16"/>
       <c r="Q26" s="17" t="str">
         <f>IF(LEN(TRIM(B26))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B26),FIND(" ",TRIM(B26)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B26),FIND(" ",TRIM(B26)&amp;" ")-1)))</f>
         <v>경기</v>
       </c>
     </row>
     <row r="27" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A27" s="14" t="s">
+      <c r="A27" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="B27" s="14" t="s">
+      <c r="B27" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="C27" s="14" t="s">
+      <c r="C27" s="16" t="s">
         <v>89</v>
       </c>
       <c r="D27" s="15">
@@ -3262,38 +3481,38 @@
       <c r="I27" s="15">
         <v>0</v>
       </c>
-      <c r="J27" s="16">
-        <v>0</v>
-      </c>
-      <c r="K27" s="16">
-        <v>1</v>
-      </c>
-      <c r="L27" s="16">
-        <v>0</v>
-      </c>
-      <c r="M27" s="16">
-        <v>0</v>
-      </c>
-      <c r="N27" s="16">
-        <v>0</v>
-      </c>
-      <c r="O27" s="19">
-        <v>1</v>
-      </c>
-      <c r="P27" s="14"/>
+      <c r="J27" s="13">
+        <v>0</v>
+      </c>
+      <c r="K27" s="13">
+        <v>1</v>
+      </c>
+      <c r="L27" s="13">
+        <v>0</v>
+      </c>
+      <c r="M27" s="13">
+        <v>0</v>
+      </c>
+      <c r="N27" s="13">
+        <v>0</v>
+      </c>
+      <c r="O27" s="13">
+        <v>1</v>
+      </c>
+      <c r="P27" s="16"/>
       <c r="Q27" s="17" t="str">
         <f>IF(LEN(TRIM(B27))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B27),FIND(" ",TRIM(B27)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B27),FIND(" ",TRIM(B27)&amp;" ")-1)))</f>
         <v>서울</v>
       </c>
     </row>
     <row r="28" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A28" s="14" t="s">
+      <c r="A28" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="B28" s="14" t="s">
+      <c r="B28" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="C28" s="14" t="s">
+      <c r="C28" s="16" t="s">
         <v>92</v>
       </c>
       <c r="D28" s="15">
@@ -3314,38 +3533,38 @@
       <c r="I28" s="15">
         <v>0</v>
       </c>
-      <c r="J28" s="16">
-        <v>1</v>
-      </c>
-      <c r="K28" s="16">
-        <v>1</v>
-      </c>
-      <c r="L28" s="16">
-        <v>1</v>
-      </c>
-      <c r="M28" s="16">
-        <v>0</v>
-      </c>
-      <c r="N28" s="16">
-        <v>0</v>
-      </c>
-      <c r="O28" s="19">
-        <v>0</v>
-      </c>
-      <c r="P28" s="14"/>
+      <c r="J28" s="13">
+        <v>1</v>
+      </c>
+      <c r="K28" s="13">
+        <v>1</v>
+      </c>
+      <c r="L28" s="13">
+        <v>1</v>
+      </c>
+      <c r="M28" s="13">
+        <v>0</v>
+      </c>
+      <c r="N28" s="13">
+        <v>0</v>
+      </c>
+      <c r="O28" s="13">
+        <v>0</v>
+      </c>
+      <c r="P28" s="16"/>
       <c r="Q28" s="17" t="str">
         <f>IF(LEN(TRIM(B28))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B28),FIND(" ",TRIM(B28)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B28),FIND(" ",TRIM(B28)&amp;" ")-1)))</f>
         <v>경기</v>
       </c>
     </row>
     <row r="29" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A29" s="14" t="s">
+      <c r="A29" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="B29" s="14" t="s">
+      <c r="B29" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="C29" s="14" t="s">
+      <c r="C29" s="16" t="s">
         <v>95</v>
       </c>
       <c r="D29" s="15">
@@ -3366,38 +3585,38 @@
       <c r="I29" s="15">
         <v>0</v>
       </c>
-      <c r="J29" s="16">
-        <v>1</v>
-      </c>
-      <c r="K29" s="16">
-        <v>1</v>
-      </c>
-      <c r="L29" s="16">
-        <v>0</v>
-      </c>
-      <c r="M29" s="16">
-        <v>1</v>
-      </c>
-      <c r="N29" s="16">
-        <v>1</v>
-      </c>
-      <c r="O29" s="19">
-        <v>0</v>
-      </c>
-      <c r="P29" s="14"/>
+      <c r="J29" s="13">
+        <v>1</v>
+      </c>
+      <c r="K29" s="13">
+        <v>1</v>
+      </c>
+      <c r="L29" s="13">
+        <v>0</v>
+      </c>
+      <c r="M29" s="13">
+        <v>1</v>
+      </c>
+      <c r="N29" s="13">
+        <v>1</v>
+      </c>
+      <c r="O29" s="13">
+        <v>0</v>
+      </c>
+      <c r="P29" s="16"/>
       <c r="Q29" s="17" t="str">
         <f>IF(LEN(TRIM(B29))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B29),FIND(" ",TRIM(B29)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B29),FIND(" ",TRIM(B29)&amp;" ")-1)))</f>
         <v>경기</v>
       </c>
     </row>
     <row r="30" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A30" s="14" t="s">
+      <c r="A30" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="B30" s="14" t="s">
+      <c r="B30" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="C30" s="14" t="s">
+      <c r="C30" s="16" t="s">
         <v>98</v>
       </c>
       <c r="D30" s="15">
@@ -3418,38 +3637,38 @@
       <c r="I30" s="15">
         <v>0</v>
       </c>
-      <c r="J30" s="16">
-        <v>1</v>
-      </c>
-      <c r="K30" s="16">
-        <v>1</v>
-      </c>
-      <c r="L30" s="16">
-        <v>0</v>
-      </c>
-      <c r="M30" s="16">
-        <v>1</v>
-      </c>
-      <c r="N30" s="16">
-        <v>1</v>
-      </c>
-      <c r="O30" s="19">
-        <v>0</v>
-      </c>
-      <c r="P30" s="14"/>
+      <c r="J30" s="13">
+        <v>1</v>
+      </c>
+      <c r="K30" s="13">
+        <v>1</v>
+      </c>
+      <c r="L30" s="13">
+        <v>0</v>
+      </c>
+      <c r="M30" s="13">
+        <v>1</v>
+      </c>
+      <c r="N30" s="13">
+        <v>1</v>
+      </c>
+      <c r="O30" s="13">
+        <v>0</v>
+      </c>
+      <c r="P30" s="16"/>
       <c r="Q30" s="17" t="str">
         <f>IF(LEN(TRIM(B30))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B30),FIND(" ",TRIM(B30)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B30),FIND(" ",TRIM(B30)&amp;" ")-1)))</f>
         <v>경기</v>
       </c>
     </row>
     <row r="31" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A31" s="14" t="s">
+      <c r="A31" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="B31" s="14" t="s">
+      <c r="B31" s="21" t="s">
         <v>100</v>
       </c>
-      <c r="C31" s="14" t="s">
+      <c r="C31" s="16" t="s">
         <v>101</v>
       </c>
       <c r="D31" s="15">
@@ -3470,38 +3689,38 @@
       <c r="I31" s="15">
         <v>0</v>
       </c>
-      <c r="J31" s="16">
-        <v>0</v>
-      </c>
-      <c r="K31" s="16">
-        <v>1</v>
-      </c>
-      <c r="L31" s="16">
-        <v>0</v>
-      </c>
-      <c r="M31" s="16">
-        <v>1</v>
-      </c>
-      <c r="N31" s="16">
-        <v>1</v>
-      </c>
-      <c r="O31" s="19">
-        <v>0</v>
-      </c>
-      <c r="P31" s="14"/>
+      <c r="J31" s="13">
+        <v>0</v>
+      </c>
+      <c r="K31" s="13">
+        <v>1</v>
+      </c>
+      <c r="L31" s="13">
+        <v>0</v>
+      </c>
+      <c r="M31" s="13">
+        <v>1</v>
+      </c>
+      <c r="N31" s="13">
+        <v>1</v>
+      </c>
+      <c r="O31" s="13">
+        <v>0</v>
+      </c>
+      <c r="P31" s="16"/>
       <c r="Q31" s="17" t="str">
         <f>IF(LEN(TRIM(B31))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B31),FIND(" ",TRIM(B31)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B31),FIND(" ",TRIM(B31)&amp;" ")-1)))</f>
         <v>경기</v>
       </c>
     </row>
     <row r="32" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A32" s="14" t="s">
+      <c r="A32" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="B32" s="14" t="s">
+      <c r="B32" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="C32" s="14" t="s">
+      <c r="C32" s="16" t="s">
         <v>104</v>
       </c>
       <c r="D32" s="15">
@@ -3522,38 +3741,38 @@
       <c r="I32" s="15">
         <v>0</v>
       </c>
-      <c r="J32" s="16">
-        <v>1</v>
-      </c>
-      <c r="K32" s="16">
-        <v>1</v>
-      </c>
-      <c r="L32" s="16">
-        <v>0</v>
-      </c>
-      <c r="M32" s="16">
-        <v>0</v>
-      </c>
-      <c r="N32" s="16">
-        <v>0</v>
-      </c>
-      <c r="O32" s="19">
-        <v>0</v>
-      </c>
-      <c r="P32" s="14"/>
+      <c r="J32" s="13">
+        <v>1</v>
+      </c>
+      <c r="K32" s="13">
+        <v>1</v>
+      </c>
+      <c r="L32" s="13">
+        <v>0</v>
+      </c>
+      <c r="M32" s="13">
+        <v>0</v>
+      </c>
+      <c r="N32" s="13">
+        <v>0</v>
+      </c>
+      <c r="O32" s="13">
+        <v>0</v>
+      </c>
+      <c r="P32" s="16"/>
       <c r="Q32" s="17" t="str">
         <f>IF(LEN(TRIM(B32))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B32),FIND(" ",TRIM(B32)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B32),FIND(" ",TRIM(B32)&amp;" ")-1)))</f>
         <v>서울</v>
       </c>
     </row>
     <row r="33" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A33" s="14" t="s">
+      <c r="A33" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="B33" s="14" t="s">
+      <c r="B33" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="C33" s="14" t="s">
+      <c r="C33" s="16" t="s">
         <v>107</v>
       </c>
       <c r="D33" s="15">
@@ -3574,38 +3793,38 @@
       <c r="I33" s="15">
         <v>0</v>
       </c>
-      <c r="J33" s="16">
-        <v>1</v>
-      </c>
-      <c r="K33" s="16">
-        <v>1</v>
-      </c>
-      <c r="L33" s="16">
-        <v>1</v>
-      </c>
-      <c r="M33" s="16">
-        <v>1</v>
-      </c>
-      <c r="N33" s="16">
-        <v>1</v>
-      </c>
-      <c r="O33" s="19">
-        <v>1</v>
-      </c>
-      <c r="P33" s="14"/>
+      <c r="J33" s="13">
+        <v>1</v>
+      </c>
+      <c r="K33" s="13">
+        <v>1</v>
+      </c>
+      <c r="L33" s="13">
+        <v>1</v>
+      </c>
+      <c r="M33" s="13">
+        <v>1</v>
+      </c>
+      <c r="N33" s="13">
+        <v>1</v>
+      </c>
+      <c r="O33" s="13">
+        <v>1</v>
+      </c>
+      <c r="P33" s="16"/>
       <c r="Q33" s="17" t="str">
         <f>IF(LEN(TRIM(B33))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B33),FIND(" ",TRIM(B33)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B33),FIND(" ",TRIM(B33)&amp;" ")-1)))</f>
         <v>서울</v>
       </c>
     </row>
     <row r="34" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A34" s="14" t="s">
+      <c r="A34" s="21" t="s">
         <v>108</v>
       </c>
-      <c r="B34" s="14" t="s">
+      <c r="B34" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="C34" s="14" t="s">
+      <c r="C34" s="16" t="s">
         <v>110</v>
       </c>
       <c r="D34" s="15">
@@ -3626,38 +3845,38 @@
       <c r="I34" s="15">
         <v>0</v>
       </c>
-      <c r="J34" s="16">
-        <v>0</v>
-      </c>
-      <c r="K34" s="16">
-        <v>1</v>
-      </c>
-      <c r="L34" s="16">
-        <v>0</v>
-      </c>
-      <c r="M34" s="16">
-        <v>1</v>
-      </c>
-      <c r="N34" s="16">
-        <v>0</v>
-      </c>
-      <c r="O34" s="19">
-        <v>1</v>
-      </c>
-      <c r="P34" s="14"/>
+      <c r="J34" s="13">
+        <v>0</v>
+      </c>
+      <c r="K34" s="13">
+        <v>1</v>
+      </c>
+      <c r="L34" s="13">
+        <v>0</v>
+      </c>
+      <c r="M34" s="13">
+        <v>1</v>
+      </c>
+      <c r="N34" s="13">
+        <v>0</v>
+      </c>
+      <c r="O34" s="13">
+        <v>1</v>
+      </c>
+      <c r="P34" s="16"/>
       <c r="Q34" s="17" t="str">
         <f>IF(LEN(TRIM(B34))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B34),FIND(" ",TRIM(B34)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B34),FIND(" ",TRIM(B34)&amp;" ")-1)))</f>
         <v>서울</v>
       </c>
     </row>
     <row r="35" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A35" s="14" t="s">
+      <c r="A35" s="21" t="s">
         <v>111</v>
       </c>
-      <c r="B35" s="14" t="s">
+      <c r="B35" s="21" t="s">
         <v>112</v>
       </c>
-      <c r="C35" s="14" t="s">
+      <c r="C35" s="16" t="s">
         <v>113</v>
       </c>
       <c r="D35" s="15">
@@ -3678,38 +3897,38 @@
       <c r="I35" s="15">
         <v>0</v>
       </c>
-      <c r="J35" s="16">
-        <v>1</v>
-      </c>
-      <c r="K35" s="16">
-        <v>1</v>
-      </c>
-      <c r="L35" s="16">
-        <v>0</v>
-      </c>
-      <c r="M35" s="16">
-        <v>0</v>
-      </c>
-      <c r="N35" s="16">
-        <v>0</v>
-      </c>
-      <c r="O35" s="19">
-        <v>1</v>
-      </c>
-      <c r="P35" s="14"/>
+      <c r="J35" s="13">
+        <v>1</v>
+      </c>
+      <c r="K35" s="13">
+        <v>1</v>
+      </c>
+      <c r="L35" s="13">
+        <v>0</v>
+      </c>
+      <c r="M35" s="13">
+        <v>0</v>
+      </c>
+      <c r="N35" s="13">
+        <v>0</v>
+      </c>
+      <c r="O35" s="13">
+        <v>1</v>
+      </c>
+      <c r="P35" s="16"/>
       <c r="Q35" s="17" t="str">
         <f>IF(LEN(TRIM(B35))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B35),FIND(" ",TRIM(B35)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B35),FIND(" ",TRIM(B35)&amp;" ")-1)))</f>
         <v>서울</v>
       </c>
     </row>
     <row r="36" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A36" s="14" t="s">
+      <c r="A36" s="21" t="s">
         <v>114</v>
       </c>
-      <c r="B36" s="14" t="s">
+      <c r="B36" s="21" t="s">
         <v>115</v>
       </c>
-      <c r="C36" s="14" t="s">
+      <c r="C36" s="16" t="s">
         <v>116</v>
       </c>
       <c r="D36" s="15">
@@ -3730,38 +3949,38 @@
       <c r="I36" s="15">
         <v>0</v>
       </c>
-      <c r="J36" s="16">
-        <v>1</v>
-      </c>
-      <c r="K36" s="16">
-        <v>1</v>
-      </c>
-      <c r="L36" s="16">
-        <v>0</v>
-      </c>
-      <c r="M36" s="16">
-        <v>1</v>
-      </c>
-      <c r="N36" s="16">
-        <v>1</v>
-      </c>
-      <c r="O36" s="19">
-        <v>1</v>
-      </c>
-      <c r="P36" s="14"/>
+      <c r="J36" s="13">
+        <v>1</v>
+      </c>
+      <c r="K36" s="13">
+        <v>1</v>
+      </c>
+      <c r="L36" s="13">
+        <v>0</v>
+      </c>
+      <c r="M36" s="13">
+        <v>1</v>
+      </c>
+      <c r="N36" s="13">
+        <v>1</v>
+      </c>
+      <c r="O36" s="13">
+        <v>1</v>
+      </c>
+      <c r="P36" s="16"/>
       <c r="Q36" s="17" t="str">
         <f>IF(LEN(TRIM(B36))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B36),FIND(" ",TRIM(B36)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B36),FIND(" ",TRIM(B36)&amp;" ")-1)))</f>
         <v>서울</v>
       </c>
     </row>
     <row r="37" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A37" s="14" t="s">
+      <c r="A37" s="21" t="s">
         <v>117</v>
       </c>
-      <c r="B37" s="14" t="s">
+      <c r="B37" s="21" t="s">
         <v>118</v>
       </c>
-      <c r="C37" s="14" t="s">
+      <c r="C37" s="16" t="s">
         <v>119</v>
       </c>
       <c r="D37" s="15">
@@ -3782,38 +4001,38 @@
       <c r="I37" s="15">
         <v>0</v>
       </c>
-      <c r="J37" s="16">
-        <v>1</v>
-      </c>
-      <c r="K37" s="16">
-        <v>1</v>
-      </c>
-      <c r="L37" s="16">
-        <v>0</v>
-      </c>
-      <c r="M37" s="16">
-        <v>1</v>
-      </c>
-      <c r="N37" s="16">
-        <v>1</v>
-      </c>
-      <c r="O37" s="19">
-        <v>0</v>
-      </c>
-      <c r="P37" s="14"/>
+      <c r="J37" s="13">
+        <v>1</v>
+      </c>
+      <c r="K37" s="13">
+        <v>1</v>
+      </c>
+      <c r="L37" s="13">
+        <v>0</v>
+      </c>
+      <c r="M37" s="13">
+        <v>1</v>
+      </c>
+      <c r="N37" s="13">
+        <v>1</v>
+      </c>
+      <c r="O37" s="13">
+        <v>0</v>
+      </c>
+      <c r="P37" s="16"/>
       <c r="Q37" s="17" t="str">
         <f>IF(LEN(TRIM(B37))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B37),FIND(" ",TRIM(B37)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B37),FIND(" ",TRIM(B37)&amp;" ")-1)))</f>
         <v>서울</v>
       </c>
     </row>
     <row r="38" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A38" s="14" t="s">
+      <c r="A38" s="21" t="s">
         <v>120</v>
       </c>
-      <c r="B38" s="14" t="s">
+      <c r="B38" s="21" t="s">
         <v>121</v>
       </c>
-      <c r="C38" s="14" t="s">
+      <c r="C38" s="16" t="s">
         <v>122</v>
       </c>
       <c r="D38" s="15">
@@ -3834,38 +4053,38 @@
       <c r="I38" s="15">
         <v>0</v>
       </c>
-      <c r="J38" s="16">
-        <v>0</v>
-      </c>
-      <c r="K38" s="16">
-        <v>1</v>
-      </c>
-      <c r="L38" s="16">
-        <v>0</v>
-      </c>
-      <c r="M38" s="16">
-        <v>0</v>
-      </c>
-      <c r="N38" s="16">
-        <v>0</v>
-      </c>
-      <c r="O38" s="19">
-        <v>0</v>
-      </c>
-      <c r="P38" s="14"/>
+      <c r="J38" s="13">
+        <v>0</v>
+      </c>
+      <c r="K38" s="13">
+        <v>1</v>
+      </c>
+      <c r="L38" s="13">
+        <v>0</v>
+      </c>
+      <c r="M38" s="13">
+        <v>0</v>
+      </c>
+      <c r="N38" s="13">
+        <v>0</v>
+      </c>
+      <c r="O38" s="13">
+        <v>0</v>
+      </c>
+      <c r="P38" s="16"/>
       <c r="Q38" s="17" t="str">
         <f>IF(LEN(TRIM(B38))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B38),FIND(" ",TRIM(B38)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B38),FIND(" ",TRIM(B38)&amp;" ")-1)))</f>
         <v>서울</v>
       </c>
     </row>
     <row r="39" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A39" s="14" t="s">
+      <c r="A39" s="21" t="s">
         <v>123</v>
       </c>
-      <c r="B39" s="14" t="s">
+      <c r="B39" s="21" t="s">
         <v>124</v>
       </c>
-      <c r="C39" s="14" t="s">
+      <c r="C39" s="16" t="s">
         <v>125</v>
       </c>
       <c r="D39" s="15">
@@ -3886,38 +4105,38 @@
       <c r="I39" s="15">
         <v>0</v>
       </c>
-      <c r="J39" s="16">
-        <v>0</v>
-      </c>
-      <c r="K39" s="16">
-        <v>1</v>
-      </c>
-      <c r="L39" s="16">
-        <v>0</v>
-      </c>
-      <c r="M39" s="16">
-        <v>0</v>
-      </c>
-      <c r="N39" s="16">
-        <v>0</v>
-      </c>
-      <c r="O39" s="19">
-        <v>0</v>
-      </c>
-      <c r="P39" s="14"/>
+      <c r="J39" s="13">
+        <v>0</v>
+      </c>
+      <c r="K39" s="13">
+        <v>1</v>
+      </c>
+      <c r="L39" s="13">
+        <v>0</v>
+      </c>
+      <c r="M39" s="13">
+        <v>0</v>
+      </c>
+      <c r="N39" s="13">
+        <v>0</v>
+      </c>
+      <c r="O39" s="13">
+        <v>0</v>
+      </c>
+      <c r="P39" s="16"/>
       <c r="Q39" s="17" t="str">
         <f>IF(LEN(TRIM(B39))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B39),FIND(" ",TRIM(B39)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B39),FIND(" ",TRIM(B39)&amp;" ")-1)))</f>
         <v>서울</v>
       </c>
     </row>
     <row r="40" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A40" s="14" t="s">
+      <c r="A40" s="21" t="s">
         <v>126</v>
       </c>
-      <c r="B40" s="14" t="s">
+      <c r="B40" s="21" t="s">
         <v>127</v>
       </c>
-      <c r="C40" s="14" t="s">
+      <c r="C40" s="16" t="s">
         <v>128</v>
       </c>
       <c r="D40" s="15">
@@ -3938,38 +4157,38 @@
       <c r="I40" s="15">
         <v>0</v>
       </c>
-      <c r="J40" s="16">
-        <v>0</v>
-      </c>
-      <c r="K40" s="16">
-        <v>1</v>
-      </c>
-      <c r="L40" s="16">
-        <v>0</v>
-      </c>
-      <c r="M40" s="16">
-        <v>0</v>
-      </c>
-      <c r="N40" s="16">
-        <v>0</v>
-      </c>
-      <c r="O40" s="19">
-        <v>0</v>
-      </c>
-      <c r="P40" s="14"/>
+      <c r="J40" s="13">
+        <v>0</v>
+      </c>
+      <c r="K40" s="13">
+        <v>1</v>
+      </c>
+      <c r="L40" s="13">
+        <v>0</v>
+      </c>
+      <c r="M40" s="13">
+        <v>0</v>
+      </c>
+      <c r="N40" s="13">
+        <v>0</v>
+      </c>
+      <c r="O40" s="13">
+        <v>0</v>
+      </c>
+      <c r="P40" s="16"/>
       <c r="Q40" s="17" t="str">
         <f>IF(LEN(TRIM(B40))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B40),FIND(" ",TRIM(B40)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B40),FIND(" ",TRIM(B40)&amp;" ")-1)))</f>
         <v>서울</v>
       </c>
     </row>
     <row r="41" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A41" s="14" t="s">
+      <c r="A41" s="21" t="s">
         <v>129</v>
       </c>
-      <c r="B41" s="14" t="s">
+      <c r="B41" s="21" t="s">
         <v>130</v>
       </c>
-      <c r="C41" s="14" t="s">
+      <c r="C41" s="16" t="s">
         <v>131</v>
       </c>
       <c r="D41" s="15">
@@ -3990,38 +4209,38 @@
       <c r="I41" s="15">
         <v>0</v>
       </c>
-      <c r="J41" s="16">
-        <v>1</v>
-      </c>
-      <c r="K41" s="16">
-        <v>1</v>
-      </c>
-      <c r="L41" s="16">
-        <v>0</v>
-      </c>
-      <c r="M41" s="16">
-        <v>0</v>
-      </c>
-      <c r="N41" s="16">
-        <v>0</v>
-      </c>
-      <c r="O41" s="19">
-        <v>0</v>
-      </c>
-      <c r="P41" s="14"/>
+      <c r="J41" s="13">
+        <v>1</v>
+      </c>
+      <c r="K41" s="13">
+        <v>1</v>
+      </c>
+      <c r="L41" s="13">
+        <v>0</v>
+      </c>
+      <c r="M41" s="13">
+        <v>0</v>
+      </c>
+      <c r="N41" s="13">
+        <v>0</v>
+      </c>
+      <c r="O41" s="13">
+        <v>0</v>
+      </c>
+      <c r="P41" s="16"/>
       <c r="Q41" s="17" t="str">
         <f>IF(LEN(TRIM(B41))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B41),FIND(" ",TRIM(B41)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B41),FIND(" ",TRIM(B41)&amp;" ")-1)))</f>
         <v>서울</v>
       </c>
     </row>
     <row r="42" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A42" s="14" t="s">
+      <c r="A42" s="21" t="s">
         <v>132</v>
       </c>
-      <c r="B42" s="14" t="s">
+      <c r="B42" s="21" t="s">
         <v>133</v>
       </c>
-      <c r="C42" s="14" t="s">
+      <c r="C42" s="16" t="s">
         <v>134</v>
       </c>
       <c r="D42" s="15">
@@ -4042,38 +4261,38 @@
       <c r="I42" s="15">
         <v>0</v>
       </c>
-      <c r="J42" s="16">
-        <v>1</v>
-      </c>
-      <c r="K42" s="16">
-        <v>1</v>
-      </c>
-      <c r="L42" s="16">
-        <v>1</v>
-      </c>
-      <c r="M42" s="16">
-        <v>0</v>
-      </c>
-      <c r="N42" s="16">
-        <v>0</v>
-      </c>
-      <c r="O42" s="19">
-        <v>0</v>
-      </c>
-      <c r="P42" s="14"/>
+      <c r="J42" s="13">
+        <v>1</v>
+      </c>
+      <c r="K42" s="13">
+        <v>1</v>
+      </c>
+      <c r="L42" s="13">
+        <v>1</v>
+      </c>
+      <c r="M42" s="13">
+        <v>0</v>
+      </c>
+      <c r="N42" s="13">
+        <v>0</v>
+      </c>
+      <c r="O42" s="13">
+        <v>0</v>
+      </c>
+      <c r="P42" s="16"/>
       <c r="Q42" s="17" t="str">
         <f>IF(LEN(TRIM(B42))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B42),FIND(" ",TRIM(B42)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B42),FIND(" ",TRIM(B42)&amp;" ")-1)))</f>
         <v>경기</v>
       </c>
     </row>
     <row r="43" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A43" s="14" t="s">
+      <c r="A43" s="21" t="s">
         <v>135</v>
       </c>
-      <c r="B43" s="14" t="s">
+      <c r="B43" s="21" t="s">
         <v>136</v>
       </c>
-      <c r="C43" s="14" t="s">
+      <c r="C43" s="16" t="s">
         <v>137</v>
       </c>
       <c r="D43" s="15">
@@ -4094,38 +4313,38 @@
       <c r="I43" s="15">
         <v>0</v>
       </c>
-      <c r="J43" s="16">
-        <v>1</v>
-      </c>
-      <c r="K43" s="16">
-        <v>1</v>
-      </c>
-      <c r="L43" s="16">
-        <v>0</v>
-      </c>
-      <c r="M43" s="16">
-        <v>0</v>
-      </c>
-      <c r="N43" s="16">
-        <v>0</v>
-      </c>
-      <c r="O43" s="19">
-        <v>0</v>
-      </c>
-      <c r="P43" s="14"/>
+      <c r="J43" s="13">
+        <v>1</v>
+      </c>
+      <c r="K43" s="13">
+        <v>1</v>
+      </c>
+      <c r="L43" s="13">
+        <v>0</v>
+      </c>
+      <c r="M43" s="13">
+        <v>0</v>
+      </c>
+      <c r="N43" s="13">
+        <v>0</v>
+      </c>
+      <c r="O43" s="13">
+        <v>0</v>
+      </c>
+      <c r="P43" s="16"/>
       <c r="Q43" s="17" t="str">
         <f>IF(LEN(TRIM(B43))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B43),FIND(" ",TRIM(B43)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B43),FIND(" ",TRIM(B43)&amp;" ")-1)))</f>
         <v>서울</v>
       </c>
     </row>
     <row r="44" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A44" s="14" t="s">
+      <c r="A44" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="B44" s="14" t="s">
+      <c r="B44" s="21" t="s">
         <v>139</v>
       </c>
-      <c r="C44" s="14" t="s">
+      <c r="C44" s="16" t="s">
         <v>140</v>
       </c>
       <c r="D44" s="15">
@@ -4146,38 +4365,38 @@
       <c r="I44" s="15">
         <v>0</v>
       </c>
-      <c r="J44" s="16">
-        <v>0</v>
-      </c>
-      <c r="K44" s="16">
-        <v>1</v>
-      </c>
-      <c r="L44" s="16">
-        <v>0</v>
-      </c>
-      <c r="M44" s="16">
-        <v>0</v>
-      </c>
-      <c r="N44" s="16">
-        <v>0</v>
-      </c>
-      <c r="O44" s="19">
-        <v>0</v>
-      </c>
-      <c r="P44" s="14"/>
+      <c r="J44" s="13">
+        <v>0</v>
+      </c>
+      <c r="K44" s="13">
+        <v>1</v>
+      </c>
+      <c r="L44" s="13">
+        <v>0</v>
+      </c>
+      <c r="M44" s="13">
+        <v>0</v>
+      </c>
+      <c r="N44" s="13">
+        <v>0</v>
+      </c>
+      <c r="O44" s="13">
+        <v>0</v>
+      </c>
+      <c r="P44" s="16"/>
       <c r="Q44" s="17" t="str">
         <f>IF(LEN(TRIM(B44))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B44),FIND(" ",TRIM(B44)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B44),FIND(" ",TRIM(B44)&amp;" ")-1)))</f>
         <v>경기</v>
       </c>
     </row>
     <row r="45" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A45" s="14" t="s">
+      <c r="A45" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="B45" s="14" t="s">
+      <c r="B45" s="21" t="s">
         <v>142</v>
       </c>
-      <c r="C45" s="14" t="s">
+      <c r="C45" s="16" t="s">
         <v>143</v>
       </c>
       <c r="D45" s="15">
@@ -4198,38 +4417,38 @@
       <c r="I45" s="15">
         <v>0</v>
       </c>
-      <c r="J45" s="16">
-        <v>1</v>
-      </c>
-      <c r="K45" s="16">
-        <v>1</v>
-      </c>
-      <c r="L45" s="16">
-        <v>0</v>
-      </c>
-      <c r="M45" s="16">
-        <v>0</v>
-      </c>
-      <c r="N45" s="16">
-        <v>0</v>
-      </c>
-      <c r="O45" s="19">
-        <v>0</v>
-      </c>
-      <c r="P45" s="14"/>
+      <c r="J45" s="13">
+        <v>1</v>
+      </c>
+      <c r="K45" s="13">
+        <v>1</v>
+      </c>
+      <c r="L45" s="13">
+        <v>0</v>
+      </c>
+      <c r="M45" s="13">
+        <v>0</v>
+      </c>
+      <c r="N45" s="13">
+        <v>0</v>
+      </c>
+      <c r="O45" s="13">
+        <v>0</v>
+      </c>
+      <c r="P45" s="16"/>
       <c r="Q45" s="17" t="str">
         <f>IF(LEN(TRIM(B45))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B45),FIND(" ",TRIM(B45)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B45),FIND(" ",TRIM(B45)&amp;" ")-1)))</f>
         <v>서울</v>
       </c>
     </row>
     <row r="46" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A46" s="14" t="s">
+      <c r="A46" s="21" t="s">
         <v>144</v>
       </c>
-      <c r="B46" s="14" t="s">
+      <c r="B46" s="21" t="s">
         <v>145</v>
       </c>
-      <c r="C46" s="14" t="s">
+      <c r="C46" s="16" t="s">
         <v>146</v>
       </c>
       <c r="D46" s="15">
@@ -4250,38 +4469,38 @@
       <c r="I46" s="15">
         <v>0</v>
       </c>
-      <c r="J46" s="16">
-        <v>1</v>
-      </c>
-      <c r="K46" s="16">
-        <v>1</v>
-      </c>
-      <c r="L46" s="16">
-        <v>1</v>
-      </c>
-      <c r="M46" s="16">
-        <v>0</v>
-      </c>
-      <c r="N46" s="16">
-        <v>0</v>
-      </c>
-      <c r="O46" s="19">
-        <v>0</v>
-      </c>
-      <c r="P46" s="14"/>
+      <c r="J46" s="13">
+        <v>1</v>
+      </c>
+      <c r="K46" s="13">
+        <v>1</v>
+      </c>
+      <c r="L46" s="13">
+        <v>1</v>
+      </c>
+      <c r="M46" s="13">
+        <v>0</v>
+      </c>
+      <c r="N46" s="13">
+        <v>0</v>
+      </c>
+      <c r="O46" s="13">
+        <v>0</v>
+      </c>
+      <c r="P46" s="16"/>
       <c r="Q46" s="17" t="str">
         <f>IF(LEN(TRIM(B46))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B46),FIND(" ",TRIM(B46)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B46),FIND(" ",TRIM(B46)&amp;" ")-1)))</f>
         <v>서울</v>
       </c>
     </row>
     <row r="47" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A47" s="14" t="s">
+      <c r="A47" s="21" t="s">
         <v>147</v>
       </c>
-      <c r="B47" s="14" t="s">
+      <c r="B47" s="21" t="s">
         <v>148</v>
       </c>
-      <c r="C47" s="14" t="s">
+      <c r="C47" s="16" t="s">
         <v>149</v>
       </c>
       <c r="D47" s="15">
@@ -4302,38 +4521,38 @@
       <c r="I47" s="15">
         <v>0</v>
       </c>
-      <c r="J47" s="16">
-        <v>1</v>
-      </c>
-      <c r="K47" s="16">
-        <v>1</v>
-      </c>
-      <c r="L47" s="16">
-        <v>0</v>
-      </c>
-      <c r="M47" s="16">
-        <v>0</v>
-      </c>
-      <c r="N47" s="16">
-        <v>0</v>
-      </c>
-      <c r="O47" s="19">
-        <v>0</v>
-      </c>
-      <c r="P47" s="14"/>
+      <c r="J47" s="13">
+        <v>1</v>
+      </c>
+      <c r="K47" s="13">
+        <v>1</v>
+      </c>
+      <c r="L47" s="13">
+        <v>0</v>
+      </c>
+      <c r="M47" s="13">
+        <v>0</v>
+      </c>
+      <c r="N47" s="13">
+        <v>0</v>
+      </c>
+      <c r="O47" s="13">
+        <v>0</v>
+      </c>
+      <c r="P47" s="16"/>
       <c r="Q47" s="17" t="str">
         <f>IF(LEN(TRIM(B47))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B47),FIND(" ",TRIM(B47)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B47),FIND(" ",TRIM(B47)&amp;" ")-1)))</f>
         <v>서울</v>
       </c>
     </row>
     <row r="48" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A48" s="14" t="s">
+      <c r="A48" s="21" t="s">
         <v>150</v>
       </c>
-      <c r="B48" s="14" t="s">
+      <c r="B48" s="21" t="s">
         <v>151</v>
       </c>
-      <c r="C48" s="14" t="s">
+      <c r="C48" s="16" t="s">
         <v>152</v>
       </c>
       <c r="D48" s="15">
@@ -4354,25 +4573,25 @@
       <c r="I48" s="15">
         <v>0</v>
       </c>
-      <c r="J48" s="16">
-        <v>1</v>
-      </c>
-      <c r="K48" s="16">
-        <v>0</v>
-      </c>
-      <c r="L48" s="16">
-        <v>1</v>
-      </c>
-      <c r="M48" s="16">
-        <v>0</v>
-      </c>
-      <c r="N48" s="16">
-        <v>0</v>
-      </c>
-      <c r="O48" s="19">
-        <v>0</v>
-      </c>
-      <c r="P48" s="14" t="s">
+      <c r="J48" s="13">
+        <v>1</v>
+      </c>
+      <c r="K48" s="13">
+        <v>0</v>
+      </c>
+      <c r="L48" s="13">
+        <v>1</v>
+      </c>
+      <c r="M48" s="13">
+        <v>0</v>
+      </c>
+      <c r="N48" s="13">
+        <v>0</v>
+      </c>
+      <c r="O48" s="13">
+        <v>0</v>
+      </c>
+      <c r="P48" s="16" t="s">
         <v>153</v>
       </c>
       <c r="Q48" s="17" t="str">
@@ -4381,13 +4600,13 @@
       </c>
     </row>
     <row r="49" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A49" s="14" t="s">
+      <c r="A49" s="21" t="s">
         <v>154</v>
       </c>
-      <c r="B49" s="14" t="s">
+      <c r="B49" s="21" t="s">
         <v>155</v>
       </c>
-      <c r="C49" s="14" t="s">
+      <c r="C49" s="16" t="s">
         <v>156</v>
       </c>
       <c r="D49" s="15">
@@ -4408,38 +4627,38 @@
       <c r="I49" s="15">
         <v>0</v>
       </c>
-      <c r="J49" s="16">
-        <v>0</v>
-      </c>
-      <c r="K49" s="16">
-        <v>1</v>
-      </c>
-      <c r="L49" s="16">
-        <v>0</v>
-      </c>
-      <c r="M49" s="16">
-        <v>0</v>
-      </c>
-      <c r="N49" s="16">
-        <v>0</v>
-      </c>
-      <c r="O49" s="19">
-        <v>0</v>
-      </c>
-      <c r="P49" s="14"/>
+      <c r="J49" s="13">
+        <v>0</v>
+      </c>
+      <c r="K49" s="13">
+        <v>1</v>
+      </c>
+      <c r="L49" s="13">
+        <v>0</v>
+      </c>
+      <c r="M49" s="13">
+        <v>0</v>
+      </c>
+      <c r="N49" s="13">
+        <v>0</v>
+      </c>
+      <c r="O49" s="13">
+        <v>0</v>
+      </c>
+      <c r="P49" s="16"/>
       <c r="Q49" s="17" t="str">
         <f>IF(LEN(TRIM(B49))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B49),FIND(" ",TRIM(B49)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B49),FIND(" ",TRIM(B49)&amp;" ")-1)))</f>
         <v>서울</v>
       </c>
     </row>
     <row r="50" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A50" s="14" t="s">
+      <c r="A50" s="21" t="s">
         <v>157</v>
       </c>
-      <c r="B50" s="14" t="s">
+      <c r="B50" s="21" t="s">
         <v>158</v>
       </c>
-      <c r="C50" s="14" t="s">
+      <c r="C50" s="16" t="s">
         <v>159</v>
       </c>
       <c r="D50" s="15">
@@ -4460,38 +4679,38 @@
       <c r="I50" s="15">
         <v>0</v>
       </c>
-      <c r="J50" s="16">
-        <v>1</v>
-      </c>
-      <c r="K50" s="16">
-        <v>1</v>
-      </c>
-      <c r="L50" s="16">
-        <v>0</v>
-      </c>
-      <c r="M50" s="16">
-        <v>0</v>
-      </c>
-      <c r="N50" s="16">
-        <v>0</v>
-      </c>
-      <c r="O50" s="19">
-        <v>0</v>
-      </c>
-      <c r="P50" s="14"/>
+      <c r="J50" s="13">
+        <v>1</v>
+      </c>
+      <c r="K50" s="13">
+        <v>1</v>
+      </c>
+      <c r="L50" s="13">
+        <v>0</v>
+      </c>
+      <c r="M50" s="13">
+        <v>0</v>
+      </c>
+      <c r="N50" s="13">
+        <v>0</v>
+      </c>
+      <c r="O50" s="13">
+        <v>0</v>
+      </c>
+      <c r="P50" s="16"/>
       <c r="Q50" s="17" t="str">
         <f>IF(LEN(TRIM(B50))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B50),FIND(" ",TRIM(B50)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B50),FIND(" ",TRIM(B50)&amp;" ")-1)))</f>
         <v>서울</v>
       </c>
     </row>
     <row r="51" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A51" s="14" t="s">
+      <c r="A51" s="21" t="s">
         <v>160</v>
       </c>
-      <c r="B51" s="14" t="s">
+      <c r="B51" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="C51" s="14" t="s">
+      <c r="C51" s="16" t="s">
         <v>162</v>
       </c>
       <c r="D51" s="15">
@@ -4512,25 +4731,25 @@
       <c r="I51" s="15">
         <v>0</v>
       </c>
-      <c r="J51" s="16">
-        <v>1</v>
-      </c>
-      <c r="K51" s="16">
-        <v>1</v>
-      </c>
-      <c r="L51" s="16">
-        <v>0</v>
-      </c>
-      <c r="M51" s="16">
-        <v>0</v>
-      </c>
-      <c r="N51" s="16">
-        <v>0</v>
-      </c>
-      <c r="O51" s="19">
-        <v>0</v>
-      </c>
-      <c r="P51" s="14" t="s">
+      <c r="J51" s="13">
+        <v>1</v>
+      </c>
+      <c r="K51" s="13">
+        <v>1</v>
+      </c>
+      <c r="L51" s="13">
+        <v>0</v>
+      </c>
+      <c r="M51" s="13">
+        <v>0</v>
+      </c>
+      <c r="N51" s="13">
+        <v>0</v>
+      </c>
+      <c r="O51" s="13">
+        <v>0</v>
+      </c>
+      <c r="P51" s="16" t="s">
         <v>163</v>
       </c>
       <c r="Q51" s="17" t="str">
@@ -4539,13 +4758,13 @@
       </c>
     </row>
     <row r="52" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A52" s="14" t="s">
+      <c r="A52" s="21" t="s">
         <v>164</v>
       </c>
-      <c r="B52" s="14" t="s">
+      <c r="B52" s="21" t="s">
         <v>165</v>
       </c>
-      <c r="C52" s="14" t="s">
+      <c r="C52" s="16" t="s">
         <v>166</v>
       </c>
       <c r="D52" s="15">
@@ -4566,38 +4785,38 @@
       <c r="I52" s="15">
         <v>0</v>
       </c>
-      <c r="J52" s="16">
-        <v>0</v>
-      </c>
-      <c r="K52" s="16">
-        <v>1</v>
-      </c>
-      <c r="L52" s="16">
-        <v>1</v>
-      </c>
-      <c r="M52" s="16">
-        <v>0</v>
-      </c>
-      <c r="N52" s="16">
-        <v>0</v>
-      </c>
-      <c r="O52" s="19">
-        <v>0</v>
-      </c>
-      <c r="P52" s="14"/>
+      <c r="J52" s="13">
+        <v>0</v>
+      </c>
+      <c r="K52" s="13">
+        <v>1</v>
+      </c>
+      <c r="L52" s="13">
+        <v>1</v>
+      </c>
+      <c r="M52" s="13">
+        <v>0</v>
+      </c>
+      <c r="N52" s="13">
+        <v>0</v>
+      </c>
+      <c r="O52" s="13">
+        <v>0</v>
+      </c>
+      <c r="P52" s="16"/>
       <c r="Q52" s="17" t="str">
         <f>IF(LEN(TRIM(B52))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B52),FIND(" ",TRIM(B52)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B52),FIND(" ",TRIM(B52)&amp;" ")-1)))</f>
         <v>서울</v>
       </c>
     </row>
     <row r="53" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A53" s="14" t="s">
+      <c r="A53" s="21" t="s">
         <v>167</v>
       </c>
-      <c r="B53" s="14" t="s">
+      <c r="B53" s="21" t="s">
         <v>168</v>
       </c>
-      <c r="C53" s="14" t="s">
+      <c r="C53" s="16" t="s">
         <v>169</v>
       </c>
       <c r="D53" s="15">
@@ -4618,25 +4837,25 @@
       <c r="I53" s="15">
         <v>0</v>
       </c>
-      <c r="J53" s="16">
-        <v>1</v>
-      </c>
-      <c r="K53" s="16">
-        <v>1</v>
-      </c>
-      <c r="L53" s="16">
-        <v>0</v>
-      </c>
-      <c r="M53" s="16">
-        <v>0</v>
-      </c>
-      <c r="N53" s="16">
-        <v>0</v>
-      </c>
-      <c r="O53" s="19">
-        <v>0</v>
-      </c>
-      <c r="P53" s="14" t="s">
+      <c r="J53" s="13">
+        <v>1</v>
+      </c>
+      <c r="K53" s="13">
+        <v>1</v>
+      </c>
+      <c r="L53" s="13">
+        <v>0</v>
+      </c>
+      <c r="M53" s="13">
+        <v>0</v>
+      </c>
+      <c r="N53" s="13">
+        <v>0</v>
+      </c>
+      <c r="O53" s="13">
+        <v>0</v>
+      </c>
+      <c r="P53" s="16" t="s">
         <v>170</v>
       </c>
       <c r="Q53" s="17" t="str">
@@ -4645,13 +4864,13 @@
       </c>
     </row>
     <row r="54" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A54" s="14" t="s">
+      <c r="A54" s="21" t="s">
         <v>171</v>
       </c>
-      <c r="B54" s="14" t="s">
+      <c r="B54" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="C54" s="14" t="s">
+      <c r="C54" s="16" t="s">
         <v>173</v>
       </c>
       <c r="D54" s="15">
@@ -4672,25 +4891,25 @@
       <c r="I54" s="15">
         <v>0</v>
       </c>
-      <c r="J54" s="16">
-        <v>1</v>
-      </c>
-      <c r="K54" s="16">
-        <v>1</v>
-      </c>
-      <c r="L54" s="16">
-        <v>1</v>
-      </c>
-      <c r="M54" s="16">
-        <v>0</v>
-      </c>
-      <c r="N54" s="16">
-        <v>0</v>
-      </c>
-      <c r="O54" s="19">
-        <v>0</v>
-      </c>
-      <c r="P54" s="14" t="s">
+      <c r="J54" s="13">
+        <v>1</v>
+      </c>
+      <c r="K54" s="13">
+        <v>1</v>
+      </c>
+      <c r="L54" s="13">
+        <v>1</v>
+      </c>
+      <c r="M54" s="13">
+        <v>0</v>
+      </c>
+      <c r="N54" s="13">
+        <v>0</v>
+      </c>
+      <c r="O54" s="13">
+        <v>0</v>
+      </c>
+      <c r="P54" s="16" t="s">
         <v>174</v>
       </c>
       <c r="Q54" s="17" t="str">
@@ -4699,13 +4918,13 @@
       </c>
     </row>
     <row r="55" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A55" s="14" t="s">
+      <c r="A55" s="21" t="s">
         <v>175</v>
       </c>
-      <c r="B55" s="14" t="s">
+      <c r="B55" s="21" t="s">
         <v>176</v>
       </c>
-      <c r="C55" s="14" t="s">
+      <c r="C55" s="16" t="s">
         <v>177</v>
       </c>
       <c r="D55" s="15">
@@ -4726,25 +4945,25 @@
       <c r="I55" s="15">
         <v>0</v>
       </c>
-      <c r="J55" s="16">
-        <v>0</v>
-      </c>
-      <c r="K55" s="16">
-        <v>0</v>
-      </c>
-      <c r="L55" s="16">
-        <v>1</v>
-      </c>
-      <c r="M55" s="16">
-        <v>0</v>
-      </c>
-      <c r="N55" s="16">
-        <v>0</v>
-      </c>
-      <c r="O55" s="19">
-        <v>0</v>
-      </c>
-      <c r="P55" s="14" t="s">
+      <c r="J55" s="13">
+        <v>0</v>
+      </c>
+      <c r="K55" s="13">
+        <v>0</v>
+      </c>
+      <c r="L55" s="13">
+        <v>1</v>
+      </c>
+      <c r="M55" s="13">
+        <v>0</v>
+      </c>
+      <c r="N55" s="13">
+        <v>0</v>
+      </c>
+      <c r="O55" s="13">
+        <v>0</v>
+      </c>
+      <c r="P55" s="16" t="s">
         <v>178</v>
       </c>
       <c r="Q55" s="17" t="str">
@@ -4753,13 +4972,13 @@
       </c>
     </row>
     <row r="56" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A56" s="14" t="s">
+      <c r="A56" s="21" t="s">
         <v>179</v>
       </c>
-      <c r="B56" s="14" t="s">
+      <c r="B56" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="C56" s="14" t="s">
+      <c r="C56" s="16" t="s">
         <v>181</v>
       </c>
       <c r="D56" s="15">
@@ -4780,25 +4999,25 @@
       <c r="I56" s="15">
         <v>0</v>
       </c>
-      <c r="J56" s="16">
-        <v>1</v>
-      </c>
-      <c r="K56" s="16">
-        <v>1</v>
-      </c>
-      <c r="L56" s="16">
-        <v>0</v>
-      </c>
-      <c r="M56" s="16">
-        <v>0</v>
-      </c>
-      <c r="N56" s="16">
-        <v>0</v>
-      </c>
-      <c r="O56" s="19">
-        <v>0</v>
-      </c>
-      <c r="P56" s="14" t="s">
+      <c r="J56" s="13">
+        <v>1</v>
+      </c>
+      <c r="K56" s="13">
+        <v>1</v>
+      </c>
+      <c r="L56" s="13">
+        <v>0</v>
+      </c>
+      <c r="M56" s="13">
+        <v>0</v>
+      </c>
+      <c r="N56" s="13">
+        <v>0</v>
+      </c>
+      <c r="O56" s="13">
+        <v>0</v>
+      </c>
+      <c r="P56" s="16" t="s">
         <v>182</v>
       </c>
       <c r="Q56" s="17" t="str">
@@ -4807,13 +5026,13 @@
       </c>
     </row>
     <row r="57" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A57" s="14" t="s">
+      <c r="A57" s="21" t="s">
         <v>183</v>
       </c>
-      <c r="B57" s="14" t="s">
+      <c r="B57" s="21" t="s">
         <v>184</v>
       </c>
-      <c r="C57" s="14" t="s">
+      <c r="C57" s="16" t="s">
         <v>185</v>
       </c>
       <c r="D57" s="15">
@@ -4834,38 +5053,38 @@
       <c r="I57" s="15">
         <v>0</v>
       </c>
-      <c r="J57" s="16">
-        <v>1</v>
-      </c>
-      <c r="K57" s="16">
-        <v>1</v>
-      </c>
-      <c r="L57" s="16">
-        <v>0</v>
-      </c>
-      <c r="M57" s="16">
-        <v>0</v>
-      </c>
-      <c r="N57" s="16">
-        <v>0</v>
-      </c>
-      <c r="O57" s="19">
-        <v>0</v>
-      </c>
-      <c r="P57" s="14"/>
+      <c r="J57" s="13">
+        <v>1</v>
+      </c>
+      <c r="K57" s="13">
+        <v>1</v>
+      </c>
+      <c r="L57" s="13">
+        <v>0</v>
+      </c>
+      <c r="M57" s="13">
+        <v>0</v>
+      </c>
+      <c r="N57" s="13">
+        <v>0</v>
+      </c>
+      <c r="O57" s="13">
+        <v>0</v>
+      </c>
+      <c r="P57" s="16"/>
       <c r="Q57" s="17" t="str">
         <f>IF(LEN(TRIM(B57))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B57),FIND(" ",TRIM(B57)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B57),FIND(" ",TRIM(B57)&amp;" ")-1)))</f>
         <v>서울</v>
       </c>
     </row>
     <row r="58" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A58" s="14" t="s">
+      <c r="A58" s="21" t="s">
         <v>186</v>
       </c>
-      <c r="B58" s="14" t="s">
+      <c r="B58" s="21" t="s">
         <v>187</v>
       </c>
-      <c r="C58" s="14" t="s">
+      <c r="C58" s="16" t="s">
         <v>188</v>
       </c>
       <c r="D58" s="15">
@@ -4886,25 +5105,25 @@
       <c r="I58" s="15">
         <v>0</v>
       </c>
-      <c r="J58" s="16">
-        <v>1</v>
-      </c>
-      <c r="K58" s="16">
-        <v>1</v>
-      </c>
-      <c r="L58" s="16">
-        <v>1</v>
-      </c>
-      <c r="M58" s="16">
-        <v>0</v>
-      </c>
-      <c r="N58" s="16">
-        <v>0</v>
-      </c>
-      <c r="O58" s="19">
-        <v>0</v>
-      </c>
-      <c r="P58" s="14" t="s">
+      <c r="J58" s="13">
+        <v>1</v>
+      </c>
+      <c r="K58" s="13">
+        <v>1</v>
+      </c>
+      <c r="L58" s="13">
+        <v>1</v>
+      </c>
+      <c r="M58" s="13">
+        <v>0</v>
+      </c>
+      <c r="N58" s="13">
+        <v>0</v>
+      </c>
+      <c r="O58" s="13">
+        <v>0</v>
+      </c>
+      <c r="P58" s="16" t="s">
         <v>189</v>
       </c>
       <c r="Q58" s="17" t="str">
@@ -4913,13 +5132,13 @@
       </c>
     </row>
     <row r="59" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A59" s="14" t="s">
+      <c r="A59" s="21" t="s">
         <v>190</v>
       </c>
-      <c r="B59" s="14" t="s">
+      <c r="B59" s="21" t="s">
         <v>191</v>
       </c>
-      <c r="C59" s="14" t="s">
+      <c r="C59" s="16" t="s">
         <v>192</v>
       </c>
       <c r="D59" s="15">
@@ -4940,25 +5159,25 @@
       <c r="I59" s="15">
         <v>0</v>
       </c>
-      <c r="J59" s="16">
-        <v>1</v>
-      </c>
-      <c r="K59" s="16">
-        <v>0</v>
-      </c>
-      <c r="L59" s="16">
-        <v>1</v>
-      </c>
-      <c r="M59" s="16">
-        <v>0</v>
-      </c>
-      <c r="N59" s="16">
-        <v>0</v>
-      </c>
-      <c r="O59" s="19">
-        <v>0</v>
-      </c>
-      <c r="P59" s="14" t="s">
+      <c r="J59" s="13">
+        <v>1</v>
+      </c>
+      <c r="K59" s="13">
+        <v>0</v>
+      </c>
+      <c r="L59" s="13">
+        <v>1</v>
+      </c>
+      <c r="M59" s="13">
+        <v>0</v>
+      </c>
+      <c r="N59" s="13">
+        <v>0</v>
+      </c>
+      <c r="O59" s="13">
+        <v>0</v>
+      </c>
+      <c r="P59" s="16" t="s">
         <v>193</v>
       </c>
       <c r="Q59" s="17" t="str">
@@ -4967,13 +5186,13 @@
       </c>
     </row>
     <row r="60" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A60" s="14" t="s">
+      <c r="A60" s="21" t="s">
         <v>194</v>
       </c>
-      <c r="B60" s="14" t="s">
+      <c r="B60" s="21" t="s">
         <v>195</v>
       </c>
-      <c r="C60" s="14" t="s">
+      <c r="C60" s="16" t="s">
         <v>196</v>
       </c>
       <c r="D60" s="15">
@@ -4994,25 +5213,25 @@
       <c r="I60" s="15">
         <v>0</v>
       </c>
-      <c r="J60" s="16">
-        <v>1</v>
-      </c>
-      <c r="K60" s="16">
-        <v>1</v>
-      </c>
-      <c r="L60" s="16">
-        <v>0</v>
-      </c>
-      <c r="M60" s="16">
-        <v>0</v>
-      </c>
-      <c r="N60" s="16">
-        <v>0</v>
-      </c>
-      <c r="O60" s="19">
-        <v>0</v>
-      </c>
-      <c r="P60" s="14" t="s">
+      <c r="J60" s="13">
+        <v>1</v>
+      </c>
+      <c r="K60" s="13">
+        <v>1</v>
+      </c>
+      <c r="L60" s="13">
+        <v>0</v>
+      </c>
+      <c r="M60" s="13">
+        <v>0</v>
+      </c>
+      <c r="N60" s="13">
+        <v>0</v>
+      </c>
+      <c r="O60" s="13">
+        <v>0</v>
+      </c>
+      <c r="P60" s="16" t="s">
         <v>182</v>
       </c>
       <c r="Q60" s="17" t="str">
@@ -5021,13 +5240,13 @@
       </c>
     </row>
     <row r="61" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A61" s="14" t="s">
+      <c r="A61" s="21" t="s">
         <v>197</v>
       </c>
-      <c r="B61" s="14" t="s">
+      <c r="B61" s="21" t="s">
         <v>198</v>
       </c>
-      <c r="C61" s="14" t="s">
+      <c r="C61" s="16" t="s">
         <v>199</v>
       </c>
       <c r="D61" s="15">
@@ -5048,25 +5267,25 @@
       <c r="I61" s="15">
         <v>0</v>
       </c>
-      <c r="J61" s="16">
-        <v>0</v>
-      </c>
-      <c r="K61" s="16">
-        <v>0</v>
-      </c>
-      <c r="L61" s="16">
-        <v>1</v>
-      </c>
-      <c r="M61" s="16">
-        <v>0</v>
-      </c>
-      <c r="N61" s="16">
-        <v>0</v>
-      </c>
-      <c r="O61" s="19">
-        <v>0</v>
-      </c>
-      <c r="P61" s="14" t="s">
+      <c r="J61" s="13">
+        <v>0</v>
+      </c>
+      <c r="K61" s="13">
+        <v>0</v>
+      </c>
+      <c r="L61" s="13">
+        <v>1</v>
+      </c>
+      <c r="M61" s="13">
+        <v>0</v>
+      </c>
+      <c r="N61" s="13">
+        <v>0</v>
+      </c>
+      <c r="O61" s="13">
+        <v>0</v>
+      </c>
+      <c r="P61" s="16" t="s">
         <v>200</v>
       </c>
       <c r="Q61" s="17" t="str">
@@ -5075,13 +5294,13 @@
       </c>
     </row>
     <row r="62" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A62" s="14" t="s">
+      <c r="A62" s="21" t="s">
         <v>201</v>
       </c>
-      <c r="B62" s="14" t="s">
+      <c r="B62" s="21" t="s">
         <v>202</v>
       </c>
-      <c r="C62" s="14" t="s">
+      <c r="C62" s="16" t="s">
         <v>203</v>
       </c>
       <c r="D62" s="15">
@@ -5102,25 +5321,25 @@
       <c r="I62" s="15">
         <v>0</v>
       </c>
-      <c r="J62" s="16">
-        <v>0</v>
-      </c>
-      <c r="K62" s="16">
-        <v>0</v>
-      </c>
-      <c r="L62" s="16">
-        <v>1</v>
-      </c>
-      <c r="M62" s="16">
-        <v>0</v>
-      </c>
-      <c r="N62" s="16">
-        <v>0</v>
-      </c>
-      <c r="O62" s="19">
-        <v>0</v>
-      </c>
-      <c r="P62" s="14" t="s">
+      <c r="J62" s="13">
+        <v>0</v>
+      </c>
+      <c r="K62" s="13">
+        <v>0</v>
+      </c>
+      <c r="L62" s="13">
+        <v>1</v>
+      </c>
+      <c r="M62" s="13">
+        <v>0</v>
+      </c>
+      <c r="N62" s="13">
+        <v>0</v>
+      </c>
+      <c r="O62" s="13">
+        <v>0</v>
+      </c>
+      <c r="P62" s="16" t="s">
         <v>200</v>
       </c>
       <c r="Q62" s="17" t="str">
@@ -5129,13 +5348,13 @@
       </c>
     </row>
     <row r="63" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A63" s="14" t="s">
+      <c r="A63" s="21" t="s">
         <v>204</v>
       </c>
-      <c r="B63" s="14" t="s">
+      <c r="B63" s="21" t="s">
         <v>205</v>
       </c>
-      <c r="C63" s="14" t="s">
+      <c r="C63" s="16" t="s">
         <v>206</v>
       </c>
       <c r="D63" s="15">
@@ -5156,38 +5375,38 @@
       <c r="I63" s="15">
         <v>0</v>
       </c>
-      <c r="J63" s="16">
-        <v>1</v>
-      </c>
-      <c r="K63" s="16">
-        <v>1</v>
-      </c>
-      <c r="L63" s="16">
-        <v>1</v>
-      </c>
-      <c r="M63" s="16">
-        <v>0</v>
-      </c>
-      <c r="N63" s="16">
-        <v>0</v>
-      </c>
-      <c r="O63" s="19">
-        <v>0</v>
-      </c>
-      <c r="P63" s="14"/>
+      <c r="J63" s="13">
+        <v>1</v>
+      </c>
+      <c r="K63" s="13">
+        <v>1</v>
+      </c>
+      <c r="L63" s="13">
+        <v>1</v>
+      </c>
+      <c r="M63" s="13">
+        <v>0</v>
+      </c>
+      <c r="N63" s="13">
+        <v>0</v>
+      </c>
+      <c r="O63" s="13">
+        <v>0</v>
+      </c>
+      <c r="P63" s="16"/>
       <c r="Q63" s="17" t="str">
         <f>IF(LEN(TRIM(B63))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B63),FIND(" ",TRIM(B63)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B63),FIND(" ",TRIM(B63)&amp;" ")-1)))</f>
         <v>서울</v>
       </c>
     </row>
     <row r="64" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A64" s="14" t="s">
+      <c r="A64" s="21" t="s">
         <v>207</v>
       </c>
-      <c r="B64" s="14" t="s">
+      <c r="B64" s="21" t="s">
         <v>208</v>
       </c>
-      <c r="C64" s="14" t="s">
+      <c r="C64" s="16" t="s">
         <v>209</v>
       </c>
       <c r="D64" s="15">
@@ -5208,38 +5427,38 @@
       <c r="I64" s="15">
         <v>0</v>
       </c>
-      <c r="J64" s="16">
-        <v>0</v>
-      </c>
-      <c r="K64" s="16">
-        <v>1</v>
-      </c>
-      <c r="L64" s="16">
-        <v>0</v>
-      </c>
-      <c r="M64" s="16">
-        <v>0</v>
-      </c>
-      <c r="N64" s="16">
-        <v>0</v>
-      </c>
-      <c r="O64" s="19">
-        <v>0</v>
-      </c>
-      <c r="P64" s="14"/>
+      <c r="J64" s="13">
+        <v>0</v>
+      </c>
+      <c r="K64" s="13">
+        <v>1</v>
+      </c>
+      <c r="L64" s="13">
+        <v>0</v>
+      </c>
+      <c r="M64" s="13">
+        <v>0</v>
+      </c>
+      <c r="N64" s="13">
+        <v>0</v>
+      </c>
+      <c r="O64" s="13">
+        <v>0</v>
+      </c>
+      <c r="P64" s="16"/>
       <c r="Q64" s="17" t="str">
         <f>IF(LEN(TRIM(B64))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B64),FIND(" ",TRIM(B64)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B64),FIND(" ",TRIM(B64)&amp;" ")-1)))</f>
         <v>서울</v>
       </c>
     </row>
     <row r="65" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A65" s="14" t="s">
+      <c r="A65" s="21" t="s">
         <v>210</v>
       </c>
-      <c r="B65" s="14" t="s">
+      <c r="B65" s="21" t="s">
         <v>211</v>
       </c>
-      <c r="C65" s="14" t="s">
+      <c r="C65" s="16" t="s">
         <v>212</v>
       </c>
       <c r="D65" s="15">
@@ -5260,25 +5479,25 @@
       <c r="I65" s="15">
         <v>0</v>
       </c>
-      <c r="J65" s="16">
-        <v>1</v>
-      </c>
-      <c r="K65" s="16">
-        <v>1</v>
-      </c>
-      <c r="L65" s="16">
-        <v>1</v>
-      </c>
-      <c r="M65" s="16">
-        <v>0</v>
-      </c>
-      <c r="N65" s="16">
-        <v>0</v>
-      </c>
-      <c r="O65" s="19">
-        <v>0</v>
-      </c>
-      <c r="P65" s="14" t="s">
+      <c r="J65" s="13">
+        <v>1</v>
+      </c>
+      <c r="K65" s="13">
+        <v>1</v>
+      </c>
+      <c r="L65" s="13">
+        <v>1</v>
+      </c>
+      <c r="M65" s="13">
+        <v>0</v>
+      </c>
+      <c r="N65" s="13">
+        <v>0</v>
+      </c>
+      <c r="O65" s="13">
+        <v>0</v>
+      </c>
+      <c r="P65" s="16" t="s">
         <v>182</v>
       </c>
       <c r="Q65" s="17" t="str">
@@ -5287,13 +5506,13 @@
       </c>
     </row>
     <row r="66" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A66" s="14" t="s">
+      <c r="A66" s="21" t="s">
         <v>213</v>
       </c>
-      <c r="B66" s="14" t="s">
+      <c r="B66" s="21" t="s">
         <v>214</v>
       </c>
-      <c r="C66" s="14" t="s">
+      <c r="C66" s="16" t="s">
         <v>215</v>
       </c>
       <c r="D66" s="15">
@@ -5314,38 +5533,38 @@
       <c r="I66" s="15">
         <v>0</v>
       </c>
-      <c r="J66" s="16">
-        <v>1</v>
-      </c>
-      <c r="K66" s="16">
-        <v>1</v>
-      </c>
-      <c r="L66" s="16">
-        <v>1</v>
-      </c>
-      <c r="M66" s="16">
-        <v>0</v>
-      </c>
-      <c r="N66" s="16">
-        <v>0</v>
-      </c>
-      <c r="O66" s="19">
-        <v>0</v>
-      </c>
-      <c r="P66" s="14"/>
+      <c r="J66" s="13">
+        <v>1</v>
+      </c>
+      <c r="K66" s="13">
+        <v>1</v>
+      </c>
+      <c r="L66" s="13">
+        <v>1</v>
+      </c>
+      <c r="M66" s="13">
+        <v>0</v>
+      </c>
+      <c r="N66" s="13">
+        <v>0</v>
+      </c>
+      <c r="O66" s="13">
+        <v>0</v>
+      </c>
+      <c r="P66" s="16"/>
       <c r="Q66" s="17" t="str">
         <f>IF(LEN(TRIM(B66))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B66),FIND(" ",TRIM(B66)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B66),FIND(" ",TRIM(B66)&amp;" ")-1)))</f>
         <v>서울</v>
       </c>
     </row>
     <row r="67" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A67" s="14" t="s">
+      <c r="A67" s="21" t="s">
         <v>306</v>
       </c>
-      <c r="B67" s="14" t="s">
+      <c r="B67" s="21" t="s">
         <v>305</v>
       </c>
-      <c r="C67" s="14" t="s">
+      <c r="C67" s="16" t="s">
         <v>307</v>
       </c>
       <c r="D67" s="15">
@@ -5366,25 +5585,25 @@
       <c r="I67" s="15">
         <v>0</v>
       </c>
-      <c r="J67" s="16">
-        <v>1</v>
-      </c>
-      <c r="K67" s="16">
-        <v>1</v>
-      </c>
-      <c r="L67" s="16">
-        <v>0</v>
-      </c>
-      <c r="M67" s="16">
-        <v>0</v>
-      </c>
-      <c r="N67" s="16">
-        <v>0</v>
-      </c>
-      <c r="O67" s="19">
-        <v>0</v>
-      </c>
-      <c r="P67" s="14" t="s">
+      <c r="J67" s="13">
+        <v>1</v>
+      </c>
+      <c r="K67" s="13">
+        <v>1</v>
+      </c>
+      <c r="L67" s="13">
+        <v>0</v>
+      </c>
+      <c r="M67" s="13">
+        <v>0</v>
+      </c>
+      <c r="N67" s="13">
+        <v>0</v>
+      </c>
+      <c r="O67" s="13">
+        <v>0</v>
+      </c>
+      <c r="P67" s="16" t="s">
         <v>304</v>
       </c>
       <c r="Q67" s="17" t="str">
@@ -5393,13 +5612,13 @@
       </c>
     </row>
     <row r="68" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A68" s="14" t="s">
+      <c r="A68" s="21" t="s">
         <v>311</v>
       </c>
-      <c r="B68" s="14" t="s">
+      <c r="B68" s="21" t="s">
         <v>310</v>
       </c>
-      <c r="C68" s="14" t="s">
+      <c r="C68" s="16" t="s">
         <v>309</v>
       </c>
       <c r="D68" s="15">
@@ -5420,25 +5639,25 @@
       <c r="I68" s="15">
         <v>0</v>
       </c>
-      <c r="J68" s="16">
-        <v>1</v>
-      </c>
-      <c r="K68" s="16">
-        <v>1</v>
-      </c>
-      <c r="L68" s="16">
-        <v>0</v>
-      </c>
-      <c r="M68" s="16">
-        <v>0</v>
-      </c>
-      <c r="N68" s="16">
-        <v>0</v>
-      </c>
-      <c r="O68" s="19">
-        <v>0</v>
-      </c>
-      <c r="P68" s="14" t="s">
+      <c r="J68" s="13">
+        <v>1</v>
+      </c>
+      <c r="K68" s="13">
+        <v>1</v>
+      </c>
+      <c r="L68" s="13">
+        <v>0</v>
+      </c>
+      <c r="M68" s="13">
+        <v>0</v>
+      </c>
+      <c r="N68" s="13">
+        <v>0</v>
+      </c>
+      <c r="O68" s="13">
+        <v>0</v>
+      </c>
+      <c r="P68" s="16" t="s">
         <v>308</v>
       </c>
       <c r="Q68" s="17" t="str">
@@ -5447,13 +5666,13 @@
       </c>
     </row>
     <row r="69" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A69" s="14" t="s">
+      <c r="A69" s="21" t="s">
         <v>315</v>
       </c>
-      <c r="B69" s="14" t="s">
+      <c r="B69" s="21" t="s">
         <v>313</v>
       </c>
-      <c r="C69" s="14" t="s">
+      <c r="C69" s="16" t="s">
         <v>314</v>
       </c>
       <c r="D69" s="15">
@@ -5474,25 +5693,25 @@
       <c r="I69" s="15">
         <v>0</v>
       </c>
-      <c r="J69" s="16">
-        <v>1</v>
-      </c>
-      <c r="K69" s="16">
-        <v>1</v>
-      </c>
-      <c r="L69" s="16">
-        <v>1</v>
-      </c>
-      <c r="M69" s="16">
-        <v>0</v>
-      </c>
-      <c r="N69" s="16">
-        <v>0</v>
-      </c>
-      <c r="O69" s="19">
-        <v>0</v>
-      </c>
-      <c r="P69" s="14" t="s">
+      <c r="J69" s="13">
+        <v>1</v>
+      </c>
+      <c r="K69" s="13">
+        <v>1</v>
+      </c>
+      <c r="L69" s="13">
+        <v>1</v>
+      </c>
+      <c r="M69" s="13">
+        <v>0</v>
+      </c>
+      <c r="N69" s="13">
+        <v>0</v>
+      </c>
+      <c r="O69" s="13">
+        <v>0</v>
+      </c>
+      <c r="P69" s="16" t="s">
         <v>312</v>
       </c>
       <c r="Q69" s="17" t="str">
@@ -5501,13 +5720,13 @@
       </c>
     </row>
     <row r="70" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A70" s="14" t="s">
+      <c r="A70" s="21" t="s">
         <v>319</v>
       </c>
-      <c r="B70" s="14" t="s">
+      <c r="B70" s="21" t="s">
         <v>318</v>
       </c>
-      <c r="C70" s="14" t="s">
+      <c r="C70" s="16" t="s">
         <v>317</v>
       </c>
       <c r="D70" s="15">
@@ -5528,25 +5747,25 @@
       <c r="I70" s="15">
         <v>0</v>
       </c>
-      <c r="J70" s="16">
-        <v>1</v>
-      </c>
-      <c r="K70" s="16">
-        <v>1</v>
-      </c>
-      <c r="L70" s="16">
-        <v>0</v>
-      </c>
-      <c r="M70" s="16">
-        <v>0</v>
-      </c>
-      <c r="N70" s="16">
-        <v>0</v>
-      </c>
-      <c r="O70" s="19">
-        <v>0</v>
-      </c>
-      <c r="P70" s="14" t="s">
+      <c r="J70" s="13">
+        <v>1</v>
+      </c>
+      <c r="K70" s="13">
+        <v>1</v>
+      </c>
+      <c r="L70" s="13">
+        <v>0</v>
+      </c>
+      <c r="M70" s="13">
+        <v>0</v>
+      </c>
+      <c r="N70" s="13">
+        <v>0</v>
+      </c>
+      <c r="O70" s="13">
+        <v>0</v>
+      </c>
+      <c r="P70" s="16" t="s">
         <v>316</v>
       </c>
       <c r="Q70" s="17" t="str">
@@ -5555,13 +5774,13 @@
       </c>
     </row>
     <row r="71" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A71" s="14" t="s">
+      <c r="A71" s="21" t="s">
         <v>323</v>
       </c>
-      <c r="B71" s="14" t="s">
+      <c r="B71" s="21" t="s">
         <v>322</v>
       </c>
-      <c r="C71" s="14" t="s">
+      <c r="C71" s="16" t="s">
         <v>321</v>
       </c>
       <c r="D71" s="15">
@@ -5582,25 +5801,25 @@
       <c r="I71" s="15">
         <v>0</v>
       </c>
-      <c r="J71" s="16">
-        <v>0</v>
-      </c>
-      <c r="K71" s="16">
-        <v>1</v>
-      </c>
-      <c r="L71" s="16">
-        <v>0</v>
-      </c>
-      <c r="M71" s="16">
-        <v>0</v>
-      </c>
-      <c r="N71" s="16">
-        <v>0</v>
-      </c>
-      <c r="O71" s="19">
-        <v>0</v>
-      </c>
-      <c r="P71" s="14" t="s">
+      <c r="J71" s="13">
+        <v>0</v>
+      </c>
+      <c r="K71" s="13">
+        <v>1</v>
+      </c>
+      <c r="L71" s="13">
+        <v>0</v>
+      </c>
+      <c r="M71" s="13">
+        <v>0</v>
+      </c>
+      <c r="N71" s="13">
+        <v>0</v>
+      </c>
+      <c r="O71" s="13">
+        <v>0</v>
+      </c>
+      <c r="P71" s="16" t="s">
         <v>320</v>
       </c>
       <c r="Q71" s="17" t="str">
@@ -5609,13 +5828,13 @@
       </c>
     </row>
     <row r="72" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A72" s="14" t="s">
+      <c r="A72" s="21" t="s">
         <v>326</v>
       </c>
-      <c r="B72" s="14" t="s">
+      <c r="B72" s="21" t="s">
         <v>325</v>
       </c>
-      <c r="C72" s="14" t="s">
+      <c r="C72" s="16" t="s">
         <v>324</v>
       </c>
       <c r="D72" s="15">
@@ -5636,38 +5855,38 @@
       <c r="I72" s="15">
         <v>0</v>
       </c>
-      <c r="J72" s="16">
-        <v>0</v>
-      </c>
-      <c r="K72" s="16">
-        <v>1</v>
-      </c>
-      <c r="L72" s="16">
-        <v>0</v>
-      </c>
-      <c r="M72" s="16">
-        <v>0</v>
-      </c>
-      <c r="N72" s="16">
-        <v>0</v>
-      </c>
-      <c r="O72" s="19">
-        <v>0</v>
-      </c>
-      <c r="P72" s="14"/>
+      <c r="J72" s="13">
+        <v>0</v>
+      </c>
+      <c r="K72" s="13">
+        <v>1</v>
+      </c>
+      <c r="L72" s="13">
+        <v>0</v>
+      </c>
+      <c r="M72" s="13">
+        <v>0</v>
+      </c>
+      <c r="N72" s="13">
+        <v>0</v>
+      </c>
+      <c r="O72" s="13">
+        <v>0</v>
+      </c>
+      <c r="P72" s="16"/>
       <c r="Q72" s="17" t="str">
         <f>IF(LEN(TRIM(B72))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B72),FIND(" ",TRIM(B72)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B72),FIND(" ",TRIM(B72)&amp;" ")-1)))</f>
         <v>대구</v>
       </c>
     </row>
     <row r="73" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A73" s="14" t="s">
+      <c r="A73" s="21" t="s">
         <v>329</v>
       </c>
-      <c r="B73" s="14" t="s">
+      <c r="B73" s="21" t="s">
         <v>328</v>
       </c>
-      <c r="C73" s="14" t="s">
+      <c r="C73" s="16" t="s">
         <v>327</v>
       </c>
       <c r="D73" s="15">
@@ -5688,38 +5907,38 @@
       <c r="I73" s="15">
         <v>0</v>
       </c>
-      <c r="J73" s="16">
-        <v>1</v>
-      </c>
-      <c r="K73" s="16">
-        <v>1</v>
-      </c>
-      <c r="L73" s="16">
-        <v>1</v>
-      </c>
-      <c r="M73" s="16">
-        <v>0</v>
-      </c>
-      <c r="N73" s="16">
-        <v>0</v>
-      </c>
-      <c r="O73" s="19">
-        <v>0</v>
-      </c>
-      <c r="P73" s="14"/>
+      <c r="J73" s="13">
+        <v>1</v>
+      </c>
+      <c r="K73" s="13">
+        <v>1</v>
+      </c>
+      <c r="L73" s="13">
+        <v>1</v>
+      </c>
+      <c r="M73" s="13">
+        <v>0</v>
+      </c>
+      <c r="N73" s="13">
+        <v>0</v>
+      </c>
+      <c r="O73" s="13">
+        <v>0</v>
+      </c>
+      <c r="P73" s="16"/>
       <c r="Q73" s="17" t="str">
         <f>IF(LEN(TRIM(B73))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B73),FIND(" ",TRIM(B73)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B73),FIND(" ",TRIM(B73)&amp;" ")-1)))</f>
         <v>대구</v>
       </c>
     </row>
     <row r="74" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A74" s="14" t="s">
+      <c r="A74" s="21" t="s">
         <v>333</v>
       </c>
-      <c r="B74" s="14" t="s">
+      <c r="B74" s="21" t="s">
         <v>332</v>
       </c>
-      <c r="C74" s="14" t="s">
+      <c r="C74" s="16" t="s">
         <v>331</v>
       </c>
       <c r="D74" s="15">
@@ -5740,25 +5959,25 @@
       <c r="I74" s="15">
         <v>0</v>
       </c>
-      <c r="J74" s="16">
-        <v>1</v>
-      </c>
-      <c r="K74" s="16">
-        <v>1</v>
-      </c>
-      <c r="L74" s="16">
-        <v>0</v>
-      </c>
-      <c r="M74" s="16">
-        <v>0</v>
-      </c>
-      <c r="N74" s="16">
-        <v>0</v>
-      </c>
-      <c r="O74" s="19">
-        <v>0</v>
-      </c>
-      <c r="P74" s="14" t="s">
+      <c r="J74" s="13">
+        <v>1</v>
+      </c>
+      <c r="K74" s="13">
+        <v>1</v>
+      </c>
+      <c r="L74" s="13">
+        <v>0</v>
+      </c>
+      <c r="M74" s="13">
+        <v>0</v>
+      </c>
+      <c r="N74" s="13">
+        <v>0</v>
+      </c>
+      <c r="O74" s="13">
+        <v>0</v>
+      </c>
+      <c r="P74" s="16" t="s">
         <v>330</v>
       </c>
       <c r="Q74" s="17" t="str">
@@ -5767,13 +5986,13 @@
       </c>
     </row>
     <row r="75" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A75" s="14" t="s">
+      <c r="A75" s="21" t="s">
         <v>336</v>
       </c>
-      <c r="B75" s="14" t="s">
+      <c r="B75" s="21" t="s">
         <v>335</v>
       </c>
-      <c r="C75" s="14" t="s">
+      <c r="C75" s="16" t="s">
         <v>334</v>
       </c>
       <c r="D75" s="15">
@@ -5794,38 +6013,38 @@
       <c r="I75" s="15">
         <v>0</v>
       </c>
-      <c r="J75" s="16">
-        <v>1</v>
-      </c>
-      <c r="K75" s="16">
-        <v>1</v>
-      </c>
-      <c r="L75" s="16">
-        <v>1</v>
-      </c>
-      <c r="M75" s="16">
-        <v>0</v>
-      </c>
-      <c r="N75" s="16">
-        <v>0</v>
-      </c>
-      <c r="O75" s="19">
-        <v>0</v>
-      </c>
-      <c r="P75" s="14"/>
+      <c r="J75" s="13">
+        <v>1</v>
+      </c>
+      <c r="K75" s="13">
+        <v>1</v>
+      </c>
+      <c r="L75" s="13">
+        <v>1</v>
+      </c>
+      <c r="M75" s="13">
+        <v>0</v>
+      </c>
+      <c r="N75" s="13">
+        <v>0</v>
+      </c>
+      <c r="O75" s="13">
+        <v>0</v>
+      </c>
+      <c r="P75" s="16"/>
       <c r="Q75" s="17" t="str">
         <f>IF(LEN(TRIM(B75))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B75),FIND(" ",TRIM(B75)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B75),FIND(" ",TRIM(B75)&amp;" ")-1)))</f>
         <v>대구</v>
       </c>
     </row>
     <row r="76" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A76" s="14" t="s">
+      <c r="A76" s="21" t="s">
         <v>340</v>
       </c>
-      <c r="B76" s="14" t="s">
+      <c r="B76" s="21" t="s">
         <v>339</v>
       </c>
-      <c r="C76" s="14" t="s">
+      <c r="C76" s="16" t="s">
         <v>338</v>
       </c>
       <c r="D76" s="15">
@@ -5846,25 +6065,25 @@
       <c r="I76" s="15">
         <v>0</v>
       </c>
-      <c r="J76" s="16">
-        <v>0</v>
-      </c>
-      <c r="K76" s="16">
-        <v>1</v>
-      </c>
-      <c r="L76" s="16">
-        <v>0</v>
-      </c>
-      <c r="M76" s="16">
-        <v>0</v>
-      </c>
-      <c r="N76" s="16">
-        <v>0</v>
-      </c>
-      <c r="O76" s="19">
-        <v>0</v>
-      </c>
-      <c r="P76" s="14" t="s">
+      <c r="J76" s="13">
+        <v>0</v>
+      </c>
+      <c r="K76" s="13">
+        <v>1</v>
+      </c>
+      <c r="L76" s="13">
+        <v>0</v>
+      </c>
+      <c r="M76" s="13">
+        <v>0</v>
+      </c>
+      <c r="N76" s="13">
+        <v>0</v>
+      </c>
+      <c r="O76" s="13">
+        <v>0</v>
+      </c>
+      <c r="P76" s="16" t="s">
         <v>337</v>
       </c>
       <c r="Q76" s="17" t="str">
@@ -5873,13 +6092,13 @@
       </c>
     </row>
     <row r="77" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A77" s="14" t="s">
+      <c r="A77" s="21" t="s">
         <v>343</v>
       </c>
-      <c r="B77" s="14" t="s">
+      <c r="B77" s="21" t="s">
         <v>342</v>
       </c>
-      <c r="C77" s="14" t="s">
+      <c r="C77" s="16" t="s">
         <v>341</v>
       </c>
       <c r="D77" s="15">
@@ -5900,25 +6119,25 @@
       <c r="I77" s="15">
         <v>0</v>
       </c>
-      <c r="J77" s="16">
-        <v>1</v>
-      </c>
-      <c r="K77" s="16">
-        <v>1</v>
-      </c>
-      <c r="L77" s="16">
-        <v>0</v>
-      </c>
-      <c r="M77" s="16">
-        <v>0</v>
-      </c>
-      <c r="N77" s="16">
-        <v>0</v>
-      </c>
-      <c r="O77" s="19">
-        <v>0</v>
-      </c>
-      <c r="P77" s="14" t="s">
+      <c r="J77" s="13">
+        <v>1</v>
+      </c>
+      <c r="K77" s="13">
+        <v>1</v>
+      </c>
+      <c r="L77" s="13">
+        <v>0</v>
+      </c>
+      <c r="M77" s="13">
+        <v>0</v>
+      </c>
+      <c r="N77" s="13">
+        <v>0</v>
+      </c>
+      <c r="O77" s="13">
+        <v>0</v>
+      </c>
+      <c r="P77" s="16" t="s">
         <v>304</v>
       </c>
       <c r="Q77" s="17" t="str">
@@ -5927,13 +6146,13 @@
       </c>
     </row>
     <row r="78" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A78" s="14" t="s">
+      <c r="A78" s="21" t="s">
         <v>346</v>
       </c>
-      <c r="B78" s="14" t="s">
+      <c r="B78" s="21" t="s">
         <v>345</v>
       </c>
-      <c r="C78" s="14" t="s">
+      <c r="C78" s="16" t="s">
         <v>344</v>
       </c>
       <c r="D78" s="15">
@@ -5954,25 +6173,25 @@
       <c r="I78" s="15">
         <v>0</v>
       </c>
-      <c r="J78" s="16">
-        <v>1</v>
-      </c>
-      <c r="K78" s="16">
-        <v>1</v>
-      </c>
-      <c r="L78" s="16">
-        <v>0</v>
-      </c>
-      <c r="M78" s="16">
-        <v>0</v>
-      </c>
-      <c r="N78" s="16">
-        <v>0</v>
-      </c>
-      <c r="O78" s="19">
-        <v>0</v>
-      </c>
-      <c r="P78" s="14" t="s">
+      <c r="J78" s="13">
+        <v>1</v>
+      </c>
+      <c r="K78" s="13">
+        <v>1</v>
+      </c>
+      <c r="L78" s="13">
+        <v>0</v>
+      </c>
+      <c r="M78" s="13">
+        <v>0</v>
+      </c>
+      <c r="N78" s="13">
+        <v>0</v>
+      </c>
+      <c r="O78" s="13">
+        <v>0</v>
+      </c>
+      <c r="P78" s="16" t="s">
         <v>312</v>
       </c>
       <c r="Q78" s="17" t="str">
@@ -5981,13 +6200,13 @@
       </c>
     </row>
     <row r="79" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A79" s="14" t="s">
+      <c r="A79" s="21" t="s">
         <v>350</v>
       </c>
-      <c r="B79" s="14" t="s">
+      <c r="B79" s="21" t="s">
         <v>349</v>
       </c>
-      <c r="C79" s="14" t="s">
+      <c r="C79" s="16" t="s">
         <v>348</v>
       </c>
       <c r="D79" s="15">
@@ -6008,25 +6227,25 @@
       <c r="I79" s="15">
         <v>0</v>
       </c>
-      <c r="J79" s="16">
-        <v>1</v>
-      </c>
-      <c r="K79" s="16">
-        <v>0</v>
-      </c>
-      <c r="L79" s="16">
-        <v>1</v>
-      </c>
-      <c r="M79" s="16">
-        <v>0</v>
-      </c>
-      <c r="N79" s="16">
-        <v>0</v>
-      </c>
-      <c r="O79" s="19">
-        <v>0</v>
-      </c>
-      <c r="P79" s="14" t="s">
+      <c r="J79" s="13">
+        <v>1</v>
+      </c>
+      <c r="K79" s="13">
+        <v>0</v>
+      </c>
+      <c r="L79" s="13">
+        <v>1</v>
+      </c>
+      <c r="M79" s="13">
+        <v>0</v>
+      </c>
+      <c r="N79" s="13">
+        <v>0</v>
+      </c>
+      <c r="O79" s="13">
+        <v>0</v>
+      </c>
+      <c r="P79" s="16" t="s">
         <v>347</v>
       </c>
       <c r="Q79" s="17" t="str">
@@ -6035,13 +6254,13 @@
       </c>
     </row>
     <row r="80" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A80" s="14" t="s">
+      <c r="A80" s="21" t="s">
         <v>354</v>
       </c>
-      <c r="B80" s="14" t="s">
+      <c r="B80" s="21" t="s">
         <v>353</v>
       </c>
-      <c r="C80" s="14" t="s">
+      <c r="C80" s="16" t="s">
         <v>352</v>
       </c>
       <c r="D80" s="15">
@@ -6062,25 +6281,25 @@
       <c r="I80" s="15">
         <v>0</v>
       </c>
-      <c r="J80" s="16">
-        <v>1</v>
-      </c>
-      <c r="K80" s="16">
-        <v>0</v>
-      </c>
-      <c r="L80" s="16">
-        <v>1</v>
-      </c>
-      <c r="M80" s="16">
-        <v>0</v>
-      </c>
-      <c r="N80" s="16">
-        <v>0</v>
-      </c>
-      <c r="O80" s="19">
-        <v>0</v>
-      </c>
-      <c r="P80" s="14" t="s">
+      <c r="J80" s="13">
+        <v>1</v>
+      </c>
+      <c r="K80" s="13">
+        <v>0</v>
+      </c>
+      <c r="L80" s="13">
+        <v>1</v>
+      </c>
+      <c r="M80" s="13">
+        <v>0</v>
+      </c>
+      <c r="N80" s="13">
+        <v>0</v>
+      </c>
+      <c r="O80" s="13">
+        <v>0</v>
+      </c>
+      <c r="P80" s="16" t="s">
         <v>351</v>
       </c>
       <c r="Q80" s="17" t="str">
@@ -6089,13 +6308,13 @@
       </c>
     </row>
     <row r="81" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A81" s="14" t="s">
+      <c r="A81" s="21" t="s">
         <v>358</v>
       </c>
-      <c r="B81" s="14" t="s">
+      <c r="B81" s="21" t="s">
         <v>357</v>
       </c>
-      <c r="C81" s="14" t="s">
+      <c r="C81" s="16" t="s">
         <v>356</v>
       </c>
       <c r="D81" s="15">
@@ -6116,25 +6335,25 @@
       <c r="I81" s="15">
         <v>0</v>
       </c>
-      <c r="J81" s="16">
-        <v>1</v>
-      </c>
-      <c r="K81" s="16">
-        <v>1</v>
-      </c>
-      <c r="L81" s="16">
-        <v>1</v>
-      </c>
-      <c r="M81" s="16">
-        <v>0</v>
-      </c>
-      <c r="N81" s="16">
-        <v>0</v>
-      </c>
-      <c r="O81" s="19">
-        <v>0</v>
-      </c>
-      <c r="P81" s="14" t="s">
+      <c r="J81" s="13">
+        <v>1</v>
+      </c>
+      <c r="K81" s="13">
+        <v>1</v>
+      </c>
+      <c r="L81" s="13">
+        <v>1</v>
+      </c>
+      <c r="M81" s="13">
+        <v>0</v>
+      </c>
+      <c r="N81" s="13">
+        <v>0</v>
+      </c>
+      <c r="O81" s="13">
+        <v>0</v>
+      </c>
+      <c r="P81" s="16" t="s">
         <v>355</v>
       </c>
       <c r="Q81" s="17" t="str">
@@ -6143,13 +6362,13 @@
       </c>
     </row>
     <row r="82" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A82" s="14" t="s">
+      <c r="A82" s="21" t="s">
         <v>361</v>
       </c>
-      <c r="B82" s="14" t="s">
+      <c r="B82" s="21" t="s">
         <v>360</v>
       </c>
-      <c r="C82" s="14" t="s">
+      <c r="C82" s="16" t="s">
         <v>359</v>
       </c>
       <c r="D82" s="15">
@@ -6170,38 +6389,38 @@
       <c r="I82" s="15">
         <v>0</v>
       </c>
-      <c r="J82" s="16">
-        <v>0</v>
-      </c>
-      <c r="K82" s="16">
-        <v>1</v>
-      </c>
-      <c r="L82" s="16">
-        <v>0</v>
-      </c>
-      <c r="M82" s="16">
-        <v>0</v>
-      </c>
-      <c r="N82" s="16">
-        <v>0</v>
-      </c>
-      <c r="O82" s="19">
-        <v>0</v>
-      </c>
-      <c r="P82" s="14"/>
+      <c r="J82" s="13">
+        <v>0</v>
+      </c>
+      <c r="K82" s="13">
+        <v>1</v>
+      </c>
+      <c r="L82" s="13">
+        <v>0</v>
+      </c>
+      <c r="M82" s="13">
+        <v>0</v>
+      </c>
+      <c r="N82" s="13">
+        <v>0</v>
+      </c>
+      <c r="O82" s="13">
+        <v>0</v>
+      </c>
+      <c r="P82" s="16"/>
       <c r="Q82" s="17" t="str">
         <f>IF(LEN(TRIM(B82))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B82),FIND(" ",TRIM(B82)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B82),FIND(" ",TRIM(B82)&amp;" ")-1)))</f>
         <v>대구</v>
       </c>
     </row>
     <row r="83" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A83" s="14" t="s">
+      <c r="A83" s="21" t="s">
         <v>364</v>
       </c>
-      <c r="B83" s="14" t="s">
+      <c r="B83" s="21" t="s">
         <v>363</v>
       </c>
-      <c r="C83" s="14" t="s">
+      <c r="C83" s="16" t="s">
         <v>362</v>
       </c>
       <c r="D83" s="15">
@@ -6222,38 +6441,38 @@
       <c r="I83" s="15">
         <v>0</v>
       </c>
-      <c r="J83" s="16">
-        <v>1</v>
-      </c>
-      <c r="K83" s="16">
-        <v>1</v>
-      </c>
-      <c r="L83" s="16">
-        <v>0</v>
-      </c>
-      <c r="M83" s="16">
-        <v>0</v>
-      </c>
-      <c r="N83" s="16">
-        <v>0</v>
-      </c>
-      <c r="O83" s="19">
-        <v>0</v>
-      </c>
-      <c r="P83" s="14"/>
+      <c r="J83" s="13">
+        <v>1</v>
+      </c>
+      <c r="K83" s="13">
+        <v>1</v>
+      </c>
+      <c r="L83" s="13">
+        <v>0</v>
+      </c>
+      <c r="M83" s="13">
+        <v>0</v>
+      </c>
+      <c r="N83" s="13">
+        <v>0</v>
+      </c>
+      <c r="O83" s="13">
+        <v>0</v>
+      </c>
+      <c r="P83" s="16"/>
       <c r="Q83" s="17" t="str">
         <f>IF(LEN(TRIM(B83))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B83),FIND(" ",TRIM(B83)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B83),FIND(" ",TRIM(B83)&amp;" ")-1)))</f>
         <v>대구</v>
       </c>
     </row>
     <row r="84" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A84" s="14" t="s">
+      <c r="A84" s="21" t="s">
         <v>368</v>
       </c>
-      <c r="B84" s="14" t="s">
+      <c r="B84" s="21" t="s">
         <v>367</v>
       </c>
-      <c r="C84" s="14" t="s">
+      <c r="C84" s="16" t="s">
         <v>366</v>
       </c>
       <c r="D84" s="15">
@@ -6274,25 +6493,25 @@
       <c r="I84" s="15">
         <v>0</v>
       </c>
-      <c r="J84" s="16">
-        <v>1</v>
-      </c>
-      <c r="K84" s="16">
-        <v>1</v>
-      </c>
-      <c r="L84" s="16">
-        <v>0</v>
-      </c>
-      <c r="M84" s="16">
-        <v>0</v>
-      </c>
-      <c r="N84" s="16">
-        <v>0</v>
-      </c>
-      <c r="O84" s="19">
-        <v>0</v>
-      </c>
-      <c r="P84" s="14" t="s">
+      <c r="J84" s="13">
+        <v>1</v>
+      </c>
+      <c r="K84" s="13">
+        <v>1</v>
+      </c>
+      <c r="L84" s="13">
+        <v>0</v>
+      </c>
+      <c r="M84" s="13">
+        <v>0</v>
+      </c>
+      <c r="N84" s="13">
+        <v>0</v>
+      </c>
+      <c r="O84" s="13">
+        <v>0</v>
+      </c>
+      <c r="P84" s="16" t="s">
         <v>365</v>
       </c>
       <c r="Q84" s="17" t="str">
@@ -6301,13 +6520,13 @@
       </c>
     </row>
     <row r="85" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A85" s="14" t="s">
+      <c r="A85" s="21" t="s">
         <v>371</v>
       </c>
-      <c r="B85" s="14" t="s">
+      <c r="B85" s="21" t="s">
         <v>370</v>
       </c>
-      <c r="C85" s="14" t="s">
+      <c r="C85" s="16" t="s">
         <v>369</v>
       </c>
       <c r="D85" s="15">
@@ -6328,38 +6547,38 @@
       <c r="I85" s="15">
         <v>0</v>
       </c>
-      <c r="J85" s="16">
-        <v>1</v>
-      </c>
-      <c r="K85" s="16">
-        <v>1</v>
-      </c>
-      <c r="L85" s="16">
-        <v>1</v>
-      </c>
-      <c r="M85" s="16">
-        <v>0</v>
-      </c>
-      <c r="N85" s="16">
-        <v>0</v>
-      </c>
-      <c r="O85" s="19">
-        <v>0</v>
-      </c>
-      <c r="P85" s="14"/>
+      <c r="J85" s="13">
+        <v>1</v>
+      </c>
+      <c r="K85" s="13">
+        <v>1</v>
+      </c>
+      <c r="L85" s="13">
+        <v>1</v>
+      </c>
+      <c r="M85" s="13">
+        <v>0</v>
+      </c>
+      <c r="N85" s="13">
+        <v>0</v>
+      </c>
+      <c r="O85" s="13">
+        <v>0</v>
+      </c>
+      <c r="P85" s="16"/>
       <c r="Q85" s="17" t="str">
         <f>IF(LEN(TRIM(B85))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B85),FIND(" ",TRIM(B85)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B85),FIND(" ",TRIM(B85)&amp;" ")-1)))</f>
         <v>대구</v>
       </c>
     </row>
     <row r="86" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A86" s="14" t="s">
+      <c r="A86" s="21" t="s">
         <v>374</v>
       </c>
-      <c r="B86" s="14" t="s">
+      <c r="B86" s="21" t="s">
         <v>373</v>
       </c>
-      <c r="C86" s="14" t="s">
+      <c r="C86" s="16" t="s">
         <v>372</v>
       </c>
       <c r="D86" s="15">
@@ -6380,38 +6599,38 @@
       <c r="I86" s="15">
         <v>0</v>
       </c>
-      <c r="J86" s="16">
-        <v>1</v>
-      </c>
-      <c r="K86" s="16">
-        <v>0</v>
-      </c>
-      <c r="L86" s="16">
-        <v>0</v>
-      </c>
-      <c r="M86" s="16">
-        <v>0</v>
-      </c>
-      <c r="N86" s="16">
-        <v>0</v>
-      </c>
-      <c r="O86" s="19">
-        <v>0</v>
-      </c>
-      <c r="P86" s="14"/>
+      <c r="J86" s="13">
+        <v>1</v>
+      </c>
+      <c r="K86" s="13">
+        <v>0</v>
+      </c>
+      <c r="L86" s="13">
+        <v>0</v>
+      </c>
+      <c r="M86" s="13">
+        <v>0</v>
+      </c>
+      <c r="N86" s="13">
+        <v>0</v>
+      </c>
+      <c r="O86" s="13">
+        <v>0</v>
+      </c>
+      <c r="P86" s="16"/>
       <c r="Q86" s="17" t="str">
         <f>IF(LEN(TRIM(B86))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B86),FIND(" ",TRIM(B86)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B86),FIND(" ",TRIM(B86)&amp;" ")-1)))</f>
         <v>대구</v>
       </c>
     </row>
     <row r="87" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A87" s="14" t="s">
+      <c r="A87" s="21" t="s">
         <v>378</v>
       </c>
-      <c r="B87" s="14" t="s">
+      <c r="B87" s="21" t="s">
         <v>377</v>
       </c>
-      <c r="C87" s="14" t="s">
+      <c r="C87" s="16" t="s">
         <v>376</v>
       </c>
       <c r="D87" s="15">
@@ -6432,25 +6651,25 @@
       <c r="I87" s="15">
         <v>0</v>
       </c>
-      <c r="J87" s="16">
-        <v>1</v>
-      </c>
-      <c r="K87" s="16">
-        <v>1</v>
-      </c>
-      <c r="L87" s="16">
-        <v>1</v>
-      </c>
-      <c r="M87" s="16">
-        <v>0</v>
-      </c>
-      <c r="N87" s="16">
-        <v>0</v>
-      </c>
-      <c r="O87" s="19">
-        <v>0</v>
-      </c>
-      <c r="P87" s="14" t="s">
+      <c r="J87" s="13">
+        <v>1</v>
+      </c>
+      <c r="K87" s="13">
+        <v>1</v>
+      </c>
+      <c r="L87" s="13">
+        <v>1</v>
+      </c>
+      <c r="M87" s="13">
+        <v>0</v>
+      </c>
+      <c r="N87" s="13">
+        <v>0</v>
+      </c>
+      <c r="O87" s="13">
+        <v>0</v>
+      </c>
+      <c r="P87" s="16" t="s">
         <v>375</v>
       </c>
       <c r="Q87" s="17" t="str">
@@ -6459,13 +6678,13 @@
       </c>
     </row>
     <row r="88" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A88" s="14" t="s">
+      <c r="A88" s="21" t="s">
         <v>380</v>
       </c>
-      <c r="B88" s="14" t="s">
+      <c r="B88" s="21" t="s">
         <v>379</v>
       </c>
-      <c r="C88" s="14" t="s">
+      <c r="C88" s="16" t="s">
         <v>381</v>
       </c>
       <c r="D88" s="15">
@@ -6486,38 +6705,38 @@
       <c r="I88" s="15">
         <v>0</v>
       </c>
-      <c r="J88" s="16">
-        <v>1</v>
-      </c>
-      <c r="K88" s="16">
-        <v>1</v>
-      </c>
-      <c r="L88" s="16">
-        <v>0</v>
-      </c>
-      <c r="M88" s="16">
-        <v>0</v>
-      </c>
-      <c r="N88" s="16">
-        <v>0</v>
-      </c>
-      <c r="O88" s="19">
-        <v>0</v>
-      </c>
-      <c r="P88" s="14"/>
+      <c r="J88" s="13">
+        <v>1</v>
+      </c>
+      <c r="K88" s="13">
+        <v>1</v>
+      </c>
+      <c r="L88" s="13">
+        <v>0</v>
+      </c>
+      <c r="M88" s="13">
+        <v>0</v>
+      </c>
+      <c r="N88" s="13">
+        <v>0</v>
+      </c>
+      <c r="O88" s="13">
+        <v>0</v>
+      </c>
+      <c r="P88" s="16"/>
       <c r="Q88" s="17" t="str">
         <f>IF(LEN(TRIM(B88))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B88),FIND(" ",TRIM(B88)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B88),FIND(" ",TRIM(B88)&amp;" ")-1)))</f>
         <v>대구</v>
       </c>
     </row>
     <row r="89" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A89" s="14" t="s">
+      <c r="A89" s="21" t="s">
         <v>384</v>
       </c>
-      <c r="B89" s="14" t="s">
+      <c r="B89" s="21" t="s">
         <v>383</v>
       </c>
-      <c r="C89" s="14" t="s">
+      <c r="C89" s="16" t="s">
         <v>382</v>
       </c>
       <c r="D89" s="15">
@@ -6538,38 +6757,38 @@
       <c r="I89" s="15">
         <v>0</v>
       </c>
-      <c r="J89" s="16">
-        <v>1</v>
-      </c>
-      <c r="K89" s="16">
-        <v>1</v>
-      </c>
-      <c r="L89" s="16">
-        <v>1</v>
-      </c>
-      <c r="M89" s="16">
-        <v>0</v>
-      </c>
-      <c r="N89" s="16">
-        <v>0</v>
-      </c>
-      <c r="O89" s="19">
-        <v>0</v>
-      </c>
-      <c r="P89" s="14"/>
+      <c r="J89" s="13">
+        <v>1</v>
+      </c>
+      <c r="K89" s="13">
+        <v>1</v>
+      </c>
+      <c r="L89" s="13">
+        <v>1</v>
+      </c>
+      <c r="M89" s="13">
+        <v>0</v>
+      </c>
+      <c r="N89" s="13">
+        <v>0</v>
+      </c>
+      <c r="O89" s="13">
+        <v>0</v>
+      </c>
+      <c r="P89" s="16"/>
       <c r="Q89" s="17" t="str">
         <f>IF(LEN(TRIM(B89))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B89),FIND(" ",TRIM(B89)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B89),FIND(" ",TRIM(B89)&amp;" ")-1)))</f>
         <v>대구</v>
       </c>
     </row>
     <row r="90" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A90" s="14" t="s">
+      <c r="A90" s="21" t="s">
         <v>388</v>
       </c>
-      <c r="B90" s="14" t="s">
+      <c r="B90" s="21" t="s">
         <v>387</v>
       </c>
-      <c r="C90" s="14" t="s">
+      <c r="C90" s="16" t="s">
         <v>386</v>
       </c>
       <c r="D90" s="15">
@@ -6590,25 +6809,25 @@
       <c r="I90" s="15">
         <v>0</v>
       </c>
-      <c r="J90" s="16">
-        <v>0</v>
-      </c>
-      <c r="K90" s="16">
-        <v>1</v>
-      </c>
-      <c r="L90" s="16">
-        <v>1</v>
-      </c>
-      <c r="M90" s="16">
-        <v>0</v>
-      </c>
-      <c r="N90" s="16">
-        <v>0</v>
-      </c>
-      <c r="O90" s="19">
-        <v>0</v>
-      </c>
-      <c r="P90" s="14" t="s">
+      <c r="J90" s="13">
+        <v>0</v>
+      </c>
+      <c r="K90" s="13">
+        <v>1</v>
+      </c>
+      <c r="L90" s="13">
+        <v>1</v>
+      </c>
+      <c r="M90" s="13">
+        <v>0</v>
+      </c>
+      <c r="N90" s="13">
+        <v>0</v>
+      </c>
+      <c r="O90" s="13">
+        <v>0</v>
+      </c>
+      <c r="P90" s="16" t="s">
         <v>385</v>
       </c>
       <c r="Q90" s="17" t="str">
@@ -6617,13 +6836,13 @@
       </c>
     </row>
     <row r="91" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A91" s="14" t="s">
+      <c r="A91" s="21" t="s">
         <v>391</v>
       </c>
-      <c r="B91" s="14" t="s">
+      <c r="B91" s="21" t="s">
         <v>390</v>
       </c>
-      <c r="C91" s="14" t="s">
+      <c r="C91" s="16" t="s">
         <v>389</v>
       </c>
       <c r="D91" s="15">
@@ -6644,257 +6863,3101 @@
       <c r="I91" s="15">
         <v>0</v>
       </c>
-      <c r="J91" s="16">
-        <v>1</v>
-      </c>
-      <c r="K91" s="16">
-        <v>1</v>
-      </c>
-      <c r="L91" s="16">
-        <v>1</v>
-      </c>
-      <c r="M91" s="16">
-        <v>0</v>
-      </c>
-      <c r="N91" s="16">
-        <v>0</v>
-      </c>
-      <c r="O91" s="19">
-        <v>0</v>
-      </c>
-      <c r="P91" s="14"/>
+      <c r="J91" s="13">
+        <v>1</v>
+      </c>
+      <c r="K91" s="13">
+        <v>1</v>
+      </c>
+      <c r="L91" s="13">
+        <v>1</v>
+      </c>
+      <c r="M91" s="13">
+        <v>0</v>
+      </c>
+      <c r="N91" s="13">
+        <v>0</v>
+      </c>
+      <c r="O91" s="13">
+        <v>0</v>
+      </c>
+      <c r="P91" s="16"/>
       <c r="Q91" s="17" t="str">
         <f>IF(LEN(TRIM(B91))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B91),FIND(" ",TRIM(B91)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B91),FIND(" ",TRIM(B91)&amp;" ")-1)))</f>
         <v>대구</v>
       </c>
     </row>
     <row r="92" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A92" s="14"/>
-      <c r="B92" s="14"/>
-      <c r="C92" s="14"/>
-      <c r="D92" s="15"/>
-      <c r="E92" s="15"/>
-      <c r="F92" s="15"/>
-      <c r="G92" s="15"/>
-      <c r="H92" s="15"/>
-      <c r="I92" s="15"/>
-      <c r="J92" s="16"/>
-      <c r="K92" s="16"/>
-      <c r="L92" s="16"/>
-      <c r="M92" s="16"/>
-      <c r="N92" s="16"/>
-      <c r="O92" s="19"/>
-      <c r="P92" s="14"/>
+      <c r="A92" s="21" t="s">
+        <v>394</v>
+      </c>
+      <c r="B92" s="21" t="s">
+        <v>393</v>
+      </c>
+      <c r="C92" s="16" t="s">
+        <v>392</v>
+      </c>
+      <c r="D92" s="15">
+        <v>1</v>
+      </c>
+      <c r="E92" s="15">
+        <v>0</v>
+      </c>
+      <c r="F92" s="15">
+        <v>0</v>
+      </c>
+      <c r="G92" s="15">
+        <v>0</v>
+      </c>
+      <c r="H92" s="15">
+        <v>0</v>
+      </c>
+      <c r="I92" s="15">
+        <v>0</v>
+      </c>
+      <c r="J92" s="13">
+        <v>0</v>
+      </c>
+      <c r="K92" s="13">
+        <v>1</v>
+      </c>
+      <c r="L92" s="13">
+        <v>0</v>
+      </c>
+      <c r="M92" s="13">
+        <v>0</v>
+      </c>
+      <c r="N92" s="13">
+        <v>0</v>
+      </c>
+      <c r="O92" s="13">
+        <v>0</v>
+      </c>
+      <c r="P92" s="16"/>
       <c r="Q92" s="17" t="str">
         <f>IF(LEN(TRIM(B92))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B92),FIND(" ",TRIM(B92)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B92),FIND(" ",TRIM(B92)&amp;" ")-1)))</f>
-        <v/>
+        <v>서울</v>
       </c>
     </row>
     <row r="93" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A93" s="14"/>
-      <c r="B93" s="14"/>
-      <c r="C93" s="14"/>
-      <c r="D93" s="15"/>
-      <c r="E93" s="15"/>
-      <c r="F93" s="15"/>
-      <c r="G93" s="15"/>
-      <c r="H93" s="15"/>
-      <c r="I93" s="15"/>
-      <c r="J93" s="16"/>
-      <c r="K93" s="16"/>
-      <c r="L93" s="16"/>
-      <c r="M93" s="16"/>
-      <c r="N93" s="16"/>
-      <c r="O93" s="19"/>
-      <c r="P93" s="14"/>
+      <c r="A93" s="21" t="s">
+        <v>397</v>
+      </c>
+      <c r="B93" s="21" t="s">
+        <v>396</v>
+      </c>
+      <c r="C93" s="16" t="s">
+        <v>433</v>
+      </c>
+      <c r="D93" s="15">
+        <v>1</v>
+      </c>
+      <c r="E93" s="15">
+        <v>0</v>
+      </c>
+      <c r="F93" s="15">
+        <v>0</v>
+      </c>
+      <c r="G93" s="15">
+        <v>0</v>
+      </c>
+      <c r="H93" s="15">
+        <v>0</v>
+      </c>
+      <c r="I93" s="15">
+        <v>0</v>
+      </c>
+      <c r="J93" s="13">
+        <v>1</v>
+      </c>
+      <c r="K93" s="13">
+        <v>1</v>
+      </c>
+      <c r="L93" s="13">
+        <v>0</v>
+      </c>
+      <c r="M93" s="13">
+        <v>0</v>
+      </c>
+      <c r="N93" s="13">
+        <v>0</v>
+      </c>
+      <c r="O93" s="13">
+        <v>0</v>
+      </c>
+      <c r="P93" s="16" t="s">
+        <v>395</v>
+      </c>
       <c r="Q93" s="17" t="str">
         <f>IF(LEN(TRIM(B93))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B93),FIND(" ",TRIM(B93)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B93),FIND(" ",TRIM(B93)&amp;" ")-1)))</f>
-        <v/>
+        <v>서울</v>
       </c>
     </row>
     <row r="94" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A94" s="14"/>
-      <c r="B94" s="14"/>
-      <c r="C94" s="14"/>
-      <c r="D94" s="15"/>
-      <c r="E94" s="15"/>
-      <c r="F94" s="15"/>
-      <c r="G94" s="15"/>
-      <c r="H94" s="15"/>
-      <c r="I94" s="15"/>
-      <c r="J94" s="16"/>
-      <c r="K94" s="16"/>
-      <c r="L94" s="16"/>
-      <c r="M94" s="16"/>
-      <c r="N94" s="16"/>
-      <c r="O94" s="19"/>
-      <c r="P94" s="14"/>
+      <c r="A94" s="21" t="s">
+        <v>400</v>
+      </c>
+      <c r="B94" s="21" t="s">
+        <v>399</v>
+      </c>
+      <c r="C94" s="16" t="s">
+        <v>398</v>
+      </c>
+      <c r="D94" s="15">
+        <v>1</v>
+      </c>
+      <c r="E94" s="15">
+        <v>0</v>
+      </c>
+      <c r="F94" s="15">
+        <v>0</v>
+      </c>
+      <c r="G94" s="15">
+        <v>1</v>
+      </c>
+      <c r="H94" s="15">
+        <v>0</v>
+      </c>
+      <c r="I94" s="15">
+        <v>0</v>
+      </c>
+      <c r="J94" s="13">
+        <v>1</v>
+      </c>
+      <c r="K94" s="13">
+        <v>1</v>
+      </c>
+      <c r="L94" s="13">
+        <v>1</v>
+      </c>
+      <c r="M94" s="13">
+        <v>0</v>
+      </c>
+      <c r="N94" s="13">
+        <v>0</v>
+      </c>
+      <c r="O94" s="13">
+        <v>0</v>
+      </c>
+      <c r="P94" s="16"/>
       <c r="Q94" s="17" t="str">
         <f>IF(LEN(TRIM(B94))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B94),FIND(" ",TRIM(B94)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B94),FIND(" ",TRIM(B94)&amp;" ")-1)))</f>
-        <v/>
+        <v>서울</v>
       </c>
     </row>
     <row r="95" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A95" s="14"/>
-      <c r="B95" s="14"/>
-      <c r="C95" s="14"/>
-      <c r="D95" s="15"/>
-      <c r="E95" s="15"/>
-      <c r="F95" s="15"/>
-      <c r="G95" s="15"/>
-      <c r="H95" s="15"/>
-      <c r="I95" s="15"/>
-      <c r="J95" s="16"/>
-      <c r="K95" s="16"/>
-      <c r="L95" s="16"/>
-      <c r="M95" s="16"/>
-      <c r="N95" s="16"/>
-      <c r="O95" s="19"/>
-      <c r="P95" s="14"/>
+      <c r="A95" s="21" t="s">
+        <v>403</v>
+      </c>
+      <c r="B95" s="21" t="s">
+        <v>402</v>
+      </c>
+      <c r="C95" s="16" t="s">
+        <v>401</v>
+      </c>
+      <c r="D95" s="15">
+        <v>1</v>
+      </c>
+      <c r="E95" s="15">
+        <v>0</v>
+      </c>
+      <c r="F95" s="15">
+        <v>0</v>
+      </c>
+      <c r="G95" s="15">
+        <v>0</v>
+      </c>
+      <c r="H95" s="15">
+        <v>0</v>
+      </c>
+      <c r="I95" s="15">
+        <v>0</v>
+      </c>
+      <c r="J95" s="13">
+        <v>1</v>
+      </c>
+      <c r="K95" s="13">
+        <v>1</v>
+      </c>
+      <c r="L95" s="13">
+        <v>0</v>
+      </c>
+      <c r="M95" s="13">
+        <v>0</v>
+      </c>
+      <c r="N95" s="13">
+        <v>0</v>
+      </c>
+      <c r="O95" s="13">
+        <v>0</v>
+      </c>
+      <c r="P95" s="16"/>
       <c r="Q95" s="17" t="str">
         <f>IF(LEN(TRIM(B95))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B95),FIND(" ",TRIM(B95)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B95),FIND(" ",TRIM(B95)&amp;" ")-1)))</f>
-        <v/>
+        <v>서울</v>
       </c>
     </row>
     <row r="96" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A96" s="14"/>
-      <c r="B96" s="14"/>
-      <c r="C96" s="14"/>
-      <c r="D96" s="15"/>
-      <c r="E96" s="15"/>
-      <c r="F96" s="15"/>
-      <c r="G96" s="15"/>
-      <c r="H96" s="15"/>
-      <c r="I96" s="15"/>
-      <c r="J96" s="16"/>
-      <c r="K96" s="16"/>
-      <c r="L96" s="16"/>
-      <c r="M96" s="16"/>
-      <c r="N96" s="16"/>
-      <c r="O96" s="19"/>
-      <c r="P96" s="14"/>
+      <c r="A96" s="21" t="s">
+        <v>407</v>
+      </c>
+      <c r="B96" s="21" t="s">
+        <v>406</v>
+      </c>
+      <c r="C96" s="16" t="s">
+        <v>405</v>
+      </c>
+      <c r="D96" s="15">
+        <v>1</v>
+      </c>
+      <c r="E96" s="15">
+        <v>0</v>
+      </c>
+      <c r="F96" s="15">
+        <v>0</v>
+      </c>
+      <c r="G96" s="15">
+        <v>0</v>
+      </c>
+      <c r="H96" s="15">
+        <v>0</v>
+      </c>
+      <c r="I96" s="15">
+        <v>0</v>
+      </c>
+      <c r="J96" s="13">
+        <v>1</v>
+      </c>
+      <c r="K96" s="13">
+        <v>1</v>
+      </c>
+      <c r="L96" s="13">
+        <v>0</v>
+      </c>
+      <c r="M96" s="13">
+        <v>0</v>
+      </c>
+      <c r="N96" s="13">
+        <v>0</v>
+      </c>
+      <c r="O96" s="13">
+        <v>0</v>
+      </c>
+      <c r="P96" s="16" t="s">
+        <v>404</v>
+      </c>
       <c r="Q96" s="17" t="str">
         <f>IF(LEN(TRIM(B96))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B96),FIND(" ",TRIM(B96)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B96),FIND(" ",TRIM(B96)&amp;" ")-1)))</f>
-        <v/>
+        <v>서울</v>
       </c>
     </row>
     <row r="97" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A97" s="14"/>
-      <c r="B97" s="14"/>
-      <c r="C97" s="14"/>
-      <c r="D97" s="15"/>
-      <c r="E97" s="15"/>
-      <c r="F97" s="15"/>
-      <c r="G97" s="15"/>
-      <c r="H97" s="15"/>
-      <c r="I97" s="15"/>
-      <c r="J97" s="16"/>
-      <c r="K97" s="16"/>
-      <c r="L97" s="16"/>
-      <c r="M97" s="16"/>
-      <c r="N97" s="16"/>
-      <c r="O97" s="19"/>
-      <c r="P97" s="14"/>
+      <c r="A97" s="21" t="s">
+        <v>410</v>
+      </c>
+      <c r="B97" s="21" t="s">
+        <v>409</v>
+      </c>
+      <c r="C97" s="16" t="s">
+        <v>408</v>
+      </c>
+      <c r="D97" s="15">
+        <v>1</v>
+      </c>
+      <c r="E97" s="15">
+        <v>0</v>
+      </c>
+      <c r="F97" s="15">
+        <v>0</v>
+      </c>
+      <c r="G97" s="15">
+        <v>0</v>
+      </c>
+      <c r="H97" s="15">
+        <v>0</v>
+      </c>
+      <c r="I97" s="15">
+        <v>0</v>
+      </c>
+      <c r="J97" s="13">
+        <v>0</v>
+      </c>
+      <c r="K97" s="13">
+        <v>1</v>
+      </c>
+      <c r="L97" s="13">
+        <v>0</v>
+      </c>
+      <c r="M97" s="13">
+        <v>0</v>
+      </c>
+      <c r="N97" s="13">
+        <v>0</v>
+      </c>
+      <c r="O97" s="13">
+        <v>0</v>
+      </c>
+      <c r="P97" s="16"/>
       <c r="Q97" s="17" t="str">
         <f>IF(LEN(TRIM(B97))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B97),FIND(" ",TRIM(B97)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B97),FIND(" ",TRIM(B97)&amp;" ")-1)))</f>
-        <v/>
+        <v>서울</v>
       </c>
     </row>
     <row r="98" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A98" s="14"/>
-      <c r="B98" s="14"/>
-      <c r="C98" s="14"/>
-      <c r="D98" s="15"/>
-      <c r="E98" s="15"/>
-      <c r="F98" s="15"/>
-      <c r="G98" s="15"/>
-      <c r="H98" s="15"/>
-      <c r="I98" s="15"/>
-      <c r="J98" s="16"/>
-      <c r="K98" s="16"/>
-      <c r="L98" s="16"/>
-      <c r="M98" s="16"/>
-      <c r="N98" s="16"/>
-      <c r="O98" s="19"/>
-      <c r="P98" s="14"/>
+      <c r="A98" s="21" t="s">
+        <v>413</v>
+      </c>
+      <c r="B98" s="21" t="s">
+        <v>412</v>
+      </c>
+      <c r="C98" s="16" t="s">
+        <v>411</v>
+      </c>
+      <c r="D98" s="15">
+        <v>1</v>
+      </c>
+      <c r="E98" s="15">
+        <v>0</v>
+      </c>
+      <c r="F98" s="15">
+        <v>0</v>
+      </c>
+      <c r="G98" s="15">
+        <v>1</v>
+      </c>
+      <c r="H98" s="15">
+        <v>1</v>
+      </c>
+      <c r="I98" s="15">
+        <v>0</v>
+      </c>
+      <c r="J98" s="13">
+        <v>1</v>
+      </c>
+      <c r="K98" s="13">
+        <v>1</v>
+      </c>
+      <c r="L98" s="13">
+        <v>0</v>
+      </c>
+      <c r="M98" s="13">
+        <v>0</v>
+      </c>
+      <c r="N98" s="13">
+        <v>0</v>
+      </c>
+      <c r="O98" s="13">
+        <v>0</v>
+      </c>
+      <c r="P98" s="16"/>
       <c r="Q98" s="17" t="str">
         <f>IF(LEN(TRIM(B98))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B98),FIND(" ",TRIM(B98)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B98),FIND(" ",TRIM(B98)&amp;" ")-1)))</f>
-        <v/>
+        <v>서울</v>
       </c>
     </row>
     <row r="99" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A99" s="14"/>
-      <c r="B99" s="14"/>
-      <c r="C99" s="14"/>
-      <c r="D99" s="15"/>
-      <c r="E99" s="15"/>
-      <c r="F99" s="15"/>
-      <c r="G99" s="15"/>
-      <c r="H99" s="15"/>
-      <c r="I99" s="15"/>
-      <c r="J99" s="16"/>
-      <c r="K99" s="16"/>
-      <c r="L99" s="16"/>
-      <c r="M99" s="16"/>
-      <c r="N99" s="16"/>
-      <c r="O99" s="19"/>
-      <c r="P99" s="14"/>
+      <c r="A99" s="21" t="s">
+        <v>416</v>
+      </c>
+      <c r="B99" s="21" t="s">
+        <v>415</v>
+      </c>
+      <c r="C99" s="16" t="s">
+        <v>414</v>
+      </c>
+      <c r="D99" s="15">
+        <v>1</v>
+      </c>
+      <c r="E99" s="15">
+        <v>0</v>
+      </c>
+      <c r="F99" s="15">
+        <v>0</v>
+      </c>
+      <c r="G99" s="15">
+        <v>0</v>
+      </c>
+      <c r="H99" s="15">
+        <v>0</v>
+      </c>
+      <c r="I99" s="15">
+        <v>0</v>
+      </c>
+      <c r="J99" s="13">
+        <v>0</v>
+      </c>
+      <c r="K99" s="13">
+        <v>1</v>
+      </c>
+      <c r="L99" s="13">
+        <v>0</v>
+      </c>
+      <c r="M99" s="13">
+        <v>0</v>
+      </c>
+      <c r="N99" s="13">
+        <v>0</v>
+      </c>
+      <c r="O99" s="13">
+        <v>0</v>
+      </c>
+      <c r="P99" s="16"/>
       <c r="Q99" s="17" t="str">
         <f>IF(LEN(TRIM(B99))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B99),FIND(" ",TRIM(B99)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B99),FIND(" ",TRIM(B99)&amp;" ")-1)))</f>
-        <v/>
+        <v>서울</v>
       </c>
     </row>
     <row r="100" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A100" s="14"/>
-      <c r="B100" s="14"/>
-      <c r="C100" s="14"/>
-      <c r="D100" s="15"/>
-      <c r="E100" s="15"/>
-      <c r="F100" s="15"/>
-      <c r="G100" s="15"/>
-      <c r="H100" s="15"/>
-      <c r="I100" s="15"/>
-      <c r="J100" s="16"/>
-      <c r="K100" s="16"/>
-      <c r="L100" s="16"/>
-      <c r="M100" s="16"/>
-      <c r="N100" s="16"/>
-      <c r="O100" s="19"/>
-      <c r="P100" s="14"/>
+      <c r="A100" s="21" t="s">
+        <v>419</v>
+      </c>
+      <c r="B100" s="21" t="s">
+        <v>418</v>
+      </c>
+      <c r="C100" s="16" t="s">
+        <v>417</v>
+      </c>
+      <c r="D100" s="15">
+        <v>1</v>
+      </c>
+      <c r="E100" s="15">
+        <v>0</v>
+      </c>
+      <c r="F100" s="15">
+        <v>0</v>
+      </c>
+      <c r="G100" s="15">
+        <v>1</v>
+      </c>
+      <c r="H100" s="15">
+        <v>0</v>
+      </c>
+      <c r="I100" s="15">
+        <v>0</v>
+      </c>
+      <c r="J100" s="13">
+        <v>1</v>
+      </c>
+      <c r="K100" s="13">
+        <v>1</v>
+      </c>
+      <c r="L100" s="13">
+        <v>1</v>
+      </c>
+      <c r="M100" s="13">
+        <v>0</v>
+      </c>
+      <c r="N100" s="13">
+        <v>0</v>
+      </c>
+      <c r="O100" s="13">
+        <v>0</v>
+      </c>
+      <c r="P100" s="16"/>
       <c r="Q100" s="17" t="str">
         <f>IF(LEN(TRIM(B100))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B100),FIND(" ",TRIM(B100)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B100),FIND(" ",TRIM(B100)&amp;" ")-1)))</f>
-        <v/>
+        <v>서울</v>
       </c>
     </row>
     <row r="101" spans="1:17" ht="25.5" customHeight="1">
-      <c r="A101" s="14"/>
-      <c r="B101" s="14"/>
-      <c r="C101" s="14"/>
-      <c r="D101" s="15"/>
-      <c r="E101" s="15"/>
-      <c r="F101" s="15"/>
-      <c r="G101" s="15"/>
-      <c r="H101" s="15"/>
-      <c r="I101" s="15"/>
-      <c r="J101" s="16"/>
-      <c r="K101" s="16"/>
-      <c r="L101" s="16"/>
-      <c r="M101" s="16"/>
-      <c r="N101" s="16"/>
-      <c r="O101" s="19"/>
-      <c r="P101" s="14"/>
+      <c r="A101" s="21" t="s">
+        <v>422</v>
+      </c>
+      <c r="B101" s="21" t="s">
+        <v>421</v>
+      </c>
+      <c r="C101" s="16" t="s">
+        <v>420</v>
+      </c>
+      <c r="D101" s="15">
+        <v>1</v>
+      </c>
+      <c r="E101" s="15">
+        <v>0</v>
+      </c>
+      <c r="F101" s="15">
+        <v>0</v>
+      </c>
+      <c r="G101" s="15">
+        <v>0</v>
+      </c>
+      <c r="H101" s="15">
+        <v>0</v>
+      </c>
+      <c r="I101" s="15">
+        <v>0</v>
+      </c>
+      <c r="J101" s="13">
+        <v>1</v>
+      </c>
+      <c r="K101" s="13">
+        <v>1</v>
+      </c>
+      <c r="L101" s="13">
+        <v>1</v>
+      </c>
+      <c r="M101" s="13">
+        <v>0</v>
+      </c>
+      <c r="N101" s="13">
+        <v>0</v>
+      </c>
+      <c r="O101" s="13">
+        <v>0</v>
+      </c>
+      <c r="P101" s="16"/>
       <c r="Q101" s="17" t="str">
         <f>IF(LEN(TRIM(B101))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B101),FIND(" ",TRIM(B101)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B101),FIND(" ",TRIM(B101)&amp;" ")-1)))</f>
+        <v>서울</v>
+      </c>
+    </row>
+    <row r="102" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A102" s="22" t="s">
+        <v>426</v>
+      </c>
+      <c r="B102" s="22" t="s">
+        <v>425</v>
+      </c>
+      <c r="C102" s="19" t="s">
+        <v>424</v>
+      </c>
+      <c r="D102" s="15">
+        <v>1</v>
+      </c>
+      <c r="E102" s="15">
+        <v>0</v>
+      </c>
+      <c r="F102" s="15">
+        <v>0</v>
+      </c>
+      <c r="G102" s="15">
+        <v>0</v>
+      </c>
+      <c r="H102" s="15">
+        <v>0</v>
+      </c>
+      <c r="I102" s="15">
+        <v>0</v>
+      </c>
+      <c r="J102" s="13">
+        <v>0</v>
+      </c>
+      <c r="K102" s="13">
+        <v>1</v>
+      </c>
+      <c r="L102" s="13">
+        <v>0</v>
+      </c>
+      <c r="M102" s="13">
+        <v>0</v>
+      </c>
+      <c r="N102" s="13">
+        <v>0</v>
+      </c>
+      <c r="O102" s="13">
+        <v>0</v>
+      </c>
+      <c r="P102" s="19" t="s">
+        <v>423</v>
+      </c>
+      <c r="Q102" s="17" t="str">
+        <f>IF(LEN(TRIM(B102))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B102),FIND(" ",TRIM(B102)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B102),FIND(" ",TRIM(B102)&amp;" ")-1)))</f>
+        <v>서울</v>
+      </c>
+    </row>
+    <row r="103" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A103" s="22" t="s">
+        <v>429</v>
+      </c>
+      <c r="B103" s="22" t="s">
+        <v>428</v>
+      </c>
+      <c r="C103" s="19" t="s">
+        <v>427</v>
+      </c>
+      <c r="D103" s="15">
+        <v>1</v>
+      </c>
+      <c r="E103" s="15">
+        <v>0</v>
+      </c>
+      <c r="F103" s="15">
+        <v>0</v>
+      </c>
+      <c r="G103" s="15">
+        <v>0</v>
+      </c>
+      <c r="H103" s="15">
+        <v>0</v>
+      </c>
+      <c r="I103" s="15">
+        <v>0</v>
+      </c>
+      <c r="J103" s="13">
+        <v>0</v>
+      </c>
+      <c r="K103" s="13">
+        <v>1</v>
+      </c>
+      <c r="L103" s="13">
+        <v>1</v>
+      </c>
+      <c r="M103" s="20">
+        <v>0</v>
+      </c>
+      <c r="N103" s="20">
+        <v>0</v>
+      </c>
+      <c r="O103" s="20">
+        <v>0</v>
+      </c>
+      <c r="P103" s="19"/>
+      <c r="Q103" s="17" t="str">
+        <f>IF(LEN(TRIM(B103))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B103),FIND(" ",TRIM(B103)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B103),FIND(" ",TRIM(B103)&amp;" ")-1)))</f>
+        <v>서울</v>
+      </c>
+    </row>
+    <row r="104" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A104" s="22" t="s">
+        <v>432</v>
+      </c>
+      <c r="B104" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="C104" s="19" t="s">
+        <v>430</v>
+      </c>
+      <c r="D104" s="15">
+        <v>1</v>
+      </c>
+      <c r="E104" s="15">
+        <v>0</v>
+      </c>
+      <c r="F104" s="15">
+        <v>0</v>
+      </c>
+      <c r="G104" s="15">
+        <v>0</v>
+      </c>
+      <c r="H104" s="15">
+        <v>0</v>
+      </c>
+      <c r="I104" s="15">
+        <v>0</v>
+      </c>
+      <c r="J104" s="13">
+        <v>0</v>
+      </c>
+      <c r="K104" s="13">
+        <v>1</v>
+      </c>
+      <c r="L104" s="13">
+        <v>0</v>
+      </c>
+      <c r="M104" s="20">
+        <v>0</v>
+      </c>
+      <c r="N104" s="20">
+        <v>0</v>
+      </c>
+      <c r="O104" s="20">
+        <v>0</v>
+      </c>
+      <c r="P104" s="19" t="s">
+        <v>404</v>
+      </c>
+      <c r="Q104" s="17" t="str">
+        <f>IF(LEN(TRIM(B104))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B104),FIND(" ",TRIM(B104)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B104),FIND(" ",TRIM(B104)&amp;" ")-1)))</f>
+        <v>서울</v>
+      </c>
+    </row>
+    <row r="105" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A105" s="22"/>
+      <c r="B105" s="22"/>
+      <c r="C105" s="19"/>
+      <c r="D105" s="15"/>
+      <c r="E105" s="15"/>
+      <c r="F105" s="15"/>
+      <c r="G105" s="15"/>
+      <c r="H105" s="15"/>
+      <c r="I105" s="15"/>
+      <c r="J105" s="13"/>
+      <c r="K105" s="13"/>
+      <c r="L105" s="13"/>
+      <c r="M105" s="20"/>
+      <c r="N105" s="20"/>
+      <c r="O105" s="20"/>
+      <c r="P105" s="19"/>
+      <c r="Q105" s="17" t="str">
+        <f>IF(LEN(TRIM(B105))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B105),FIND(" ",TRIM(B105)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B105),FIND(" ",TRIM(B105)&amp;" ")-1)))</f>
         <v/>
       </c>
+    </row>
+    <row r="106" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A106" s="22"/>
+      <c r="B106" s="22"/>
+      <c r="C106" s="19"/>
+      <c r="D106" s="15"/>
+      <c r="E106" s="15"/>
+      <c r="F106" s="15"/>
+      <c r="G106" s="15"/>
+      <c r="H106" s="15"/>
+      <c r="I106" s="15"/>
+      <c r="J106" s="13"/>
+      <c r="K106" s="13"/>
+      <c r="L106" s="13"/>
+      <c r="M106" s="20"/>
+      <c r="N106" s="20"/>
+      <c r="O106" s="20"/>
+      <c r="P106" s="19"/>
+      <c r="Q106" s="17" t="str">
+        <f>IF(LEN(TRIM(B106))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B106),FIND(" ",TRIM(B106)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B106),FIND(" ",TRIM(B106)&amp;" ")-1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A107" s="22"/>
+      <c r="B107" s="22"/>
+      <c r="C107" s="19"/>
+      <c r="D107" s="15"/>
+      <c r="E107" s="15"/>
+      <c r="F107" s="15"/>
+      <c r="G107" s="15"/>
+      <c r="H107" s="15"/>
+      <c r="I107" s="15"/>
+      <c r="J107" s="13"/>
+      <c r="K107" s="13"/>
+      <c r="L107" s="13"/>
+      <c r="M107" s="20"/>
+      <c r="N107" s="20"/>
+      <c r="O107" s="20"/>
+      <c r="P107" s="19"/>
+      <c r="Q107" s="17" t="str">
+        <f>IF(LEN(TRIM(B107))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B107),FIND(" ",TRIM(B107)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B107),FIND(" ",TRIM(B107)&amp;" ")-1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A108" s="22"/>
+      <c r="B108" s="22"/>
+      <c r="C108" s="19"/>
+      <c r="D108" s="15"/>
+      <c r="E108" s="15"/>
+      <c r="F108" s="15"/>
+      <c r="G108" s="15"/>
+      <c r="H108" s="15"/>
+      <c r="I108" s="15"/>
+      <c r="J108" s="13"/>
+      <c r="K108" s="13"/>
+      <c r="L108" s="13"/>
+      <c r="M108" s="20"/>
+      <c r="N108" s="20"/>
+      <c r="O108" s="20"/>
+      <c r="P108" s="19"/>
+      <c r="Q108" s="17" t="str">
+        <f>IF(LEN(TRIM(B108))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B108),FIND(" ",TRIM(B108)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B108),FIND(" ",TRIM(B108)&amp;" ")-1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="109" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A109" s="22"/>
+      <c r="B109" s="22"/>
+      <c r="C109" s="19"/>
+      <c r="D109" s="15"/>
+      <c r="E109" s="15"/>
+      <c r="F109" s="15"/>
+      <c r="G109" s="15"/>
+      <c r="H109" s="15"/>
+      <c r="I109" s="15"/>
+      <c r="J109" s="13"/>
+      <c r="K109" s="13"/>
+      <c r="L109" s="13"/>
+      <c r="M109" s="20"/>
+      <c r="N109" s="20"/>
+      <c r="O109" s="20"/>
+      <c r="P109" s="19"/>
+      <c r="Q109" s="17" t="str">
+        <f>IF(LEN(TRIM(B109))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B109),FIND(" ",TRIM(B109)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B109),FIND(" ",TRIM(B109)&amp;" ")-1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A110" s="22"/>
+      <c r="B110" s="22"/>
+      <c r="C110" s="19"/>
+      <c r="D110" s="15"/>
+      <c r="E110" s="15"/>
+      <c r="F110" s="15"/>
+      <c r="G110" s="15"/>
+      <c r="H110" s="15"/>
+      <c r="I110" s="15"/>
+      <c r="J110" s="13"/>
+      <c r="K110" s="13"/>
+      <c r="L110" s="13"/>
+      <c r="M110" s="20"/>
+      <c r="N110" s="20"/>
+      <c r="O110" s="20"/>
+      <c r="P110" s="19"/>
+      <c r="Q110" s="17" t="str">
+        <f>IF(LEN(TRIM(B110))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B110),FIND(" ",TRIM(B110)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B110),FIND(" ",TRIM(B110)&amp;" ")-1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A111" s="22"/>
+      <c r="B111" s="22"/>
+      <c r="C111" s="19"/>
+      <c r="D111" s="15"/>
+      <c r="E111" s="15"/>
+      <c r="F111" s="15"/>
+      <c r="G111" s="15"/>
+      <c r="H111" s="15"/>
+      <c r="I111" s="15"/>
+      <c r="J111" s="13"/>
+      <c r="K111" s="13"/>
+      <c r="L111" s="13"/>
+      <c r="M111" s="20"/>
+      <c r="N111" s="20"/>
+      <c r="O111" s="20"/>
+      <c r="P111" s="19"/>
+      <c r="Q111" s="17" t="str">
+        <f>IF(LEN(TRIM(B111))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B111),FIND(" ",TRIM(B111)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B111),FIND(" ",TRIM(B111)&amp;" ")-1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A112" s="22"/>
+      <c r="B112" s="22"/>
+      <c r="C112" s="19"/>
+      <c r="D112" s="15"/>
+      <c r="E112" s="15"/>
+      <c r="F112" s="15"/>
+      <c r="G112" s="15"/>
+      <c r="H112" s="15"/>
+      <c r="I112" s="15"/>
+      <c r="J112" s="13"/>
+      <c r="K112" s="13"/>
+      <c r="L112" s="13"/>
+      <c r="M112" s="20"/>
+      <c r="N112" s="20"/>
+      <c r="O112" s="20"/>
+      <c r="P112" s="19"/>
+      <c r="Q112" s="17" t="str">
+        <f>IF(LEN(TRIM(B112))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B112),FIND(" ",TRIM(B112)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B112),FIND(" ",TRIM(B112)&amp;" ")-1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A113" s="22"/>
+      <c r="B113" s="22"/>
+      <c r="C113" s="19"/>
+      <c r="D113" s="15"/>
+      <c r="E113" s="15"/>
+      <c r="F113" s="15"/>
+      <c r="G113" s="15"/>
+      <c r="H113" s="15"/>
+      <c r="I113" s="15"/>
+      <c r="J113" s="13"/>
+      <c r="K113" s="13"/>
+      <c r="L113" s="13"/>
+      <c r="M113" s="20"/>
+      <c r="N113" s="20"/>
+      <c r="O113" s="20"/>
+      <c r="P113" s="19"/>
+      <c r="Q113" s="17" t="str">
+        <f>IF(LEN(TRIM(B113))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B113),FIND(" ",TRIM(B113)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B113),FIND(" ",TRIM(B113)&amp;" ")-1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A114" s="22"/>
+      <c r="B114" s="22"/>
+      <c r="C114" s="19"/>
+      <c r="D114" s="15"/>
+      <c r="E114" s="15"/>
+      <c r="F114" s="15"/>
+      <c r="G114" s="15"/>
+      <c r="H114" s="15"/>
+      <c r="I114" s="15"/>
+      <c r="J114" s="13"/>
+      <c r="K114" s="13"/>
+      <c r="L114" s="13"/>
+      <c r="M114" s="20"/>
+      <c r="N114" s="20"/>
+      <c r="O114" s="20"/>
+      <c r="P114" s="19"/>
+      <c r="Q114" s="17" t="str">
+        <f>IF(LEN(TRIM(B114))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B114),FIND(" ",TRIM(B114)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B114),FIND(" ",TRIM(B114)&amp;" ")-1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A115" s="22"/>
+      <c r="B115" s="22"/>
+      <c r="C115" s="19"/>
+      <c r="D115" s="15"/>
+      <c r="E115" s="15"/>
+      <c r="F115" s="15"/>
+      <c r="G115" s="15"/>
+      <c r="H115" s="15"/>
+      <c r="I115" s="15"/>
+      <c r="J115" s="13"/>
+      <c r="K115" s="13"/>
+      <c r="L115" s="13"/>
+      <c r="M115" s="20"/>
+      <c r="N115" s="20"/>
+      <c r="O115" s="20"/>
+      <c r="P115" s="19"/>
+      <c r="Q115" s="17" t="str">
+        <f>IF(LEN(TRIM(B115))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B115),FIND(" ",TRIM(B115)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B115),FIND(" ",TRIM(B115)&amp;" ")-1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A116" s="22"/>
+      <c r="B116" s="22"/>
+      <c r="C116" s="19"/>
+      <c r="D116" s="15"/>
+      <c r="E116" s="15"/>
+      <c r="F116" s="15"/>
+      <c r="G116" s="15"/>
+      <c r="H116" s="15"/>
+      <c r="I116" s="15"/>
+      <c r="J116" s="13"/>
+      <c r="K116" s="13"/>
+      <c r="L116" s="13"/>
+      <c r="M116" s="20"/>
+      <c r="N116" s="20"/>
+      <c r="O116" s="20"/>
+      <c r="P116" s="19"/>
+      <c r="Q116" s="17" t="str">
+        <f>IF(LEN(TRIM(B116))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B116),FIND(" ",TRIM(B116)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B116),FIND(" ",TRIM(B116)&amp;" ")-1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A117" s="22"/>
+      <c r="B117" s="22"/>
+      <c r="C117" s="19"/>
+      <c r="D117" s="15"/>
+      <c r="E117" s="15"/>
+      <c r="F117" s="15"/>
+      <c r="G117" s="15"/>
+      <c r="H117" s="15"/>
+      <c r="I117" s="15"/>
+      <c r="J117" s="13"/>
+      <c r="K117" s="13"/>
+      <c r="L117" s="13"/>
+      <c r="M117" s="20"/>
+      <c r="N117" s="20"/>
+      <c r="O117" s="20"/>
+      <c r="P117" s="19"/>
+      <c r="Q117" s="17" t="str">
+        <f>IF(LEN(TRIM(B117))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B117),FIND(" ",TRIM(B117)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B117),FIND(" ",TRIM(B117)&amp;" ")-1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A118" s="22"/>
+      <c r="B118" s="22"/>
+      <c r="C118" s="19"/>
+      <c r="D118" s="15"/>
+      <c r="E118" s="15"/>
+      <c r="F118" s="15"/>
+      <c r="G118" s="15"/>
+      <c r="H118" s="15"/>
+      <c r="I118" s="15"/>
+      <c r="J118" s="13"/>
+      <c r="K118" s="13"/>
+      <c r="L118" s="13"/>
+      <c r="M118" s="20"/>
+      <c r="N118" s="20"/>
+      <c r="O118" s="20"/>
+      <c r="P118" s="19"/>
+      <c r="Q118" s="17" t="str">
+        <f>IF(LEN(TRIM(B118))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B118),FIND(" ",TRIM(B118)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B118),FIND(" ",TRIM(B118)&amp;" ")-1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="119" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A119" s="22"/>
+      <c r="B119" s="22"/>
+      <c r="C119" s="19"/>
+      <c r="D119" s="15"/>
+      <c r="E119" s="15"/>
+      <c r="F119" s="15"/>
+      <c r="G119" s="15"/>
+      <c r="H119" s="15"/>
+      <c r="I119" s="15"/>
+      <c r="J119" s="13"/>
+      <c r="K119" s="13"/>
+      <c r="L119" s="13"/>
+      <c r="M119" s="20"/>
+      <c r="N119" s="20"/>
+      <c r="O119" s="20"/>
+      <c r="P119" s="19"/>
+      <c r="Q119" s="17" t="str">
+        <f>IF(LEN(TRIM(B119))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B119),FIND(" ",TRIM(B119)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B119),FIND(" ",TRIM(B119)&amp;" ")-1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="120" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A120" s="22"/>
+      <c r="B120" s="22"/>
+      <c r="C120" s="19"/>
+      <c r="D120" s="15"/>
+      <c r="E120" s="15"/>
+      <c r="F120" s="15"/>
+      <c r="G120" s="15"/>
+      <c r="H120" s="15"/>
+      <c r="I120" s="15"/>
+      <c r="J120" s="13"/>
+      <c r="K120" s="13"/>
+      <c r="L120" s="13"/>
+      <c r="M120" s="20"/>
+      <c r="N120" s="20"/>
+      <c r="O120" s="20"/>
+      <c r="P120" s="19"/>
+      <c r="Q120" s="17" t="str">
+        <f>IF(LEN(TRIM(B120))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B120),FIND(" ",TRIM(B120)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B120),FIND(" ",TRIM(B120)&amp;" ")-1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="121" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A121" s="22"/>
+      <c r="B121" s="22"/>
+      <c r="C121" s="19"/>
+      <c r="D121" s="15"/>
+      <c r="E121" s="15"/>
+      <c r="F121" s="15"/>
+      <c r="G121" s="15"/>
+      <c r="H121" s="15"/>
+      <c r="I121" s="15"/>
+      <c r="J121" s="13"/>
+      <c r="K121" s="13"/>
+      <c r="L121" s="13"/>
+      <c r="M121" s="20"/>
+      <c r="N121" s="20"/>
+      <c r="O121" s="20"/>
+      <c r="P121" s="19"/>
+      <c r="Q121" s="17" t="str">
+        <f>IF(LEN(TRIM(B121))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B121),FIND(" ",TRIM(B121)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B121),FIND(" ",TRIM(B121)&amp;" ")-1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="122" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A122" s="22"/>
+      <c r="B122" s="22"/>
+      <c r="C122" s="19"/>
+      <c r="D122" s="15"/>
+      <c r="E122" s="15"/>
+      <c r="F122" s="15"/>
+      <c r="G122" s="15"/>
+      <c r="H122" s="15"/>
+      <c r="I122" s="15"/>
+      <c r="J122" s="13"/>
+      <c r="K122" s="13"/>
+      <c r="L122" s="13"/>
+      <c r="M122" s="20"/>
+      <c r="N122" s="20"/>
+      <c r="O122" s="20"/>
+      <c r="P122" s="19"/>
+      <c r="Q122" s="17" t="str">
+        <f>IF(LEN(TRIM(B122))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B122),FIND(" ",TRIM(B122)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B122),FIND(" ",TRIM(B122)&amp;" ")-1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="123" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A123" s="22"/>
+      <c r="B123" s="22"/>
+      <c r="C123" s="19"/>
+      <c r="D123" s="15"/>
+      <c r="E123" s="15"/>
+      <c r="F123" s="15"/>
+      <c r="G123" s="15"/>
+      <c r="H123" s="15"/>
+      <c r="I123" s="15"/>
+      <c r="J123" s="13"/>
+      <c r="K123" s="13"/>
+      <c r="L123" s="13"/>
+      <c r="M123" s="20"/>
+      <c r="N123" s="20"/>
+      <c r="O123" s="20"/>
+      <c r="P123" s="19"/>
+      <c r="Q123" s="17" t="str">
+        <f>IF(LEN(TRIM(B123))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B123),FIND(" ",TRIM(B123)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B123),FIND(" ",TRIM(B123)&amp;" ")-1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="124" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A124" s="22"/>
+      <c r="B124" s="22"/>
+      <c r="C124" s="19"/>
+      <c r="D124" s="15"/>
+      <c r="E124" s="15"/>
+      <c r="F124" s="15"/>
+      <c r="G124" s="15"/>
+      <c r="H124" s="15"/>
+      <c r="I124" s="15"/>
+      <c r="J124" s="13"/>
+      <c r="K124" s="13"/>
+      <c r="L124" s="13"/>
+      <c r="M124" s="20"/>
+      <c r="N124" s="20"/>
+      <c r="O124" s="20"/>
+      <c r="P124" s="19"/>
+      <c r="Q124" s="17" t="str">
+        <f>IF(LEN(TRIM(B124))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B124),FIND(" ",TRIM(B124)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B124),FIND(" ",TRIM(B124)&amp;" ")-1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="125" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A125" s="22"/>
+      <c r="B125" s="22"/>
+      <c r="C125" s="19"/>
+      <c r="D125" s="15"/>
+      <c r="E125" s="15"/>
+      <c r="F125" s="15"/>
+      <c r="G125" s="15"/>
+      <c r="H125" s="15"/>
+      <c r="I125" s="15"/>
+      <c r="J125" s="13"/>
+      <c r="K125" s="13"/>
+      <c r="L125" s="13"/>
+      <c r="M125" s="20"/>
+      <c r="N125" s="20"/>
+      <c r="O125" s="20"/>
+      <c r="P125" s="19"/>
+      <c r="Q125" s="17" t="str">
+        <f>IF(LEN(TRIM(B125))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B125),FIND(" ",TRIM(B125)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B125),FIND(" ",TRIM(B125)&amp;" ")-1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="126" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A126" s="22"/>
+      <c r="B126" s="22"/>
+      <c r="C126" s="19"/>
+      <c r="D126" s="15"/>
+      <c r="E126" s="15"/>
+      <c r="F126" s="15"/>
+      <c r="G126" s="15"/>
+      <c r="H126" s="15"/>
+      <c r="I126" s="15"/>
+      <c r="J126" s="13"/>
+      <c r="K126" s="13"/>
+      <c r="L126" s="13"/>
+      <c r="M126" s="20"/>
+      <c r="N126" s="20"/>
+      <c r="O126" s="20"/>
+      <c r="P126" s="19"/>
+      <c r="Q126" s="17" t="str">
+        <f>IF(LEN(TRIM(B126))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B126),FIND(" ",TRIM(B126)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B126),FIND(" ",TRIM(B126)&amp;" ")-1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="127" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A127" s="22"/>
+      <c r="B127" s="22"/>
+      <c r="C127" s="19"/>
+      <c r="D127" s="15"/>
+      <c r="E127" s="15"/>
+      <c r="F127" s="15"/>
+      <c r="G127" s="15"/>
+      <c r="H127" s="15"/>
+      <c r="I127" s="15"/>
+      <c r="J127" s="13"/>
+      <c r="K127" s="13"/>
+      <c r="L127" s="13"/>
+      <c r="M127" s="20"/>
+      <c r="N127" s="20"/>
+      <c r="O127" s="20"/>
+      <c r="P127" s="19"/>
+      <c r="Q127" s="17" t="str">
+        <f>IF(LEN(TRIM(B127))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B127),FIND(" ",TRIM(B127)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B127),FIND(" ",TRIM(B127)&amp;" ")-1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="128" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A128" s="22"/>
+      <c r="B128" s="22"/>
+      <c r="C128" s="19"/>
+      <c r="D128" s="15"/>
+      <c r="E128" s="15"/>
+      <c r="F128" s="15"/>
+      <c r="G128" s="15"/>
+      <c r="H128" s="15"/>
+      <c r="I128" s="15"/>
+      <c r="J128" s="13"/>
+      <c r="K128" s="13"/>
+      <c r="L128" s="13"/>
+      <c r="M128" s="20"/>
+      <c r="N128" s="20"/>
+      <c r="O128" s="20"/>
+      <c r="P128" s="19"/>
+      <c r="Q128" s="17" t="str">
+        <f>IF(LEN(TRIM(B128))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B128),FIND(" ",TRIM(B128)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B128),FIND(" ",TRIM(B128)&amp;" ")-1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="129" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A129" s="22"/>
+      <c r="B129" s="22"/>
+      <c r="C129" s="19"/>
+      <c r="D129" s="15"/>
+      <c r="E129" s="15"/>
+      <c r="F129" s="15"/>
+      <c r="G129" s="15"/>
+      <c r="H129" s="15"/>
+      <c r="I129" s="15"/>
+      <c r="J129" s="13"/>
+      <c r="K129" s="13"/>
+      <c r="L129" s="13"/>
+      <c r="M129" s="20"/>
+      <c r="N129" s="20"/>
+      <c r="O129" s="20"/>
+      <c r="P129" s="19"/>
+      <c r="Q129" s="17" t="str">
+        <f>IF(LEN(TRIM(B129))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B129),FIND(" ",TRIM(B129)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B129),FIND(" ",TRIM(B129)&amp;" ")-1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="130" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A130" s="22"/>
+      <c r="B130" s="22"/>
+      <c r="C130" s="19"/>
+      <c r="D130" s="15"/>
+      <c r="E130" s="15"/>
+      <c r="F130" s="15"/>
+      <c r="G130" s="15"/>
+      <c r="H130" s="15"/>
+      <c r="I130" s="15"/>
+      <c r="J130" s="13"/>
+      <c r="K130" s="13"/>
+      <c r="L130" s="13"/>
+      <c r="M130" s="20"/>
+      <c r="N130" s="20"/>
+      <c r="O130" s="20"/>
+      <c r="P130" s="19"/>
+      <c r="Q130" s="17" t="str">
+        <f>IF(LEN(TRIM(B130))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B130),FIND(" ",TRIM(B130)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B130),FIND(" ",TRIM(B130)&amp;" ")-1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="131" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A131" s="22"/>
+      <c r="B131" s="22"/>
+      <c r="C131" s="19"/>
+      <c r="D131" s="15"/>
+      <c r="E131" s="15"/>
+      <c r="F131" s="15"/>
+      <c r="G131" s="15"/>
+      <c r="H131" s="15"/>
+      <c r="I131" s="15"/>
+      <c r="J131" s="13"/>
+      <c r="K131" s="13"/>
+      <c r="L131" s="13"/>
+      <c r="M131" s="20"/>
+      <c r="N131" s="20"/>
+      <c r="O131" s="20"/>
+      <c r="P131" s="19"/>
+      <c r="Q131" s="17" t="str">
+        <f>IF(LEN(TRIM(B131))=0,"",IFERROR(VLOOKUP(LEFT(TRIM(B131),FIND(" ",TRIM(B131)&amp;" ")-1),작성안내!$D$4:$E$23,2,FALSE),LEFT(TRIM(B131),FIND(" ",TRIM(B131)&amp;" ")-1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="132" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A132" s="22"/>
+      <c r="B132" s="22"/>
+      <c r="C132" s="19"/>
+      <c r="D132" s="15"/>
+      <c r="E132" s="15"/>
+      <c r="F132" s="15"/>
+      <c r="G132" s="15"/>
+      <c r="H132" s="15"/>
+      <c r="I132" s="15"/>
+      <c r="J132" s="13"/>
+      <c r="K132" s="13"/>
+      <c r="L132" s="13"/>
+      <c r="M132" s="20"/>
+      <c r="N132" s="20"/>
+      <c r="O132" s="20"/>
+      <c r="P132" s="19"/>
+      <c r="Q132" s="19"/>
+    </row>
+    <row r="133" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A133" s="22"/>
+      <c r="B133" s="22"/>
+      <c r="C133" s="19"/>
+      <c r="D133" s="15"/>
+      <c r="E133" s="15"/>
+      <c r="F133" s="15"/>
+      <c r="G133" s="15"/>
+      <c r="H133" s="15"/>
+      <c r="I133" s="15"/>
+      <c r="J133" s="13"/>
+      <c r="K133" s="13"/>
+      <c r="L133" s="13"/>
+      <c r="M133" s="20"/>
+      <c r="N133" s="20"/>
+      <c r="O133" s="20"/>
+      <c r="P133" s="19"/>
+      <c r="Q133" s="19"/>
+    </row>
+    <row r="134" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A134" s="22"/>
+      <c r="B134" s="22"/>
+      <c r="C134" s="19"/>
+      <c r="D134" s="15"/>
+      <c r="E134" s="15"/>
+      <c r="F134" s="15"/>
+      <c r="G134" s="15"/>
+      <c r="H134" s="15"/>
+      <c r="I134" s="15"/>
+      <c r="J134" s="13"/>
+      <c r="K134" s="13"/>
+      <c r="L134" s="13"/>
+      <c r="M134" s="20"/>
+      <c r="N134" s="20"/>
+      <c r="O134" s="20"/>
+      <c r="P134" s="19"/>
+      <c r="Q134" s="19"/>
+    </row>
+    <row r="135" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A135" s="22"/>
+      <c r="B135" s="22"/>
+      <c r="C135" s="19"/>
+      <c r="D135" s="15"/>
+      <c r="E135" s="15"/>
+      <c r="F135" s="15"/>
+      <c r="G135" s="15"/>
+      <c r="H135" s="15"/>
+      <c r="I135" s="15"/>
+      <c r="J135" s="13"/>
+      <c r="K135" s="13"/>
+      <c r="L135" s="13"/>
+      <c r="M135" s="20"/>
+      <c r="N135" s="20"/>
+      <c r="O135" s="20"/>
+      <c r="P135" s="19"/>
+      <c r="Q135" s="19"/>
+    </row>
+    <row r="136" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A136" s="22"/>
+      <c r="B136" s="22"/>
+      <c r="C136" s="19"/>
+      <c r="D136" s="15"/>
+      <c r="E136" s="15"/>
+      <c r="F136" s="15"/>
+      <c r="G136" s="15"/>
+      <c r="H136" s="15"/>
+      <c r="I136" s="15"/>
+      <c r="J136" s="13"/>
+      <c r="K136" s="13"/>
+      <c r="L136" s="13"/>
+      <c r="M136" s="20"/>
+      <c r="N136" s="20"/>
+      <c r="O136" s="20"/>
+      <c r="P136" s="19"/>
+      <c r="Q136" s="19"/>
+    </row>
+    <row r="137" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A137" s="22"/>
+      <c r="B137" s="22"/>
+      <c r="C137" s="19"/>
+      <c r="D137" s="15"/>
+      <c r="E137" s="15"/>
+      <c r="F137" s="15"/>
+      <c r="G137" s="15"/>
+      <c r="H137" s="15"/>
+      <c r="I137" s="15"/>
+      <c r="J137" s="13"/>
+      <c r="K137" s="13"/>
+      <c r="L137" s="13"/>
+      <c r="M137" s="20"/>
+      <c r="N137" s="20"/>
+      <c r="O137" s="20"/>
+      <c r="P137" s="19"/>
+      <c r="Q137" s="19"/>
+    </row>
+    <row r="138" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A138" s="22"/>
+      <c r="B138" s="22"/>
+      <c r="C138" s="19"/>
+      <c r="D138" s="15"/>
+      <c r="E138" s="15"/>
+      <c r="F138" s="15"/>
+      <c r="G138" s="15"/>
+      <c r="H138" s="15"/>
+      <c r="I138" s="15"/>
+      <c r="J138" s="13"/>
+      <c r="K138" s="13"/>
+      <c r="L138" s="13"/>
+      <c r="M138" s="20"/>
+      <c r="N138" s="20"/>
+      <c r="O138" s="20"/>
+      <c r="P138" s="19"/>
+      <c r="Q138" s="19"/>
+    </row>
+    <row r="139" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A139" s="22"/>
+      <c r="B139" s="22"/>
+      <c r="C139" s="19"/>
+      <c r="D139" s="15"/>
+      <c r="E139" s="15"/>
+      <c r="F139" s="15"/>
+      <c r="G139" s="15"/>
+      <c r="H139" s="15"/>
+      <c r="I139" s="15"/>
+      <c r="J139" s="13"/>
+      <c r="K139" s="13"/>
+      <c r="L139" s="13"/>
+      <c r="M139" s="20"/>
+      <c r="N139" s="20"/>
+      <c r="O139" s="20"/>
+      <c r="P139" s="19"/>
+      <c r="Q139" s="19"/>
+    </row>
+    <row r="140" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A140" s="22"/>
+      <c r="B140" s="22"/>
+      <c r="C140" s="19"/>
+      <c r="D140" s="15"/>
+      <c r="E140" s="15"/>
+      <c r="F140" s="15"/>
+      <c r="G140" s="15"/>
+      <c r="H140" s="15"/>
+      <c r="I140" s="15"/>
+      <c r="J140" s="13"/>
+      <c r="K140" s="13"/>
+      <c r="L140" s="13"/>
+      <c r="M140" s="20"/>
+      <c r="N140" s="20"/>
+      <c r="O140" s="20"/>
+      <c r="P140" s="19"/>
+      <c r="Q140" s="19"/>
+    </row>
+    <row r="141" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A141" s="22"/>
+      <c r="B141" s="22"/>
+      <c r="C141" s="19"/>
+      <c r="D141" s="15"/>
+      <c r="E141" s="15"/>
+      <c r="F141" s="15"/>
+      <c r="G141" s="15"/>
+      <c r="H141" s="15"/>
+      <c r="I141" s="15"/>
+      <c r="J141" s="13"/>
+      <c r="K141" s="13"/>
+      <c r="L141" s="13"/>
+      <c r="M141" s="20"/>
+      <c r="N141" s="20"/>
+      <c r="O141" s="20"/>
+      <c r="P141" s="19"/>
+      <c r="Q141" s="19"/>
+    </row>
+    <row r="142" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A142" s="22"/>
+      <c r="B142" s="22"/>
+      <c r="C142" s="19"/>
+      <c r="D142" s="15"/>
+      <c r="E142" s="15"/>
+      <c r="F142" s="15"/>
+      <c r="G142" s="15"/>
+      <c r="H142" s="15"/>
+      <c r="I142" s="15"/>
+      <c r="J142" s="13"/>
+      <c r="K142" s="13"/>
+      <c r="L142" s="13"/>
+      <c r="M142" s="20"/>
+      <c r="N142" s="20"/>
+      <c r="O142" s="20"/>
+      <c r="P142" s="19"/>
+      <c r="Q142" s="19"/>
+    </row>
+    <row r="143" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A143" s="22"/>
+      <c r="B143" s="22"/>
+      <c r="C143" s="19"/>
+      <c r="D143" s="15"/>
+      <c r="E143" s="15"/>
+      <c r="F143" s="15"/>
+      <c r="G143" s="15"/>
+      <c r="H143" s="15"/>
+      <c r="I143" s="15"/>
+      <c r="J143" s="13"/>
+      <c r="K143" s="13"/>
+      <c r="L143" s="13"/>
+      <c r="M143" s="20"/>
+      <c r="N143" s="20"/>
+      <c r="O143" s="20"/>
+      <c r="P143" s="19"/>
+      <c r="Q143" s="19"/>
+    </row>
+    <row r="144" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A144" s="22"/>
+      <c r="B144" s="22"/>
+      <c r="C144" s="19"/>
+      <c r="D144" s="15"/>
+      <c r="E144" s="15"/>
+      <c r="F144" s="15"/>
+      <c r="G144" s="15"/>
+      <c r="H144" s="15"/>
+      <c r="I144" s="15"/>
+      <c r="J144" s="13"/>
+      <c r="K144" s="13"/>
+      <c r="L144" s="13"/>
+      <c r="M144" s="20"/>
+      <c r="N144" s="20"/>
+      <c r="O144" s="20"/>
+      <c r="P144" s="19"/>
+      <c r="Q144" s="19"/>
+    </row>
+    <row r="145" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A145" s="22"/>
+      <c r="B145" s="22"/>
+      <c r="C145" s="19"/>
+      <c r="D145" s="15"/>
+      <c r="E145" s="15"/>
+      <c r="F145" s="15"/>
+      <c r="G145" s="15"/>
+      <c r="H145" s="15"/>
+      <c r="I145" s="15"/>
+      <c r="J145" s="13"/>
+      <c r="K145" s="13"/>
+      <c r="L145" s="13"/>
+      <c r="M145" s="20"/>
+      <c r="N145" s="20"/>
+      <c r="O145" s="20"/>
+      <c r="P145" s="19"/>
+      <c r="Q145" s="19"/>
+    </row>
+    <row r="146" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A146" s="22"/>
+      <c r="B146" s="22"/>
+      <c r="C146" s="19"/>
+      <c r="D146" s="15"/>
+      <c r="E146" s="15"/>
+      <c r="F146" s="15"/>
+      <c r="G146" s="15"/>
+      <c r="H146" s="15"/>
+      <c r="I146" s="15"/>
+      <c r="J146" s="13"/>
+      <c r="K146" s="13"/>
+      <c r="L146" s="13"/>
+      <c r="M146" s="20"/>
+      <c r="N146" s="20"/>
+      <c r="O146" s="20"/>
+      <c r="P146" s="19"/>
+      <c r="Q146" s="19"/>
+    </row>
+    <row r="147" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A147" s="22"/>
+      <c r="B147" s="22"/>
+      <c r="C147" s="19"/>
+      <c r="D147" s="15"/>
+      <c r="E147" s="15"/>
+      <c r="F147" s="15"/>
+      <c r="G147" s="15"/>
+      <c r="H147" s="15"/>
+      <c r="I147" s="15"/>
+      <c r="J147" s="13"/>
+      <c r="K147" s="13"/>
+      <c r="L147" s="13"/>
+      <c r="M147" s="20"/>
+      <c r="N147" s="20"/>
+      <c r="O147" s="20"/>
+      <c r="P147" s="19"/>
+      <c r="Q147" s="19"/>
+    </row>
+    <row r="148" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A148" s="22"/>
+      <c r="B148" s="22"/>
+      <c r="C148" s="19"/>
+      <c r="D148" s="15"/>
+      <c r="E148" s="15"/>
+      <c r="F148" s="15"/>
+      <c r="G148" s="15"/>
+      <c r="H148" s="15"/>
+      <c r="I148" s="15"/>
+      <c r="J148" s="13"/>
+      <c r="K148" s="13"/>
+      <c r="L148" s="13"/>
+      <c r="M148" s="20"/>
+      <c r="N148" s="20"/>
+      <c r="O148" s="20"/>
+      <c r="P148" s="19"/>
+      <c r="Q148" s="19"/>
+    </row>
+    <row r="149" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A149" s="22"/>
+      <c r="B149" s="22"/>
+      <c r="C149" s="19"/>
+      <c r="D149" s="15"/>
+      <c r="E149" s="15"/>
+      <c r="F149" s="15"/>
+      <c r="G149" s="15"/>
+      <c r="H149" s="15"/>
+      <c r="I149" s="15"/>
+      <c r="J149" s="13"/>
+      <c r="K149" s="13"/>
+      <c r="L149" s="13"/>
+      <c r="M149" s="20"/>
+      <c r="N149" s="20"/>
+      <c r="O149" s="20"/>
+      <c r="P149" s="19"/>
+      <c r="Q149" s="19"/>
+    </row>
+    <row r="150" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A150" s="22"/>
+      <c r="B150" s="22"/>
+      <c r="C150" s="19"/>
+      <c r="D150" s="15"/>
+      <c r="E150" s="15"/>
+      <c r="F150" s="15"/>
+      <c r="G150" s="15"/>
+      <c r="H150" s="15"/>
+      <c r="I150" s="15"/>
+      <c r="J150" s="13"/>
+      <c r="K150" s="13"/>
+      <c r="L150" s="13"/>
+      <c r="M150" s="20"/>
+      <c r="N150" s="20"/>
+      <c r="O150" s="20"/>
+      <c r="P150" s="19"/>
+      <c r="Q150" s="19"/>
+    </row>
+    <row r="151" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A151" s="22"/>
+      <c r="B151" s="22"/>
+      <c r="C151" s="19"/>
+      <c r="D151" s="15"/>
+      <c r="E151" s="15"/>
+      <c r="F151" s="15"/>
+      <c r="G151" s="15"/>
+      <c r="H151" s="15"/>
+      <c r="I151" s="15"/>
+      <c r="J151" s="13"/>
+      <c r="K151" s="13"/>
+      <c r="L151" s="13"/>
+      <c r="M151" s="20"/>
+      <c r="N151" s="20"/>
+      <c r="O151" s="20"/>
+      <c r="P151" s="19"/>
+      <c r="Q151" s="19"/>
+    </row>
+    <row r="152" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A152" s="22"/>
+      <c r="B152" s="22"/>
+      <c r="C152" s="19"/>
+      <c r="D152" s="15"/>
+      <c r="E152" s="15"/>
+      <c r="F152" s="15"/>
+      <c r="G152" s="15"/>
+      <c r="H152" s="15"/>
+      <c r="I152" s="15"/>
+      <c r="J152" s="13"/>
+      <c r="K152" s="13"/>
+      <c r="L152" s="13"/>
+      <c r="M152" s="20"/>
+      <c r="N152" s="20"/>
+      <c r="O152" s="20"/>
+      <c r="P152" s="19"/>
+      <c r="Q152" s="19"/>
+    </row>
+    <row r="153" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A153" s="22"/>
+      <c r="B153" s="22"/>
+      <c r="C153" s="19"/>
+      <c r="D153" s="15"/>
+      <c r="E153" s="15"/>
+      <c r="F153" s="15"/>
+      <c r="G153" s="15"/>
+      <c r="H153" s="15"/>
+      <c r="I153" s="15"/>
+      <c r="J153" s="13"/>
+      <c r="K153" s="13"/>
+      <c r="L153" s="13"/>
+      <c r="M153" s="20"/>
+      <c r="N153" s="20"/>
+      <c r="O153" s="20"/>
+      <c r="P153" s="19"/>
+      <c r="Q153" s="19"/>
+    </row>
+    <row r="154" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A154" s="22"/>
+      <c r="B154" s="22"/>
+      <c r="C154" s="19"/>
+      <c r="D154" s="15"/>
+      <c r="E154" s="15"/>
+      <c r="F154" s="15"/>
+      <c r="G154" s="15"/>
+      <c r="H154" s="15"/>
+      <c r="I154" s="15"/>
+      <c r="J154" s="13"/>
+      <c r="K154" s="13"/>
+      <c r="L154" s="13"/>
+      <c r="M154" s="20"/>
+      <c r="N154" s="20"/>
+      <c r="O154" s="20"/>
+      <c r="P154" s="19"/>
+      <c r="Q154" s="19"/>
+    </row>
+    <row r="155" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A155" s="22"/>
+      <c r="B155" s="22"/>
+      <c r="C155" s="19"/>
+      <c r="D155" s="15"/>
+      <c r="E155" s="15"/>
+      <c r="F155" s="15"/>
+      <c r="G155" s="15"/>
+      <c r="H155" s="15"/>
+      <c r="I155" s="15"/>
+      <c r="J155" s="13"/>
+      <c r="K155" s="13"/>
+      <c r="L155" s="13"/>
+      <c r="M155" s="20"/>
+      <c r="N155" s="20"/>
+      <c r="O155" s="20"/>
+      <c r="P155" s="19"/>
+      <c r="Q155" s="19"/>
+    </row>
+    <row r="156" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A156" s="22"/>
+      <c r="B156" s="22"/>
+      <c r="C156" s="19"/>
+      <c r="D156" s="15"/>
+      <c r="E156" s="15"/>
+      <c r="F156" s="15"/>
+      <c r="G156" s="15"/>
+      <c r="H156" s="15"/>
+      <c r="I156" s="15"/>
+      <c r="J156" s="13"/>
+      <c r="K156" s="13"/>
+      <c r="L156" s="13"/>
+      <c r="M156" s="20"/>
+      <c r="N156" s="20"/>
+      <c r="O156" s="20"/>
+      <c r="P156" s="19"/>
+      <c r="Q156" s="19"/>
+    </row>
+    <row r="157" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A157" s="22"/>
+      <c r="B157" s="22"/>
+      <c r="C157" s="19"/>
+      <c r="D157" s="15"/>
+      <c r="E157" s="15"/>
+      <c r="F157" s="15"/>
+      <c r="G157" s="15"/>
+      <c r="H157" s="15"/>
+      <c r="I157" s="15"/>
+      <c r="J157" s="13"/>
+      <c r="K157" s="13"/>
+      <c r="L157" s="13"/>
+      <c r="M157" s="20"/>
+      <c r="N157" s="20"/>
+      <c r="O157" s="20"/>
+      <c r="P157" s="19"/>
+      <c r="Q157" s="19"/>
+    </row>
+    <row r="158" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A158" s="22"/>
+      <c r="B158" s="22"/>
+      <c r="C158" s="19"/>
+      <c r="D158" s="15"/>
+      <c r="E158" s="15"/>
+      <c r="F158" s="15"/>
+      <c r="G158" s="15"/>
+      <c r="H158" s="15"/>
+      <c r="I158" s="15"/>
+      <c r="J158" s="13"/>
+      <c r="K158" s="13"/>
+      <c r="L158" s="13"/>
+      <c r="M158" s="20"/>
+      <c r="N158" s="20"/>
+      <c r="O158" s="20"/>
+      <c r="P158" s="19"/>
+      <c r="Q158" s="19"/>
+    </row>
+    <row r="159" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A159" s="22"/>
+      <c r="B159" s="22"/>
+      <c r="C159" s="19"/>
+      <c r="D159" s="15"/>
+      <c r="E159" s="15"/>
+      <c r="F159" s="15"/>
+      <c r="G159" s="15"/>
+      <c r="H159" s="15"/>
+      <c r="I159" s="15"/>
+      <c r="J159" s="13"/>
+      <c r="K159" s="13"/>
+      <c r="L159" s="13"/>
+      <c r="M159" s="20"/>
+      <c r="N159" s="20"/>
+      <c r="O159" s="20"/>
+      <c r="P159" s="19"/>
+      <c r="Q159" s="19"/>
+    </row>
+    <row r="160" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A160" s="22"/>
+      <c r="B160" s="22"/>
+      <c r="C160" s="19"/>
+      <c r="D160" s="15"/>
+      <c r="E160" s="15"/>
+      <c r="F160" s="15"/>
+      <c r="G160" s="15"/>
+      <c r="H160" s="15"/>
+      <c r="I160" s="15"/>
+      <c r="J160" s="13"/>
+      <c r="K160" s="13"/>
+      <c r="L160" s="13"/>
+      <c r="M160" s="20"/>
+      <c r="N160" s="20"/>
+      <c r="O160" s="20"/>
+      <c r="P160" s="19"/>
+      <c r="Q160" s="19"/>
+    </row>
+    <row r="161" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A161" s="22"/>
+      <c r="B161" s="22"/>
+      <c r="C161" s="19"/>
+      <c r="D161" s="15"/>
+      <c r="E161" s="15"/>
+      <c r="F161" s="15"/>
+      <c r="G161" s="15"/>
+      <c r="H161" s="15"/>
+      <c r="I161" s="15"/>
+      <c r="J161" s="13"/>
+      <c r="K161" s="13"/>
+      <c r="L161" s="13"/>
+      <c r="M161" s="20"/>
+      <c r="N161" s="20"/>
+      <c r="O161" s="20"/>
+      <c r="P161" s="19"/>
+      <c r="Q161" s="19"/>
+    </row>
+    <row r="162" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A162" s="22"/>
+      <c r="B162" s="22"/>
+      <c r="C162" s="19"/>
+      <c r="D162" s="15"/>
+      <c r="E162" s="15"/>
+      <c r="F162" s="15"/>
+      <c r="G162" s="15"/>
+      <c r="H162" s="15"/>
+      <c r="I162" s="15"/>
+      <c r="J162" s="13"/>
+      <c r="K162" s="13"/>
+      <c r="L162" s="13"/>
+      <c r="M162" s="20"/>
+      <c r="N162" s="20"/>
+      <c r="O162" s="20"/>
+      <c r="P162" s="19"/>
+      <c r="Q162" s="19"/>
+    </row>
+    <row r="163" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A163" s="22"/>
+      <c r="B163" s="22"/>
+      <c r="C163" s="19"/>
+      <c r="D163" s="15"/>
+      <c r="E163" s="15"/>
+      <c r="F163" s="15"/>
+      <c r="G163" s="15"/>
+      <c r="H163" s="15"/>
+      <c r="I163" s="15"/>
+      <c r="J163" s="13"/>
+      <c r="K163" s="13"/>
+      <c r="L163" s="13"/>
+      <c r="M163" s="20"/>
+      <c r="N163" s="20"/>
+      <c r="O163" s="20"/>
+      <c r="P163" s="19"/>
+      <c r="Q163" s="19"/>
+    </row>
+    <row r="164" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A164" s="22"/>
+      <c r="B164" s="22"/>
+      <c r="C164" s="19"/>
+      <c r="D164" s="15"/>
+      <c r="E164" s="15"/>
+      <c r="F164" s="15"/>
+      <c r="G164" s="15"/>
+      <c r="H164" s="15"/>
+      <c r="I164" s="15"/>
+      <c r="J164" s="13"/>
+      <c r="K164" s="13"/>
+      <c r="L164" s="13"/>
+      <c r="M164" s="20"/>
+      <c r="N164" s="20"/>
+      <c r="O164" s="20"/>
+      <c r="P164" s="19"/>
+      <c r="Q164" s="19"/>
+    </row>
+    <row r="165" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A165" s="22"/>
+      <c r="B165" s="22"/>
+      <c r="C165" s="19"/>
+      <c r="D165" s="15"/>
+      <c r="E165" s="15"/>
+      <c r="F165" s="15"/>
+      <c r="G165" s="15"/>
+      <c r="H165" s="15"/>
+      <c r="I165" s="15"/>
+      <c r="J165" s="13"/>
+      <c r="K165" s="13"/>
+      <c r="L165" s="13"/>
+      <c r="M165" s="20"/>
+      <c r="N165" s="20"/>
+      <c r="O165" s="20"/>
+      <c r="P165" s="19"/>
+      <c r="Q165" s="19"/>
+    </row>
+    <row r="166" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A166" s="22"/>
+      <c r="B166" s="22"/>
+      <c r="C166" s="19"/>
+      <c r="D166" s="15"/>
+      <c r="E166" s="15"/>
+      <c r="F166" s="15"/>
+      <c r="G166" s="15"/>
+      <c r="H166" s="15"/>
+      <c r="I166" s="15"/>
+      <c r="J166" s="13"/>
+      <c r="K166" s="13"/>
+      <c r="L166" s="13"/>
+      <c r="M166" s="20"/>
+      <c r="N166" s="20"/>
+      <c r="O166" s="20"/>
+      <c r="P166" s="19"/>
+      <c r="Q166" s="19"/>
+    </row>
+    <row r="167" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A167" s="22"/>
+      <c r="B167" s="22"/>
+      <c r="C167" s="19"/>
+      <c r="D167" s="15"/>
+      <c r="E167" s="15"/>
+      <c r="F167" s="15"/>
+      <c r="G167" s="15"/>
+      <c r="H167" s="15"/>
+      <c r="I167" s="15"/>
+      <c r="J167" s="13"/>
+      <c r="K167" s="13"/>
+      <c r="L167" s="13"/>
+      <c r="M167" s="20"/>
+      <c r="N167" s="20"/>
+      <c r="O167" s="20"/>
+      <c r="P167" s="19"/>
+      <c r="Q167" s="19"/>
+    </row>
+    <row r="168" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A168" s="22"/>
+      <c r="B168" s="22"/>
+      <c r="C168" s="19"/>
+      <c r="D168" s="15"/>
+      <c r="E168" s="15"/>
+      <c r="F168" s="15"/>
+      <c r="G168" s="15"/>
+      <c r="H168" s="15"/>
+      <c r="I168" s="15"/>
+      <c r="J168" s="13"/>
+      <c r="K168" s="13"/>
+      <c r="L168" s="13"/>
+      <c r="M168" s="20"/>
+      <c r="N168" s="20"/>
+      <c r="O168" s="20"/>
+      <c r="P168" s="19"/>
+      <c r="Q168" s="19"/>
+    </row>
+    <row r="169" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A169" s="22"/>
+      <c r="B169" s="22"/>
+      <c r="C169" s="19"/>
+      <c r="D169" s="15"/>
+      <c r="E169" s="15"/>
+      <c r="F169" s="15"/>
+      <c r="G169" s="15"/>
+      <c r="H169" s="15"/>
+      <c r="I169" s="15"/>
+      <c r="J169" s="13"/>
+      <c r="K169" s="13"/>
+      <c r="L169" s="13"/>
+      <c r="M169" s="20"/>
+      <c r="N169" s="20"/>
+      <c r="O169" s="20"/>
+      <c r="P169" s="19"/>
+      <c r="Q169" s="19"/>
+    </row>
+    <row r="170" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A170" s="22"/>
+      <c r="B170" s="22"/>
+      <c r="C170" s="19"/>
+      <c r="D170" s="15"/>
+      <c r="E170" s="15"/>
+      <c r="F170" s="15"/>
+      <c r="G170" s="15"/>
+      <c r="H170" s="15"/>
+      <c r="I170" s="15"/>
+      <c r="J170" s="13"/>
+      <c r="K170" s="13"/>
+      <c r="L170" s="13"/>
+      <c r="M170" s="20"/>
+      <c r="N170" s="20"/>
+      <c r="O170" s="20"/>
+      <c r="P170" s="19"/>
+      <c r="Q170" s="19"/>
+    </row>
+    <row r="171" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A171" s="22"/>
+      <c r="B171" s="22"/>
+      <c r="C171" s="19"/>
+      <c r="D171" s="15"/>
+      <c r="E171" s="15"/>
+      <c r="F171" s="15"/>
+      <c r="G171" s="15"/>
+      <c r="H171" s="15"/>
+      <c r="I171" s="15"/>
+      <c r="J171" s="13"/>
+      <c r="K171" s="13"/>
+      <c r="L171" s="13"/>
+      <c r="M171" s="20"/>
+      <c r="N171" s="20"/>
+      <c r="O171" s="20"/>
+      <c r="P171" s="19"/>
+      <c r="Q171" s="19"/>
+    </row>
+    <row r="172" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A172" s="22"/>
+      <c r="B172" s="22"/>
+      <c r="C172" s="19"/>
+      <c r="D172" s="15"/>
+      <c r="E172" s="15"/>
+      <c r="F172" s="15"/>
+      <c r="G172" s="15"/>
+      <c r="H172" s="15"/>
+      <c r="I172" s="15"/>
+      <c r="J172" s="13"/>
+      <c r="K172" s="13"/>
+      <c r="L172" s="13"/>
+      <c r="M172" s="20"/>
+      <c r="N172" s="20"/>
+      <c r="O172" s="20"/>
+      <c r="P172" s="19"/>
+      <c r="Q172" s="19"/>
+    </row>
+    <row r="173" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A173" s="22"/>
+      <c r="B173" s="22"/>
+      <c r="C173" s="19"/>
+      <c r="D173" s="15"/>
+      <c r="E173" s="15"/>
+      <c r="F173" s="15"/>
+      <c r="G173" s="15"/>
+      <c r="H173" s="15"/>
+      <c r="I173" s="15"/>
+      <c r="J173" s="13"/>
+      <c r="K173" s="13"/>
+      <c r="L173" s="13"/>
+      <c r="M173" s="20"/>
+      <c r="N173" s="20"/>
+      <c r="O173" s="20"/>
+      <c r="P173" s="19"/>
+      <c r="Q173" s="19"/>
+    </row>
+    <row r="174" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A174" s="22"/>
+      <c r="B174" s="22"/>
+      <c r="C174" s="19"/>
+      <c r="D174" s="15"/>
+      <c r="E174" s="15"/>
+      <c r="F174" s="15"/>
+      <c r="G174" s="15"/>
+      <c r="H174" s="15"/>
+      <c r="I174" s="15"/>
+      <c r="J174" s="13"/>
+      <c r="K174" s="13"/>
+      <c r="L174" s="13"/>
+      <c r="M174" s="20"/>
+      <c r="N174" s="20"/>
+      <c r="O174" s="20"/>
+      <c r="P174" s="19"/>
+      <c r="Q174" s="19"/>
+    </row>
+    <row r="175" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A175" s="22"/>
+      <c r="B175" s="22"/>
+      <c r="C175" s="19"/>
+      <c r="D175" s="15"/>
+      <c r="E175" s="15"/>
+      <c r="F175" s="15"/>
+      <c r="G175" s="15"/>
+      <c r="H175" s="15"/>
+      <c r="I175" s="15"/>
+      <c r="J175" s="13"/>
+      <c r="K175" s="13"/>
+      <c r="L175" s="13"/>
+      <c r="M175" s="20"/>
+      <c r="N175" s="20"/>
+      <c r="O175" s="20"/>
+      <c r="P175" s="19"/>
+      <c r="Q175" s="19"/>
+    </row>
+    <row r="176" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A176" s="22"/>
+      <c r="B176" s="22"/>
+      <c r="C176" s="19"/>
+      <c r="D176" s="15"/>
+      <c r="E176" s="15"/>
+      <c r="F176" s="15"/>
+      <c r="G176" s="15"/>
+      <c r="H176" s="15"/>
+      <c r="I176" s="15"/>
+      <c r="J176" s="13"/>
+      <c r="K176" s="13"/>
+      <c r="L176" s="13"/>
+      <c r="M176" s="20"/>
+      <c r="N176" s="20"/>
+      <c r="O176" s="20"/>
+      <c r="P176" s="19"/>
+      <c r="Q176" s="19"/>
+    </row>
+    <row r="177" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A177" s="22"/>
+      <c r="B177" s="22"/>
+      <c r="C177" s="19"/>
+      <c r="D177" s="15"/>
+      <c r="E177" s="15"/>
+      <c r="F177" s="15"/>
+      <c r="G177" s="15"/>
+      <c r="H177" s="15"/>
+      <c r="I177" s="15"/>
+      <c r="J177" s="13"/>
+      <c r="K177" s="13"/>
+      <c r="L177" s="13"/>
+      <c r="M177" s="20"/>
+      <c r="N177" s="20"/>
+      <c r="O177" s="20"/>
+      <c r="P177" s="19"/>
+      <c r="Q177" s="19"/>
+    </row>
+    <row r="178" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A178" s="22"/>
+      <c r="B178" s="22"/>
+      <c r="C178" s="19"/>
+      <c r="D178" s="15"/>
+      <c r="E178" s="15"/>
+      <c r="F178" s="15"/>
+      <c r="G178" s="15"/>
+      <c r="H178" s="15"/>
+      <c r="I178" s="15"/>
+      <c r="J178" s="13"/>
+      <c r="K178" s="13"/>
+      <c r="L178" s="13"/>
+      <c r="M178" s="20"/>
+      <c r="N178" s="20"/>
+      <c r="O178" s="20"/>
+      <c r="P178" s="19"/>
+      <c r="Q178" s="19"/>
+    </row>
+    <row r="179" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A179" s="22"/>
+      <c r="B179" s="22"/>
+      <c r="C179" s="19"/>
+      <c r="D179" s="15"/>
+      <c r="E179" s="15"/>
+      <c r="F179" s="15"/>
+      <c r="G179" s="15"/>
+      <c r="H179" s="15"/>
+      <c r="I179" s="15"/>
+      <c r="J179" s="13"/>
+      <c r="K179" s="13"/>
+      <c r="L179" s="13"/>
+      <c r="M179" s="20"/>
+      <c r="N179" s="20"/>
+      <c r="O179" s="20"/>
+      <c r="P179" s="19"/>
+      <c r="Q179" s="19"/>
+    </row>
+    <row r="180" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A180" s="22"/>
+      <c r="B180" s="22"/>
+      <c r="C180" s="19"/>
+      <c r="D180" s="15"/>
+      <c r="E180" s="15"/>
+      <c r="F180" s="15"/>
+      <c r="G180" s="15"/>
+      <c r="H180" s="15"/>
+      <c r="I180" s="15"/>
+      <c r="J180" s="13"/>
+      <c r="K180" s="13"/>
+      <c r="L180" s="13"/>
+      <c r="M180" s="20"/>
+      <c r="N180" s="20"/>
+      <c r="O180" s="20"/>
+      <c r="P180" s="19"/>
+      <c r="Q180" s="19"/>
+    </row>
+    <row r="181" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A181" s="22"/>
+      <c r="B181" s="22"/>
+      <c r="C181" s="19"/>
+      <c r="D181" s="15"/>
+      <c r="E181" s="15"/>
+      <c r="F181" s="15"/>
+      <c r="G181" s="15"/>
+      <c r="H181" s="15"/>
+      <c r="I181" s="15"/>
+      <c r="J181" s="13"/>
+      <c r="K181" s="13"/>
+      <c r="L181" s="13"/>
+      <c r="M181" s="20"/>
+      <c r="N181" s="20"/>
+      <c r="O181" s="20"/>
+      <c r="P181" s="19"/>
+      <c r="Q181" s="19"/>
+    </row>
+    <row r="182" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A182" s="22"/>
+      <c r="B182" s="22"/>
+      <c r="C182" s="19"/>
+      <c r="D182" s="15"/>
+      <c r="E182" s="15"/>
+      <c r="F182" s="15"/>
+      <c r="G182" s="15"/>
+      <c r="H182" s="15"/>
+      <c r="I182" s="15"/>
+      <c r="J182" s="13"/>
+      <c r="K182" s="13"/>
+      <c r="L182" s="13"/>
+      <c r="M182" s="20"/>
+      <c r="N182" s="20"/>
+      <c r="O182" s="20"/>
+      <c r="P182" s="19"/>
+      <c r="Q182" s="19"/>
+    </row>
+    <row r="183" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A183" s="22"/>
+      <c r="B183" s="22"/>
+      <c r="C183" s="19"/>
+      <c r="D183" s="15"/>
+      <c r="E183" s="15"/>
+      <c r="F183" s="15"/>
+      <c r="G183" s="15"/>
+      <c r="H183" s="15"/>
+      <c r="I183" s="15"/>
+      <c r="J183" s="13"/>
+      <c r="K183" s="13"/>
+      <c r="L183" s="13"/>
+      <c r="M183" s="20"/>
+      <c r="N183" s="20"/>
+      <c r="O183" s="20"/>
+      <c r="P183" s="19"/>
+      <c r="Q183" s="19"/>
+    </row>
+    <row r="184" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A184" s="22"/>
+      <c r="B184" s="22"/>
+      <c r="C184" s="19"/>
+      <c r="D184" s="15"/>
+      <c r="E184" s="15"/>
+      <c r="F184" s="15"/>
+      <c r="G184" s="15"/>
+      <c r="H184" s="15"/>
+      <c r="I184" s="15"/>
+      <c r="J184" s="13"/>
+      <c r="K184" s="13"/>
+      <c r="L184" s="13"/>
+      <c r="M184" s="20"/>
+      <c r="N184" s="20"/>
+      <c r="O184" s="20"/>
+      <c r="P184" s="19"/>
+      <c r="Q184" s="19"/>
+    </row>
+    <row r="185" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A185" s="22"/>
+      <c r="B185" s="22"/>
+      <c r="C185" s="19"/>
+      <c r="D185" s="15"/>
+      <c r="E185" s="15"/>
+      <c r="F185" s="15"/>
+      <c r="G185" s="15"/>
+      <c r="H185" s="15"/>
+      <c r="I185" s="15"/>
+      <c r="J185" s="13"/>
+      <c r="K185" s="13"/>
+      <c r="L185" s="13"/>
+      <c r="M185" s="20"/>
+      <c r="N185" s="20"/>
+      <c r="O185" s="20"/>
+      <c r="P185" s="19"/>
+      <c r="Q185" s="19"/>
+    </row>
+    <row r="186" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A186" s="22"/>
+      <c r="B186" s="22"/>
+      <c r="C186" s="19"/>
+      <c r="D186" s="15"/>
+      <c r="E186" s="15"/>
+      <c r="F186" s="15"/>
+      <c r="G186" s="15"/>
+      <c r="H186" s="15"/>
+      <c r="I186" s="15"/>
+      <c r="J186" s="13"/>
+      <c r="K186" s="13"/>
+      <c r="L186" s="13"/>
+      <c r="M186" s="20"/>
+      <c r="N186" s="20"/>
+      <c r="O186" s="20"/>
+      <c r="P186" s="19"/>
+      <c r="Q186" s="19"/>
+    </row>
+    <row r="187" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A187" s="22"/>
+      <c r="B187" s="22"/>
+      <c r="C187" s="19"/>
+      <c r="D187" s="15"/>
+      <c r="E187" s="15"/>
+      <c r="F187" s="15"/>
+      <c r="G187" s="15"/>
+      <c r="H187" s="15"/>
+      <c r="I187" s="15"/>
+      <c r="J187" s="13"/>
+      <c r="K187" s="13"/>
+      <c r="L187" s="13"/>
+      <c r="M187" s="20"/>
+      <c r="N187" s="20"/>
+      <c r="O187" s="20"/>
+      <c r="P187" s="19"/>
+      <c r="Q187" s="19"/>
+    </row>
+    <row r="188" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A188" s="22"/>
+      <c r="B188" s="22"/>
+      <c r="C188" s="19"/>
+      <c r="D188" s="15"/>
+      <c r="E188" s="15"/>
+      <c r="F188" s="15"/>
+      <c r="G188" s="15"/>
+      <c r="H188" s="15"/>
+      <c r="I188" s="15"/>
+      <c r="J188" s="13"/>
+      <c r="K188" s="13"/>
+      <c r="L188" s="13"/>
+      <c r="M188" s="20"/>
+      <c r="N188" s="20"/>
+      <c r="O188" s="20"/>
+      <c r="P188" s="19"/>
+      <c r="Q188" s="19"/>
+    </row>
+    <row r="189" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A189" s="22"/>
+      <c r="B189" s="22"/>
+      <c r="C189" s="19"/>
+      <c r="D189" s="15"/>
+      <c r="E189" s="15"/>
+      <c r="F189" s="15"/>
+      <c r="G189" s="15"/>
+      <c r="H189" s="15"/>
+      <c r="I189" s="15"/>
+      <c r="J189" s="13"/>
+      <c r="K189" s="13"/>
+      <c r="L189" s="13"/>
+      <c r="M189" s="20"/>
+      <c r="N189" s="20"/>
+      <c r="O189" s="20"/>
+      <c r="P189" s="19"/>
+      <c r="Q189" s="19"/>
+    </row>
+    <row r="190" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A190" s="22"/>
+      <c r="B190" s="22"/>
+      <c r="C190" s="19"/>
+      <c r="D190" s="15"/>
+      <c r="E190" s="15"/>
+      <c r="F190" s="15"/>
+      <c r="G190" s="15"/>
+      <c r="H190" s="15"/>
+      <c r="I190" s="15"/>
+      <c r="J190" s="13"/>
+      <c r="K190" s="13"/>
+      <c r="L190" s="13"/>
+      <c r="M190" s="20"/>
+      <c r="N190" s="20"/>
+      <c r="O190" s="20"/>
+      <c r="P190" s="19"/>
+      <c r="Q190" s="19"/>
+    </row>
+    <row r="191" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A191" s="22"/>
+      <c r="B191" s="22"/>
+      <c r="C191" s="19"/>
+      <c r="D191" s="15"/>
+      <c r="E191" s="15"/>
+      <c r="F191" s="15"/>
+      <c r="G191" s="15"/>
+      <c r="H191" s="15"/>
+      <c r="I191" s="15"/>
+      <c r="J191" s="13"/>
+      <c r="K191" s="13"/>
+      <c r="L191" s="13"/>
+      <c r="M191" s="20"/>
+      <c r="N191" s="20"/>
+      <c r="O191" s="20"/>
+      <c r="P191" s="19"/>
+      <c r="Q191" s="19"/>
+    </row>
+    <row r="192" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A192" s="22"/>
+      <c r="B192" s="22"/>
+      <c r="C192" s="19"/>
+      <c r="D192" s="15"/>
+      <c r="E192" s="15"/>
+      <c r="F192" s="15"/>
+      <c r="G192" s="15"/>
+      <c r="H192" s="15"/>
+      <c r="I192" s="15"/>
+      <c r="J192" s="13"/>
+      <c r="K192" s="13"/>
+      <c r="L192" s="13"/>
+      <c r="M192" s="20"/>
+      <c r="N192" s="20"/>
+      <c r="O192" s="20"/>
+      <c r="P192" s="19"/>
+      <c r="Q192" s="19"/>
+    </row>
+    <row r="193" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A193" s="22"/>
+      <c r="B193" s="22"/>
+      <c r="C193" s="19"/>
+      <c r="D193" s="15"/>
+      <c r="E193" s="15"/>
+      <c r="F193" s="15"/>
+      <c r="G193" s="15"/>
+      <c r="H193" s="15"/>
+      <c r="I193" s="15"/>
+      <c r="J193" s="13"/>
+      <c r="K193" s="13"/>
+      <c r="L193" s="13"/>
+      <c r="M193" s="20"/>
+      <c r="N193" s="20"/>
+      <c r="O193" s="20"/>
+      <c r="P193" s="19"/>
+      <c r="Q193" s="19"/>
+    </row>
+    <row r="194" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A194" s="22"/>
+      <c r="B194" s="22"/>
+      <c r="C194" s="19"/>
+      <c r="D194" s="15"/>
+      <c r="E194" s="15"/>
+      <c r="F194" s="15"/>
+      <c r="G194" s="15"/>
+      <c r="H194" s="15"/>
+      <c r="I194" s="15"/>
+      <c r="J194" s="13"/>
+      <c r="K194" s="13"/>
+      <c r="L194" s="13"/>
+      <c r="M194" s="20"/>
+      <c r="N194" s="20"/>
+      <c r="O194" s="20"/>
+      <c r="P194" s="19"/>
+      <c r="Q194" s="19"/>
+    </row>
+    <row r="195" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A195" s="22"/>
+      <c r="B195" s="22"/>
+      <c r="C195" s="19"/>
+      <c r="D195" s="15"/>
+      <c r="E195" s="15"/>
+      <c r="F195" s="15"/>
+      <c r="G195" s="15"/>
+      <c r="H195" s="15"/>
+      <c r="I195" s="15"/>
+      <c r="J195" s="13"/>
+      <c r="K195" s="13"/>
+      <c r="L195" s="13"/>
+      <c r="M195" s="20"/>
+      <c r="N195" s="20"/>
+      <c r="O195" s="20"/>
+      <c r="P195" s="19"/>
+      <c r="Q195" s="19"/>
+    </row>
+    <row r="196" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A196" s="22"/>
+      <c r="B196" s="22"/>
+      <c r="C196" s="19"/>
+      <c r="D196" s="15"/>
+      <c r="E196" s="15"/>
+      <c r="F196" s="15"/>
+      <c r="G196" s="15"/>
+      <c r="H196" s="15"/>
+      <c r="I196" s="15"/>
+      <c r="J196" s="13"/>
+      <c r="K196" s="13"/>
+      <c r="L196" s="13"/>
+      <c r="M196" s="20"/>
+      <c r="N196" s="20"/>
+      <c r="O196" s="20"/>
+      <c r="P196" s="19"/>
+      <c r="Q196" s="19"/>
+    </row>
+    <row r="197" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A197" s="22"/>
+      <c r="B197" s="22"/>
+      <c r="C197" s="19"/>
+      <c r="D197" s="15"/>
+      <c r="E197" s="15"/>
+      <c r="F197" s="15"/>
+      <c r="G197" s="15"/>
+      <c r="H197" s="15"/>
+      <c r="I197" s="15"/>
+      <c r="J197" s="13"/>
+      <c r="K197" s="13"/>
+      <c r="L197" s="13"/>
+      <c r="M197" s="20"/>
+      <c r="N197" s="20"/>
+      <c r="O197" s="20"/>
+      <c r="P197" s="19"/>
+      <c r="Q197" s="19"/>
+    </row>
+    <row r="198" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A198" s="22"/>
+      <c r="B198" s="22"/>
+      <c r="C198" s="19"/>
+      <c r="D198" s="15"/>
+      <c r="E198" s="15"/>
+      <c r="F198" s="15"/>
+      <c r="G198" s="15"/>
+      <c r="H198" s="15"/>
+      <c r="I198" s="15"/>
+      <c r="J198" s="13"/>
+      <c r="K198" s="13"/>
+      <c r="L198" s="13"/>
+      <c r="M198" s="20"/>
+      <c r="N198" s="20"/>
+      <c r="O198" s="20"/>
+      <c r="P198" s="19"/>
+      <c r="Q198" s="19"/>
+    </row>
+    <row r="199" spans="1:17" ht="24.95" customHeight="1">
+      <c r="A199" s="22"/>
+      <c r="B199" s="22"/>
+      <c r="C199" s="19"/>
+      <c r="D199" s="15"/>
+      <c r="E199" s="15"/>
+      <c r="F199" s="15"/>
+      <c r="G199" s="15"/>
+      <c r="H199" s="15"/>
+      <c r="I199" s="15"/>
+      <c r="J199" s="13"/>
+      <c r="K199" s="13"/>
+      <c r="L199" s="13"/>
+      <c r="M199" s="20"/>
+      <c r="N199" s="20"/>
+      <c r="O199" s="20"/>
+      <c r="P199" s="19"/>
+      <c r="Q199" s="19"/>
+    </row>
+    <row r="200" spans="1:17">
+      <c r="A200" s="22"/>
+      <c r="B200" s="22"/>
+      <c r="C200" s="19"/>
+      <c r="D200" s="15"/>
+      <c r="E200" s="15"/>
+      <c r="F200" s="15"/>
+      <c r="G200" s="15"/>
+      <c r="H200" s="15"/>
+      <c r="I200" s="15"/>
+      <c r="J200" s="13"/>
+      <c r="K200" s="13"/>
+      <c r="L200" s="13"/>
+      <c r="M200" s="20"/>
+      <c r="N200" s="20"/>
+      <c r="O200" s="20"/>
+      <c r="P200" s="19"/>
+      <c r="Q200" s="19"/>
+    </row>
+    <row r="201" spans="1:17">
+      <c r="A201" s="22"/>
+      <c r="B201" s="22"/>
+      <c r="C201" s="19"/>
+      <c r="D201" s="15"/>
+      <c r="E201" s="15"/>
+      <c r="F201" s="15"/>
+      <c r="G201" s="15"/>
+      <c r="H201" s="15"/>
+      <c r="I201" s="15"/>
+      <c r="J201" s="13"/>
+      <c r="K201" s="13"/>
+      <c r="L201" s="13"/>
+      <c r="M201" s="20"/>
+      <c r="N201" s="20"/>
+      <c r="O201" s="20"/>
+      <c r="P201" s="19"/>
+      <c r="Q201" s="19"/>
+    </row>
+    <row r="202" spans="1:17">
+      <c r="A202" s="22"/>
+      <c r="B202" s="22"/>
+      <c r="C202" s="19"/>
+      <c r="D202" s="15"/>
+      <c r="E202" s="15"/>
+      <c r="F202" s="15"/>
+      <c r="G202" s="15"/>
+      <c r="H202" s="15"/>
+      <c r="I202" s="15"/>
+      <c r="J202" s="13"/>
+      <c r="K202" s="13"/>
+      <c r="L202" s="13"/>
+      <c r="M202" s="20"/>
+      <c r="N202" s="20"/>
+      <c r="O202" s="20"/>
+      <c r="P202" s="19"/>
+      <c r="Q202" s="19"/>
+    </row>
+    <row r="203" spans="1:17">
+      <c r="A203" s="22"/>
+      <c r="B203" s="22"/>
+      <c r="C203" s="19"/>
+      <c r="D203" s="15"/>
+      <c r="E203" s="15"/>
+      <c r="F203" s="15"/>
+      <c r="G203" s="15"/>
+      <c r="H203" s="15"/>
+      <c r="I203" s="15"/>
+      <c r="J203" s="13"/>
+      <c r="K203" s="13"/>
+      <c r="L203" s="13"/>
+      <c r="M203" s="20"/>
+      <c r="N203" s="20"/>
+      <c r="O203" s="20"/>
+      <c r="P203" s="19"/>
+      <c r="Q203" s="19"/>
+    </row>
+    <row r="204" spans="1:17">
+      <c r="A204" s="22"/>
+      <c r="B204" s="22"/>
+      <c r="C204" s="19"/>
+      <c r="D204" s="15"/>
+      <c r="E204" s="15"/>
+      <c r="F204" s="15"/>
+      <c r="G204" s="15"/>
+      <c r="H204" s="15"/>
+      <c r="I204" s="15"/>
+      <c r="J204" s="13"/>
+      <c r="K204" s="13"/>
+      <c r="L204" s="13"/>
+      <c r="M204" s="20"/>
+      <c r="N204" s="20"/>
+      <c r="O204" s="20"/>
+      <c r="P204" s="19"/>
+      <c r="Q204" s="19"/>
+    </row>
+    <row r="205" spans="1:17">
+      <c r="A205" s="22"/>
+      <c r="B205" s="22"/>
+      <c r="C205" s="19"/>
+      <c r="D205" s="15"/>
+      <c r="E205" s="15"/>
+      <c r="F205" s="15"/>
+      <c r="G205" s="15"/>
+      <c r="H205" s="15"/>
+      <c r="I205" s="15"/>
+      <c r="J205" s="13"/>
+      <c r="K205" s="13"/>
+      <c r="L205" s="13"/>
+      <c r="M205" s="20"/>
+      <c r="N205" s="20"/>
+      <c r="O205" s="20"/>
+      <c r="P205" s="19"/>
+      <c r="Q205" s="19"/>
+    </row>
+    <row r="206" spans="1:17">
+      <c r="A206" s="22"/>
+      <c r="B206" s="22"/>
+      <c r="C206" s="19"/>
+      <c r="D206" s="15"/>
+      <c r="E206" s="15"/>
+      <c r="F206" s="15"/>
+      <c r="G206" s="15"/>
+      <c r="H206" s="15"/>
+      <c r="I206" s="15"/>
+      <c r="J206" s="13"/>
+      <c r="K206" s="13"/>
+      <c r="L206" s="13"/>
+      <c r="M206" s="20"/>
+      <c r="N206" s="20"/>
+      <c r="O206" s="20"/>
+      <c r="P206" s="19"/>
+      <c r="Q206" s="19"/>
+    </row>
+    <row r="207" spans="1:17">
+      <c r="A207" s="22"/>
+      <c r="B207" s="22"/>
+      <c r="C207" s="19"/>
+      <c r="D207" s="15"/>
+      <c r="E207" s="15"/>
+      <c r="F207" s="15"/>
+      <c r="G207" s="15"/>
+      <c r="H207" s="15"/>
+      <c r="I207" s="15"/>
+      <c r="J207" s="13"/>
+      <c r="K207" s="13"/>
+      <c r="L207" s="13"/>
+      <c r="M207" s="20"/>
+      <c r="N207" s="20"/>
+      <c r="O207" s="20"/>
+      <c r="P207" s="19"/>
+      <c r="Q207" s="19"/>
+    </row>
+    <row r="208" spans="1:17">
+      <c r="A208" s="22"/>
+      <c r="B208" s="22"/>
+      <c r="C208" s="19"/>
+      <c r="D208" s="15"/>
+      <c r="E208" s="15"/>
+      <c r="F208" s="15"/>
+      <c r="G208" s="15"/>
+      <c r="H208" s="15"/>
+      <c r="I208" s="15"/>
+      <c r="J208" s="13"/>
+      <c r="K208" s="13"/>
+      <c r="L208" s="13"/>
+      <c r="M208" s="20"/>
+      <c r="N208" s="20"/>
+      <c r="O208" s="20"/>
+      <c r="P208" s="19"/>
+      <c r="Q208" s="19"/>
+    </row>
+    <row r="209" spans="1:17">
+      <c r="A209" s="22"/>
+      <c r="B209" s="22"/>
+      <c r="C209" s="19"/>
+      <c r="D209" s="15"/>
+      <c r="E209" s="15"/>
+      <c r="F209" s="15"/>
+      <c r="G209" s="15"/>
+      <c r="H209" s="15"/>
+      <c r="I209" s="15"/>
+      <c r="J209" s="13"/>
+      <c r="K209" s="13"/>
+      <c r="L209" s="13"/>
+      <c r="M209" s="20"/>
+      <c r="N209" s="20"/>
+      <c r="O209" s="20"/>
+      <c r="P209" s="19"/>
+      <c r="Q209" s="19"/>
+    </row>
+    <row r="210" spans="1:17">
+      <c r="A210" s="22"/>
+      <c r="B210" s="22"/>
+      <c r="C210" s="19"/>
+      <c r="D210" s="15"/>
+      <c r="E210" s="15"/>
+      <c r="F210" s="15"/>
+      <c r="G210" s="15"/>
+      <c r="H210" s="15"/>
+      <c r="I210" s="15"/>
+      <c r="J210" s="13"/>
+      <c r="K210" s="13"/>
+      <c r="L210" s="13"/>
+      <c r="M210" s="20"/>
+      <c r="N210" s="20"/>
+      <c r="O210" s="20"/>
+      <c r="P210" s="19"/>
+      <c r="Q210" s="19"/>
+    </row>
+    <row r="211" spans="1:17">
+      <c r="A211" s="22"/>
+      <c r="B211" s="22"/>
+      <c r="C211" s="19"/>
+      <c r="D211" s="15"/>
+      <c r="E211" s="15"/>
+      <c r="F211" s="15"/>
+      <c r="G211" s="15"/>
+      <c r="H211" s="15"/>
+      <c r="I211" s="15"/>
+      <c r="J211" s="13"/>
+      <c r="K211" s="13"/>
+      <c r="L211" s="13"/>
+      <c r="M211" s="20"/>
+      <c r="N211" s="20"/>
+      <c r="O211" s="20"/>
+      <c r="P211" s="19"/>
+      <c r="Q211" s="19"/>
+    </row>
+    <row r="212" spans="1:17">
+      <c r="A212" s="22"/>
+      <c r="B212" s="22"/>
+      <c r="C212" s="19"/>
+      <c r="D212" s="15"/>
+      <c r="E212" s="15"/>
+      <c r="F212" s="15"/>
+      <c r="G212" s="15"/>
+      <c r="H212" s="15"/>
+      <c r="I212" s="15"/>
+      <c r="J212" s="13"/>
+      <c r="K212" s="13"/>
+      <c r="L212" s="13"/>
+      <c r="M212" s="20"/>
+      <c r="N212" s="20"/>
+      <c r="O212" s="20"/>
+      <c r="P212" s="19"/>
+      <c r="Q212" s="19"/>
+    </row>
+    <row r="213" spans="1:17">
+      <c r="A213" s="22"/>
+      <c r="B213" s="22"/>
+      <c r="C213" s="19"/>
+      <c r="D213" s="15"/>
+      <c r="E213" s="15"/>
+      <c r="F213" s="15"/>
+      <c r="G213" s="15"/>
+      <c r="H213" s="15"/>
+      <c r="I213" s="15"/>
+      <c r="J213" s="13"/>
+      <c r="K213" s="13"/>
+      <c r="L213" s="13"/>
+      <c r="M213" s="20"/>
+      <c r="N213" s="20"/>
+      <c r="O213" s="20"/>
+      <c r="P213" s="19"/>
+      <c r="Q213" s="19"/>
+    </row>
+    <row r="214" spans="1:17">
+      <c r="A214" s="22"/>
+      <c r="B214" s="22"/>
+      <c r="C214" s="19"/>
+      <c r="D214" s="15"/>
+      <c r="E214" s="15"/>
+      <c r="F214" s="15"/>
+      <c r="G214" s="15"/>
+      <c r="H214" s="15"/>
+      <c r="I214" s="15"/>
+      <c r="J214" s="13"/>
+      <c r="K214" s="13"/>
+      <c r="L214" s="13"/>
+      <c r="M214" s="20"/>
+      <c r="N214" s="20"/>
+      <c r="O214" s="20"/>
+      <c r="P214" s="19"/>
+      <c r="Q214" s="19"/>
+    </row>
+    <row r="215" spans="1:17">
+      <c r="A215" s="22"/>
+      <c r="B215" s="22"/>
+      <c r="C215" s="19"/>
+      <c r="D215" s="15"/>
+      <c r="E215" s="15"/>
+      <c r="F215" s="15"/>
+      <c r="G215" s="15"/>
+      <c r="H215" s="15"/>
+      <c r="I215" s="15"/>
+      <c r="J215" s="13"/>
+      <c r="K215" s="13"/>
+      <c r="L215" s="13"/>
+      <c r="M215" s="20"/>
+      <c r="N215" s="20"/>
+      <c r="O215" s="20"/>
+      <c r="P215" s="19"/>
+      <c r="Q215" s="19"/>
+    </row>
+    <row r="216" spans="1:17">
+      <c r="A216" s="22"/>
+      <c r="B216" s="22"/>
+      <c r="C216" s="19"/>
+      <c r="D216" s="15"/>
+      <c r="E216" s="15"/>
+      <c r="F216" s="15"/>
+      <c r="G216" s="15"/>
+      <c r="H216" s="15"/>
+      <c r="I216" s="15"/>
+      <c r="J216" s="13"/>
+      <c r="K216" s="13"/>
+      <c r="L216" s="13"/>
+      <c r="M216" s="20"/>
+      <c r="N216" s="20"/>
+      <c r="O216" s="20"/>
+      <c r="P216" s="19"/>
+      <c r="Q216" s="19"/>
+    </row>
+    <row r="217" spans="1:17">
+      <c r="A217" s="22"/>
+      <c r="B217" s="22"/>
+      <c r="C217" s="19"/>
+      <c r="D217" s="15"/>
+      <c r="E217" s="15"/>
+      <c r="F217" s="15"/>
+      <c r="G217" s="15"/>
+      <c r="H217" s="15"/>
+      <c r="I217" s="15"/>
+      <c r="J217" s="13"/>
+      <c r="K217" s="13"/>
+      <c r="L217" s="13"/>
+      <c r="M217" s="20"/>
+      <c r="N217" s="20"/>
+      <c r="O217" s="20"/>
+      <c r="P217" s="19"/>
+      <c r="Q217" s="19"/>
+    </row>
+    <row r="218" spans="1:17">
+      <c r="A218" s="22"/>
+      <c r="B218" s="22"/>
+      <c r="C218" s="19"/>
+      <c r="D218" s="15"/>
+      <c r="E218" s="15"/>
+      <c r="F218" s="15"/>
+      <c r="G218" s="15"/>
+      <c r="H218" s="15"/>
+      <c r="I218" s="15"/>
+      <c r="J218" s="13"/>
+      <c r="K218" s="13"/>
+      <c r="L218" s="13"/>
+      <c r="M218" s="20"/>
+      <c r="N218" s="20"/>
+      <c r="O218" s="20"/>
+      <c r="P218" s="19"/>
+      <c r="Q218" s="19"/>
+    </row>
+    <row r="219" spans="1:17">
+      <c r="A219" s="22"/>
+      <c r="B219" s="22"/>
+      <c r="C219" s="19"/>
+      <c r="D219" s="15"/>
+      <c r="E219" s="15"/>
+      <c r="F219" s="15"/>
+      <c r="G219" s="15"/>
+      <c r="H219" s="15"/>
+      <c r="I219" s="15"/>
+      <c r="J219" s="13"/>
+      <c r="K219" s="13"/>
+      <c r="L219" s="13"/>
+      <c r="M219" s="20"/>
+      <c r="N219" s="20"/>
+      <c r="O219" s="20"/>
+      <c r="P219" s="19"/>
+      <c r="Q219" s="19"/>
+    </row>
+    <row r="220" spans="1:17">
+      <c r="A220" s="22"/>
+      <c r="B220" s="22"/>
+      <c r="C220" s="19"/>
+      <c r="D220" s="15"/>
+      <c r="E220" s="15"/>
+      <c r="F220" s="15"/>
+      <c r="G220" s="15"/>
+      <c r="H220" s="15"/>
+      <c r="I220" s="15"/>
+      <c r="J220" s="13"/>
+      <c r="K220" s="13"/>
+      <c r="L220" s="13"/>
+      <c r="M220" s="20"/>
+      <c r="N220" s="20"/>
+      <c r="O220" s="20"/>
+      <c r="P220" s="19"/>
+      <c r="Q220" s="19"/>
+    </row>
+    <row r="221" spans="1:17">
+      <c r="A221" s="22"/>
+      <c r="B221" s="22"/>
+      <c r="C221" s="19"/>
+      <c r="D221" s="15"/>
+      <c r="E221" s="15"/>
+      <c r="F221" s="15"/>
+      <c r="G221" s="15"/>
+      <c r="H221" s="15"/>
+      <c r="I221" s="15"/>
+      <c r="J221" s="13"/>
+      <c r="K221" s="13"/>
+      <c r="L221" s="13"/>
+      <c r="M221" s="20"/>
+      <c r="N221" s="20"/>
+      <c r="O221" s="20"/>
+      <c r="P221" s="19"/>
+      <c r="Q221" s="19"/>
+    </row>
+    <row r="222" spans="1:17">
+      <c r="A222" s="22"/>
+      <c r="B222" s="22"/>
+      <c r="C222" s="19"/>
+      <c r="D222" s="15"/>
+      <c r="E222" s="15"/>
+      <c r="F222" s="15"/>
+      <c r="G222" s="15"/>
+      <c r="H222" s="15"/>
+      <c r="I222" s="15"/>
+      <c r="J222" s="13"/>
+      <c r="K222" s="13"/>
+      <c r="L222" s="13"/>
+      <c r="M222" s="20"/>
+      <c r="N222" s="20"/>
+      <c r="O222" s="20"/>
+      <c r="P222" s="19"/>
+      <c r="Q222" s="19"/>
+    </row>
+    <row r="223" spans="1:17">
+      <c r="A223" s="22"/>
+      <c r="B223" s="22"/>
+      <c r="C223" s="19"/>
+      <c r="D223" s="15"/>
+      <c r="E223" s="15"/>
+      <c r="F223" s="15"/>
+      <c r="G223" s="15"/>
+      <c r="H223" s="15"/>
+      <c r="I223" s="15"/>
+      <c r="J223" s="13"/>
+      <c r="K223" s="13"/>
+      <c r="L223" s="13"/>
+      <c r="M223" s="20"/>
+      <c r="N223" s="20"/>
+      <c r="O223" s="20"/>
+      <c r="P223" s="19"/>
+      <c r="Q223" s="19"/>
+    </row>
+    <row r="224" spans="1:17">
+      <c r="A224" s="22"/>
+      <c r="B224" s="22"/>
+      <c r="C224" s="19"/>
+      <c r="D224" s="15"/>
+      <c r="E224" s="15"/>
+      <c r="F224" s="15"/>
+      <c r="G224" s="15"/>
+      <c r="H224" s="15"/>
+      <c r="I224" s="15"/>
+      <c r="J224" s="13"/>
+      <c r="K224" s="13"/>
+      <c r="L224" s="13"/>
+      <c r="M224" s="20"/>
+      <c r="N224" s="20"/>
+      <c r="O224" s="20"/>
+      <c r="P224" s="19"/>
+      <c r="Q224" s="19"/>
+    </row>
+    <row r="225" spans="1:17">
+      <c r="A225" s="22"/>
+      <c r="B225" s="22"/>
+      <c r="C225" s="19"/>
+      <c r="D225" s="15"/>
+      <c r="E225" s="15"/>
+      <c r="F225" s="15"/>
+      <c r="G225" s="15"/>
+      <c r="H225" s="15"/>
+      <c r="I225" s="15"/>
+      <c r="J225" s="13"/>
+      <c r="K225" s="13"/>
+      <c r="L225" s="13"/>
+      <c r="M225" s="20"/>
+      <c r="N225" s="20"/>
+      <c r="O225" s="20"/>
+      <c r="P225" s="19"/>
+      <c r="Q225" s="19"/>
     </row>
   </sheetData>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" sqref="D2:I101">
+    <dataValidation type="list" sqref="D2:I225">
       <formula1>"1,0,예,아니오"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="J2:O101">
+    <dataValidation type="list" sqref="J2:O225">
       <formula1>"1,0,가능,불가,미확인"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6916,10 +9979,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="41.25" customHeight="1">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="14" t="s">
         <v>216</v>
       </c>
-      <c r="B1" s="20"/>
+      <c r="B1" s="14"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="1"/>
